--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="984">
   <si>
     <t>Dog</t>
   </si>
@@ -591,6 +591,12 @@
     <t>Tongue_Regular</t>
   </si>
   <si>
+    <t>Nose</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
     <t>Ears_Happy</t>
   </si>
   <si>
@@ -651,6 +657,12 @@
     <t>舌头</t>
   </si>
   <si>
+    <t>鼻子</t>
+  </si>
+  <si>
+    <t>嘴巴</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -814,6 +826,12 @@
   </si>
   <si>
     <t>Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
+    <t>Nose_Brown.png</t>
+  </si>
+  <si>
+    <t>Mouse_Natural.png</t>
   </si>
   <si>
     <t>新狗狗 1013</t>
@@ -4568,31 +4586,31 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F1" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="G1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="H1" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="I1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="J1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4609,19 +4627,19 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="G2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="J2" t="s">
         <v>109</v>
@@ -4632,31 +4650,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4664,1471 +4682,1471 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C4" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F4" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G4" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="H4" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="I4" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G5" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H5" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D6" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G6" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H6" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="D7" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G7" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H7" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="D8" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G8" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H8" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="D9" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G9" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H9" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D10" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G10" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H10" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="D11" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G11" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H11" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="D12" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G12" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H12" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="D13" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G13" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H13" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="D14" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G14" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H14" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D15" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G15" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H15" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D16" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G16" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H16" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="D17" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G17" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H17" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="D18" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G18" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H18" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D19" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G19" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H19" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D20" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G20" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H20" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D21" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G21" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H21" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D22" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G22" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H22" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D23" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G23" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H23" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D24" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G24" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H24" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D25" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G25" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H25" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="D26" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G26" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H26" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="D27" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G27" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H27" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D28" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G28" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H28" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="D29" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G29" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H29" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D30" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G30" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H30" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="D31" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G31" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H31" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D32" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G32" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H32" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="D33" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G33" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H33" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="D34" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G34" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H34" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="D35" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G35" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H35" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="D36" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G36" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H36" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D37" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G37" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H37" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="D38" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G38" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H38" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D39" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G39" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H39" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D40" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G40" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H40" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="D41" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G41" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H41" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="D42" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G42" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H42" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D43" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G43" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H43" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D44" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G44" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H44" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D45" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G45" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H45" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="D46" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G46" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H46" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D47" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G47" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H47" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="D48" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G48" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H48" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="D49" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G49" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H49" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6136,28 +6154,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="D50" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G50" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H50" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6165,28 +6183,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D51" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G51" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="H51" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6194,28 +6212,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="D52" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G52" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H52" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6223,28 +6241,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D53" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G53" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H53" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6252,28 +6270,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D54" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G54" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H54" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6281,28 +6299,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D55" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G55" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H55" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6310,28 +6328,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D56" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G56" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H56" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6339,28 +6357,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="D57" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G57" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H57" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6368,28 +6386,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D58" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G58" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H58" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6397,28 +6415,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="D59" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G59" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H59" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6426,28 +6444,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D60" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G60" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H60" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6455,28 +6473,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="D61" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G61" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H61" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6484,92 +6502,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="D62" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="G62" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H62" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="D63" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G63" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H63" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="D64" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G64" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="H64" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6577,28 +6595,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="D65" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G65" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="H65" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -6633,25 +6651,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="C1" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="D1" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="E1" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="F1" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="G1" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="H1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6665,7 +6683,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6685,28 +6703,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6714,39 +6732,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="C4" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D4" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="E4" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="F4" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="G4" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="H4" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="I4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B5" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="C5" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6764,18 +6782,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B6" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="C6" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6793,18 +6811,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B7" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="C7" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6822,18 +6840,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="C8" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6851,18 +6869,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="C9" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6880,18 +6898,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C10" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6909,18 +6927,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="C11" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6938,18 +6956,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B12" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="C12" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6967,7 +6985,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +7484,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -7477,17 +7495,19 @@
     <col min="10" max="10" width="16.5833333333333" customWidth="1"/>
     <col min="11" max="11" width="18.5" customWidth="1"/>
     <col min="12" max="13" width="20.8333333333333" customWidth="1"/>
-    <col min="14" max="14" width="14.5" customWidth="1"/>
-    <col min="15" max="15" width="13.4166666666667" customWidth="1"/>
-    <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="14.8333333333333" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="15.4166666666667" customWidth="1"/>
-    <col min="21" max="21" width="13.4166666666667" customWidth="1"/>
+    <col min="14" max="14" width="15.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="15.9513888888889" customWidth="1"/>
+    <col min="16" max="16" width="14.5" customWidth="1"/>
+    <col min="17" max="17" width="13.4166666666667" customWidth="1"/>
+    <col min="18" max="18" width="14.3333333333333" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="14.8333333333333" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
+    <col min="23" max="23" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -7551,8 +7571,14 @@
       <c r="U1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="V1" t="s">
+        <v>192</v>
+      </c>
+      <c r="W1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -7616,8 +7642,14 @@
       <c r="U2" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:22">
+      <c r="V2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:24">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
@@ -7625,17 +7657,17 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>110</v>
       </c>
@@ -7643,875 +7675,911 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="R4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="S4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+        <v>213</v>
+      </c>
+      <c r="V4" t="s">
+        <v>214</v>
+      </c>
+      <c r="W4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T5" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24">
       <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T7" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24">
       <c r="B8" s="2">
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T8" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24">
       <c r="B9" s="2">
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V9" s="2"/>
-    </row>
-    <row r="10" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24">
       <c r="B10" s="2">
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T10" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V10" s="2"/>
-    </row>
-    <row r="11" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24">
       <c r="B11" s="2">
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V11" s="2"/>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24">
       <c r="B12" s="2">
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V12" s="2"/>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="W12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24">
       <c r="B13" s="2">
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S13" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T13" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V13" s="2"/>
-    </row>
-    <row r="14" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24">
       <c r="B14" s="2">
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T14" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V14" s="2"/>
-    </row>
-    <row r="15" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24">
       <c r="B15" s="2">
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S15" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T15" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V15" s="2"/>
-    </row>
-    <row r="16" spans="1:22">
+        <v>228</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24">
       <c r="B16" s="2">
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S16" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T16" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="2:22">
+        <v>228</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="2:24">
       <c r="B17" s="2">
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S17" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="T17" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="V17" s="2"/>
-    </row>
-    <row r="18" spans="2:22">
+        <v>228</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="2:24">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -8532,8 +8600,10 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
-    </row>
-    <row r="19" spans="2:22">
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="2:24">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8554,8 +8624,10 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
-    </row>
-    <row r="20" spans="2:22">
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="2:24">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -8576,8 +8648,10 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
-    </row>
-    <row r="21" spans="2:22">
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="2:24">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -8598,8 +8672,10 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-    </row>
-    <row r="22" spans="2:22">
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="2:24">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -8620,8 +8696,10 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
-    </row>
-    <row r="23" spans="2:22">
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="2:24">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -8642,8 +8720,10 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
-    </row>
-    <row r="24" spans="2:22">
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="2:24">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -8664,8 +8744,10 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-    </row>
-    <row r="25" spans="2:22">
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+    </row>
+    <row r="25" spans="2:24">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -8686,8 +8768,10 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-    </row>
-    <row r="26" spans="2:22">
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+    </row>
+    <row r="26" spans="2:24">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -8708,8 +8792,10 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
-    </row>
-    <row r="27" spans="2:22">
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+    </row>
+    <row r="27" spans="2:24">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -8730,8 +8816,10 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
-    </row>
-    <row r="28" spans="2:22">
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+    </row>
+    <row r="28" spans="2:24">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -8752,8 +8840,10 @@
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
-    </row>
-    <row r="29" spans="2:22">
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+    </row>
+    <row r="29" spans="2:24">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -8774,8 +8864,10 @@
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
-    </row>
-    <row r="30" spans="2:22">
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+    </row>
+    <row r="30" spans="2:24">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -8796,6 +8888,8 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8823,16 +8917,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8846,7 +8940,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -8871,16 +8965,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8894,10 +8988,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8905,16 +8999,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8928,10 +9022,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8945,10 +9039,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8962,10 +9056,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F9" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8973,16 +9067,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D10" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8996,10 +9090,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F11" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9013,10 +9107,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F12" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -9049,34 +9143,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="J1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="L1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -9087,10 +9181,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -9102,7 +9196,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -9124,16 +9218,16 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9144,40 +9238,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E4" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G4" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H4" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="I4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J4" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="K4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="L4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -9200,13 +9294,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9220,22 +9314,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L6" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M6" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9249,22 +9343,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L7" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M7" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9278,22 +9372,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L8" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -9307,22 +9401,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L9" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M9" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -9336,22 +9430,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L10" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M10" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -9365,22 +9459,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L11" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -9394,22 +9488,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L12" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -9417,31 +9511,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="L13" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M13" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -9449,10 +9543,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9461,7 +9555,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -9469,10 +9563,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9481,7 +9575,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -9489,10 +9583,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9501,7 +9595,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -9509,19 +9603,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F17" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="N17" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -9529,10 +9623,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9541,7 +9635,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -9549,10 +9643,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9561,7 +9655,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9569,10 +9663,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9581,7 +9675,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9589,19 +9683,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E21" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F21" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="N21" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -9609,16 +9703,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -9626,10 +9720,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9643,10 +9737,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9660,10 +9754,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9677,10 +9771,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9694,10 +9788,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9711,10 +9805,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -9728,10 +9822,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -9740,10 +9834,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N29" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -9751,10 +9845,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -9768,10 +9862,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -9785,10 +9879,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -9797,10 +9891,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N32" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -9808,10 +9902,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -9820,7 +9914,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -9856,31 +9950,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="I1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="J1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="K1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -9906,10 +10000,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -9923,34 +10017,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -9961,31 +10055,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D4" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E4" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G4" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H4" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="I4" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="J4" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="K4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -9993,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10017,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10025,7 +10119,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10049,7 +10143,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10057,7 +10151,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10081,7 +10175,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10089,7 +10183,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10113,7 +10207,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -10144,16 +10238,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F1" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10170,7 +10264,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -10183,10 +10277,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10197,13 +10291,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D4" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10211,7 +10305,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10220,7 +10314,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10228,7 +10322,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10237,7 +10331,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10245,7 +10339,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10254,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10262,7 +10356,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10271,7 +10365,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10309,43 +10403,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="G1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="H1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="I1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="K1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="L1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10359,19 +10453,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -10397,43 +10491,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="K3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="L3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="M3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="N3" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10441,60 +10535,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C4" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D4" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E4" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="F4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G4" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="H4" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="I4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J4" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="K4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="L4" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="M4" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="N4" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10506,39 +10600,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="J5" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="K5" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="L5" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="M5" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="N5" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10550,39 +10644,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="J6" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K6" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="L6" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="M6" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="N6" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10594,39 +10688,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="J7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K7" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="L7" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="M7" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="N7" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10638,39 +10732,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="J8" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="K8" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="L8" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="M8" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="N8" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10682,39 +10776,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="J9" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="K9" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="L9" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="M9" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="N9" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -10726,39 +10820,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="J10" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="K10" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="L10" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="M10" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="N10" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -10770,39 +10864,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="J11" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="K11" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="L11" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="M11" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="N11" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -10814,39 +10908,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="J12" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="K12" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="L12" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="M12" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="N12" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -10858,39 +10952,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="J13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="K13" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L13" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="M13" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="N13" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -10902,39 +10996,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="J14" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="K14" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="L14" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="M14" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="N14" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -10946,42 +11040,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="J15" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="K15" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L15" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="M15" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="N15" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F16" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -10990,42 +11084,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="J16" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="K16" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="L16" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="M16" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="N16" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F17" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11034,42 +11128,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="J17" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="K17" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="L17" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="M17" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="N17" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F18" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11078,42 +11172,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="J18" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="K18" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L18" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="M18" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="N18" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F19" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11122,42 +11216,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="J19" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K19" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="L19" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="M19" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="N19" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F20" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11166,42 +11260,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="J20" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="K20" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="L20" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="M20" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="N20" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F21" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11210,42 +11304,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J21" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K21" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="L21" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="M21" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="N21" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F22" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11254,42 +11348,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="J22" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="K22" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="L22" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M22" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="N22" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F23" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11298,42 +11392,42 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J23" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="K23" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="L23" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M23" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="N23" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F24" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -11342,42 +11436,42 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="J24" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="K24" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="L24" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="M24" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="N24" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F25" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11386,22 +11480,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="L25" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="M25" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="N25" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11409,13 +11503,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11427,22 +11521,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="J26" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="K26" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="L26" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="M26" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="N26" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11450,16 +11544,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F27" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11468,39 +11562,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="J27" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="K27" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L27" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="M27" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="N27" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11512,39 +11606,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="J28" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="K28" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L28" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="M28" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="N28" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11556,39 +11650,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="J29" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="K29" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="L29" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="M29" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="N29" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11600,42 +11694,42 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="J30" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="K30" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="L30" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="M30" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="N30" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F31" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -11644,22 +11738,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="J31" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="K31" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="L31" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="M31" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="N31" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11667,16 +11761,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F32" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11685,22 +11779,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="J32" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="K32" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="L32" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="M32" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="N32" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="985">
   <si>
     <t>Dog</t>
   </si>
@@ -826,6 +826,9 @@
   </si>
   <si>
     <t>Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
+    <t>v0\Shiba\Sesame</t>
   </si>
   <si>
     <t>Nose_Brown.png</t>
@@ -4586,31 +4589,31 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4627,19 +4630,19 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J2" t="s">
         <v>109</v>
@@ -4650,31 +4653,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4682,1471 +4685,1471 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D6" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G6" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D7" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G7" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G9" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G10" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H10" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G11" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H11" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G12" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D13" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G14" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D15" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G15" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D16" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G16" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H16" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D17" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G17" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H17" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D18" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G18" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H18" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D19" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H19" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D20" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G20" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H20" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D21" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G21" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H21" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D22" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G22" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H22" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D23" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G23" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H23" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D24" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G24" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H24" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D25" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G25" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H25" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D26" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G26" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H26" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D27" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G27" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H27" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D28" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G28" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H28" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D29" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G29" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H29" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D30" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G30" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H30" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D31" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G31" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H31" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D32" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G32" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H32" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D33" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G33" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H33" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D34" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G34" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H34" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D35" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G35" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H35" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D36" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G36" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H36" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D37" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G37" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H37" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D38" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G38" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H38" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D39" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G39" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H39" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D40" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G40" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H40" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D41" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G41" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H41" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D42" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G42" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H42" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D43" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G43" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H43" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D44" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G44" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H44" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D45" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G45" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H45" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D46" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G46" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H46" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D47" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G47" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H47" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D48" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G48" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H48" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D49" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G49" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H49" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6154,28 +6157,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D50" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G50" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H50" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6183,28 +6186,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D51" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G51" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H51" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6212,28 +6215,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D52" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G52" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H52" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6241,28 +6244,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D53" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G53" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H53" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6270,28 +6273,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D54" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G54" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H54" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6299,28 +6302,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D55" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G55" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H55" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6328,28 +6331,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D56" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G56" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H56" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6357,28 +6360,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D57" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G57" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H57" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6386,28 +6389,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D58" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G58" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H58" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6415,28 +6418,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D59" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G59" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H59" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6444,28 +6447,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D60" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G60" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H60" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6473,28 +6476,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D61" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G61" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H61" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6502,92 +6505,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D62" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G62" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H62" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D63" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G63" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H63" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D64" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G64" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H64" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6595,28 +6598,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D65" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G65" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H65" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -6651,25 +6654,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6683,7 +6686,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6703,28 +6706,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6732,39 +6735,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B5" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C5" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6782,18 +6785,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B6" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C6" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6811,18 +6814,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B7" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C7" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6840,18 +6843,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B8" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6869,18 +6872,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6898,18 +6901,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B10" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C10" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6927,18 +6930,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C11" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6956,18 +6959,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C12" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6985,7 +6988,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
   </sheetData>
@@ -8468,7 +8471,7 @@
         <v>250</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>247</v>
@@ -8483,10 +8486,10 @@
         <v>224</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>218</v>
@@ -8519,7 +8522,7 @@
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>217</v>
@@ -8917,16 +8920,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8940,7 +8943,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -8965,16 +8968,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8988,10 +8991,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8999,16 +9002,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9022,10 +9025,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9039,10 +9042,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9056,10 +9059,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9067,16 +9070,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9090,10 +9093,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9107,10 +9110,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -9143,34 +9146,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -9181,10 +9184,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -9196,7 +9199,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -9218,16 +9221,16 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9238,40 +9241,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" t="s">
         <v>312</v>
       </c>
-      <c r="F4" t="s">
-        <v>311</v>
-      </c>
       <c r="G4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M4" t="s">
         <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -9294,13 +9297,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9323,13 +9326,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9352,13 +9355,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9381,13 +9384,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -9410,13 +9413,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -9439,13 +9442,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -9468,13 +9471,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -9497,13 +9500,13 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
+        <v>323</v>
+      </c>
+      <c r="L12" t="s">
+        <v>323</v>
+      </c>
+      <c r="M12" t="s">
         <v>322</v>
-      </c>
-      <c r="L12" t="s">
-        <v>322</v>
-      </c>
-      <c r="M12" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -9511,10 +9514,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G13" t="s">
         <v>186</v>
@@ -9526,16 +9529,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -9543,10 +9546,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9555,7 +9558,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -9563,10 +9566,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9575,7 +9578,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -9583,10 +9586,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9595,7 +9598,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -9603,19 +9606,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -9623,10 +9626,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9635,7 +9638,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -9643,10 +9646,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9655,7 +9658,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9663,10 +9666,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9675,7 +9678,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9683,19 +9686,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E21" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -9703,16 +9706,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -9720,10 +9723,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9737,10 +9740,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9754,10 +9757,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9771,10 +9774,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9788,10 +9791,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9805,10 +9808,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -9822,10 +9825,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -9834,10 +9837,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -9845,10 +9848,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -9862,10 +9865,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -9879,10 +9882,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -9891,10 +9894,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N32" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -9902,10 +9905,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -9914,7 +9917,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -9950,31 +9953,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -10000,10 +10003,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -10017,34 +10020,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -10055,31 +10058,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -10087,7 +10090,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10111,7 +10114,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10119,7 +10122,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10143,7 +10146,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10151,7 +10154,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10175,7 +10178,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10183,7 +10186,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10207,7 +10210,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -10238,16 +10241,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10264,7 +10267,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -10277,10 +10280,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10291,13 +10294,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10305,7 +10308,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10314,7 +10317,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10322,7 +10325,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10331,7 +10334,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10339,7 +10342,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10348,7 +10351,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10356,7 +10359,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10365,7 +10368,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10403,43 +10406,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10453,19 +10456,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -10491,43 +10494,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10535,60 +10538,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10600,39 +10603,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10644,39 +10647,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10688,39 +10691,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10732,39 +10735,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10776,39 +10779,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -10820,39 +10823,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -10864,39 +10867,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -10908,39 +10911,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -10952,39 +10955,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K13" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -10996,39 +10999,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -11040,42 +11043,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -11084,42 +11087,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K16" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L16" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M16" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N16" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F17" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11128,42 +11131,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J17" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K17" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L17" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N17" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F18" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11172,42 +11175,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J18" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M18" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N18" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11216,42 +11219,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F20" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11260,42 +11263,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J20" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K20" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L20" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M20" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N20" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F21" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11304,42 +11307,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J21" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K21" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L21" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N21" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11348,42 +11351,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K22" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L22" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M22" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F23" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11392,42 +11395,42 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J23" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K23" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L23" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M23" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N23" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F24" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -11436,42 +11439,42 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J24" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K24" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L24" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M24" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N24" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F25" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11480,22 +11483,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L25" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M25" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N25" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11503,13 +11506,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11521,22 +11524,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J26" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K26" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L26" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M26" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N26" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11544,16 +11547,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F27" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11562,39 +11565,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J27" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K27" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L27" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M27" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N27" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11606,39 +11609,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J28" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K28" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L28" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M28" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N28" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11650,39 +11653,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J29" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K29" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L29" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M29" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N29" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11694,42 +11697,42 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J30" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="K30" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L30" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M30" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N30" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -11738,22 +11741,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J31" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K31" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L31" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M31" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N31" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11761,16 +11764,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F32" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11779,22 +11782,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J32" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K32" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L32" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M32" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N32" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="984">
   <si>
     <t>Dog</t>
   </si>
@@ -699,67 +699,76 @@
     <t>Eyes_Cute.png</t>
   </si>
   <si>
-    <t>v1\Shiba\Red</t>
+    <t>v0\Shiba\Red</t>
+  </si>
+  <si>
+    <t>Head_Thin.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Left.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.png</t>
+  </si>
+  <si>
+    <t>Tongue_Regular.png</t>
+  </si>
+  <si>
+    <t>Nose_Brown.png</t>
+  </si>
+  <si>
+    <t>Mouse_Natural.png</t>
+  </si>
+  <si>
+    <t>Ears_Plane.png</t>
+  </si>
+  <si>
+    <t>Eyes_Bored.png</t>
+  </si>
+  <si>
+    <t>Eyes_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Lucky.png</t>
+  </si>
+  <si>
+    <t>Eyes_Neutral.png</t>
+  </si>
+  <si>
+    <t>Eyes_Wink.png</t>
+  </si>
+  <si>
+    <t>胖黑柴</t>
+  </si>
+  <si>
+    <t>Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>v0\Shiba\Black</t>
   </si>
   <si>
     <t>Head_Chubby.png</t>
   </si>
   <si>
-    <t>Claw_Lucky_Left.png</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.png</t>
-  </si>
-  <si>
-    <t>Tongue_Regular.png</t>
-  </si>
-  <si>
-    <t>Ears_Plane.png</t>
-  </si>
-  <si>
-    <t>Eyes_Bored.png</t>
-  </si>
-  <si>
-    <t>Eyes_Happy.png</t>
-  </si>
-  <si>
-    <t>Eyes_Lucky.png</t>
-  </si>
-  <si>
-    <t>Eyes_Neutral.png</t>
-  </si>
-  <si>
-    <t>Eyes_Wink.png</t>
-  </si>
-  <si>
-    <t>黑柴</t>
-  </si>
-  <si>
-    <t>Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Black</t>
-  </si>
-  <si>
-    <t>白柴</t>
+    <t>胖白柴</t>
   </si>
   <si>
     <t>Shiba_Cream.png</t>
   </si>
   <si>
-    <t>v1\Shiba\Cream</t>
-  </si>
-  <si>
-    <t>胡麻柴</t>
+    <t>v0\Shiba\Cream</t>
+  </si>
+  <si>
+    <t>胖胡麻柴</t>
   </si>
   <si>
     <t>Shiba_Sesame.png</t>
   </si>
   <si>
-    <t>v1\Shiba\Sesame</t>
-  </si>
-  <si>
-    <t>瘦赤柴</t>
+    <t>v0\Shiba\Sesame</t>
+  </si>
+  <si>
+    <t>胖赤柴</t>
   </si>
   <si>
     <t>Shiba_ThinRed.png</t>
@@ -768,9 +777,6 @@
     <t>Sunglasses_Blade.png</t>
   </si>
   <si>
-    <t>Head_Thin.png</t>
-  </si>
-  <si>
     <t>胡渣赤柴</t>
   </si>
   <si>
@@ -826,15 +832,6 @@
   </si>
   <si>
     <t>Shiba_UnshavenSesame.png</t>
-  </si>
-  <si>
-    <t>v0\Shiba\Sesame</t>
-  </si>
-  <si>
-    <t>Nose_Brown.png</t>
-  </si>
-  <si>
-    <t>Mouse_Natural.png</t>
   </si>
   <si>
     <t>新狗狗 1013</t>
@@ -4589,31 +4586,31 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C1" t="s">
         <v>675</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>676</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" t="s">
         <v>677</v>
       </c>
-      <c r="E1" t="s">
-        <v>427</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>678</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>679</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>680</v>
       </c>
-      <c r="I1" t="s">
-        <v>681</v>
-      </c>
       <c r="J1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4630,19 +4627,19 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
+        <v>681</v>
+      </c>
+      <c r="G2" t="s">
         <v>682</v>
-      </c>
-      <c r="G2" t="s">
-        <v>683</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J2" t="s">
         <v>109</v>
@@ -4653,31 +4650,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4685,1471 +4682,1471 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C4" t="s">
         <v>693</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F4" t="s">
         <v>694</v>
       </c>
-      <c r="D4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E4" t="s">
-        <v>454</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>695</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>696</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>697</v>
       </c>
-      <c r="I4" t="s">
-        <v>698</v>
-      </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>698</v>
+      </c>
+      <c r="D5" t="s">
         <v>699</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
         <v>700</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>701</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>702</v>
-      </c>
-      <c r="H5" t="s">
-        <v>703</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>704</v>
+      </c>
+      <c r="D6" t="s">
         <v>705</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>706</v>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H6" t="s">
         <v>707</v>
-      </c>
-      <c r="G6" t="s">
-        <v>702</v>
-      </c>
-      <c r="H6" t="s">
-        <v>708</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>709</v>
+      </c>
+      <c r="D7" t="s">
         <v>710</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>700</v>
+      </c>
+      <c r="G7" t="s">
+        <v>701</v>
+      </c>
+      <c r="H7" t="s">
         <v>711</v>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>701</v>
-      </c>
-      <c r="G7" t="s">
-        <v>702</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>712</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
+        <v>713</v>
+      </c>
+      <c r="D8" t="s">
         <v>714</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>700</v>
+      </c>
+      <c r="G8" t="s">
+        <v>701</v>
+      </c>
+      <c r="H8" t="s">
         <v>715</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>701</v>
-      </c>
-      <c r="G8" t="s">
-        <v>702</v>
-      </c>
-      <c r="H8" t="s">
-        <v>716</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
+        <v>717</v>
+      </c>
+      <c r="D9" t="s">
         <v>718</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>706</v>
+      </c>
+      <c r="G9" t="s">
+        <v>701</v>
+      </c>
+      <c r="H9" t="s">
         <v>719</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>707</v>
-      </c>
-      <c r="G9" t="s">
-        <v>702</v>
-      </c>
-      <c r="H9" t="s">
-        <v>720</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>721</v>
+      </c>
+      <c r="D10" t="s">
         <v>722</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>723</v>
       </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>701</v>
+      </c>
+      <c r="H10" t="s">
         <v>724</v>
       </c>
-      <c r="G10" t="s">
-        <v>702</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
         <v>725</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
+        <v>726</v>
+      </c>
+      <c r="D11" t="s">
         <v>727</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>706</v>
+      </c>
+      <c r="G11" t="s">
+        <v>701</v>
+      </c>
+      <c r="H11" t="s">
         <v>728</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>707</v>
-      </c>
-      <c r="G11" t="s">
-        <v>702</v>
-      </c>
-      <c r="H11" t="s">
-        <v>729</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>730</v>
+      </c>
+      <c r="D12" t="s">
         <v>731</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>706</v>
+      </c>
+      <c r="G12" t="s">
+        <v>701</v>
+      </c>
+      <c r="H12" t="s">
         <v>732</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>707</v>
-      </c>
-      <c r="G12" t="s">
-        <v>702</v>
-      </c>
-      <c r="H12" t="s">
-        <v>733</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
+        <v>734</v>
+      </c>
+      <c r="D13" t="s">
         <v>735</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>706</v>
+      </c>
+      <c r="G13" t="s">
+        <v>701</v>
+      </c>
+      <c r="H13" t="s">
         <v>736</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>707</v>
-      </c>
-      <c r="G13" t="s">
-        <v>702</v>
-      </c>
-      <c r="H13" t="s">
-        <v>737</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
+        <v>738</v>
+      </c>
+      <c r="D14" t="s">
         <v>739</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>723</v>
+      </c>
+      <c r="G14" t="s">
+        <v>701</v>
+      </c>
+      <c r="H14" t="s">
         <v>740</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>724</v>
-      </c>
-      <c r="G14" t="s">
-        <v>702</v>
-      </c>
-      <c r="H14" t="s">
-        <v>741</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
+        <v>742</v>
+      </c>
+      <c r="D15" t="s">
         <v>743</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>723</v>
+      </c>
+      <c r="G15" t="s">
+        <v>701</v>
+      </c>
+      <c r="H15" t="s">
         <v>744</v>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>724</v>
-      </c>
-      <c r="G15" t="s">
-        <v>702</v>
-      </c>
-      <c r="H15" t="s">
-        <v>745</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
+        <v>746</v>
+      </c>
+      <c r="D16" t="s">
         <v>747</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>706</v>
+      </c>
+      <c r="G16" t="s">
+        <v>701</v>
+      </c>
+      <c r="H16" t="s">
         <v>748</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>707</v>
-      </c>
-      <c r="G16" t="s">
-        <v>702</v>
-      </c>
-      <c r="H16" t="s">
-        <v>749</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
+        <v>750</v>
+      </c>
+      <c r="D17" t="s">
         <v>751</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>706</v>
+      </c>
+      <c r="G17" t="s">
+        <v>701</v>
+      </c>
+      <c r="H17" t="s">
         <v>752</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>707</v>
-      </c>
-      <c r="G17" t="s">
-        <v>702</v>
-      </c>
-      <c r="H17" t="s">
-        <v>753</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
+        <v>754</v>
+      </c>
+      <c r="D18" t="s">
         <v>755</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>706</v>
+      </c>
+      <c r="G18" t="s">
+        <v>701</v>
+      </c>
+      <c r="H18" t="s">
         <v>756</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>707</v>
-      </c>
-      <c r="G18" t="s">
-        <v>702</v>
-      </c>
-      <c r="H18" t="s">
-        <v>757</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D19" t="s">
+        <v>758</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>706</v>
+      </c>
+      <c r="G19" t="s">
+        <v>701</v>
+      </c>
+      <c r="H19" t="s">
         <v>759</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>707</v>
-      </c>
-      <c r="G19" t="s">
-        <v>702</v>
-      </c>
-      <c r="H19" t="s">
-        <v>760</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D20" t="s">
+        <v>761</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>706</v>
+      </c>
+      <c r="G20" t="s">
+        <v>701</v>
+      </c>
+      <c r="H20" t="s">
         <v>762</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>707</v>
-      </c>
-      <c r="G20" t="s">
-        <v>702</v>
-      </c>
-      <c r="H20" t="s">
-        <v>763</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D21" t="s">
+        <v>764</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>706</v>
+      </c>
+      <c r="G21" t="s">
+        <v>701</v>
+      </c>
+      <c r="H21" t="s">
         <v>765</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>707</v>
-      </c>
-      <c r="G21" t="s">
-        <v>702</v>
-      </c>
-      <c r="H21" t="s">
-        <v>766</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D22" t="s">
+        <v>767</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>706</v>
+      </c>
+      <c r="G22" t="s">
+        <v>701</v>
+      </c>
+      <c r="H22" t="s">
         <v>768</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>707</v>
-      </c>
-      <c r="G22" t="s">
-        <v>702</v>
-      </c>
-      <c r="H22" t="s">
-        <v>769</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D23" t="s">
+        <v>770</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>706</v>
+      </c>
+      <c r="G23" t="s">
+        <v>701</v>
+      </c>
+      <c r="H23" t="s">
         <v>771</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>707</v>
-      </c>
-      <c r="G23" t="s">
-        <v>702</v>
-      </c>
-      <c r="H23" t="s">
-        <v>772</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D24" t="s">
+        <v>773</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>706</v>
+      </c>
+      <c r="G24" t="s">
+        <v>701</v>
+      </c>
+      <c r="H24" t="s">
         <v>774</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>707</v>
-      </c>
-      <c r="G24" t="s">
-        <v>702</v>
-      </c>
-      <c r="H24" t="s">
-        <v>775</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D25" t="s">
+        <v>776</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>706</v>
+      </c>
+      <c r="G25" t="s">
+        <v>701</v>
+      </c>
+      <c r="H25" t="s">
         <v>777</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>707</v>
-      </c>
-      <c r="G25" t="s">
-        <v>702</v>
-      </c>
-      <c r="H25" t="s">
-        <v>778</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
+        <v>779</v>
+      </c>
+      <c r="D26" t="s">
         <v>780</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>706</v>
+      </c>
+      <c r="G26" t="s">
+        <v>701</v>
+      </c>
+      <c r="H26" t="s">
         <v>781</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="s">
-        <v>707</v>
-      </c>
-      <c r="G26" t="s">
-        <v>702</v>
-      </c>
-      <c r="H26" t="s">
-        <v>782</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
+        <v>783</v>
+      </c>
+      <c r="D27" t="s">
         <v>784</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>723</v>
+      </c>
+      <c r="G27" t="s">
+        <v>701</v>
+      </c>
+      <c r="H27" t="s">
         <v>785</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s">
-        <v>724</v>
-      </c>
-      <c r="G27" t="s">
-        <v>702</v>
-      </c>
-      <c r="H27" t="s">
-        <v>786</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
+        <v>787</v>
+      </c>
+      <c r="D28" t="s">
         <v>788</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>706</v>
+      </c>
+      <c r="G28" t="s">
+        <v>701</v>
+      </c>
+      <c r="H28" t="s">
         <v>789</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="s">
-        <v>707</v>
-      </c>
-      <c r="G28" t="s">
-        <v>702</v>
-      </c>
-      <c r="H28" t="s">
-        <v>790</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
+        <v>791</v>
+      </c>
+      <c r="D29" t="s">
         <v>792</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>706</v>
+      </c>
+      <c r="G29" t="s">
+        <v>701</v>
+      </c>
+      <c r="H29" t="s">
         <v>793</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>707</v>
-      </c>
-      <c r="G29" t="s">
-        <v>702</v>
-      </c>
-      <c r="H29" t="s">
-        <v>794</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
+        <v>795</v>
+      </c>
+      <c r="D30" t="s">
         <v>796</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>706</v>
+      </c>
+      <c r="G30" t="s">
+        <v>701</v>
+      </c>
+      <c r="H30" t="s">
         <v>797</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>707</v>
-      </c>
-      <c r="G30" t="s">
-        <v>702</v>
-      </c>
-      <c r="H30" t="s">
-        <v>798</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
+        <v>799</v>
+      </c>
+      <c r="D31" t="s">
         <v>800</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>706</v>
+      </c>
+      <c r="G31" t="s">
+        <v>701</v>
+      </c>
+      <c r="H31" t="s">
         <v>801</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" t="s">
-        <v>707</v>
-      </c>
-      <c r="G31" t="s">
-        <v>702</v>
-      </c>
-      <c r="H31" t="s">
-        <v>802</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
+        <v>803</v>
+      </c>
+      <c r="D32" t="s">
         <v>804</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>706</v>
+      </c>
+      <c r="G32" t="s">
+        <v>701</v>
+      </c>
+      <c r="H32" t="s">
         <v>805</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" t="s">
-        <v>707</v>
-      </c>
-      <c r="G32" t="s">
-        <v>702</v>
-      </c>
-      <c r="H32" t="s">
-        <v>806</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
+        <v>807</v>
+      </c>
+      <c r="D33" t="s">
         <v>808</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>706</v>
+      </c>
+      <c r="G33" t="s">
+        <v>701</v>
+      </c>
+      <c r="H33" t="s">
         <v>809</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="s">
-        <v>707</v>
-      </c>
-      <c r="G33" t="s">
-        <v>702</v>
-      </c>
-      <c r="H33" t="s">
-        <v>810</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
+        <v>811</v>
+      </c>
+      <c r="D34" t="s">
         <v>812</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>706</v>
+      </c>
+      <c r="G34" t="s">
+        <v>701</v>
+      </c>
+      <c r="H34" t="s">
         <v>813</v>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>707</v>
-      </c>
-      <c r="G34" t="s">
-        <v>702</v>
-      </c>
-      <c r="H34" t="s">
-        <v>814</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
+        <v>815</v>
+      </c>
+      <c r="D35" t="s">
         <v>816</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>706</v>
+      </c>
+      <c r="G35" t="s">
+        <v>701</v>
+      </c>
+      <c r="H35" t="s">
         <v>817</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" t="s">
-        <v>707</v>
-      </c>
-      <c r="G35" t="s">
-        <v>702</v>
-      </c>
-      <c r="H35" t="s">
-        <v>818</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
+        <v>819</v>
+      </c>
+      <c r="D36" t="s">
         <v>820</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>706</v>
+      </c>
+      <c r="G36" t="s">
+        <v>701</v>
+      </c>
+      <c r="H36" t="s">
         <v>821</v>
-      </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>707</v>
-      </c>
-      <c r="G36" t="s">
-        <v>702</v>
-      </c>
-      <c r="H36" t="s">
-        <v>822</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
+        <v>823</v>
+      </c>
+      <c r="D37" t="s">
         <v>824</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>706</v>
+      </c>
+      <c r="G37" t="s">
+        <v>701</v>
+      </c>
+      <c r="H37" t="s">
         <v>825</v>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" t="s">
-        <v>707</v>
-      </c>
-      <c r="G37" t="s">
-        <v>702</v>
-      </c>
-      <c r="H37" t="s">
-        <v>826</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
+        <v>827</v>
+      </c>
+      <c r="D38" t="s">
         <v>828</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>706</v>
+      </c>
+      <c r="G38" t="s">
+        <v>701</v>
+      </c>
+      <c r="H38" t="s">
         <v>829</v>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" t="s">
-        <v>707</v>
-      </c>
-      <c r="G38" t="s">
-        <v>702</v>
-      </c>
-      <c r="H38" t="s">
-        <v>830</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
+        <v>831</v>
+      </c>
+      <c r="D39" t="s">
         <v>832</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>706</v>
+      </c>
+      <c r="G39" t="s">
+        <v>701</v>
+      </c>
+      <c r="H39" t="s">
         <v>833</v>
-      </c>
-      <c r="E39" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" t="s">
-        <v>707</v>
-      </c>
-      <c r="G39" t="s">
-        <v>702</v>
-      </c>
-      <c r="H39" t="s">
-        <v>834</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
+        <v>835</v>
+      </c>
+      <c r="D40" t="s">
         <v>836</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>706</v>
+      </c>
+      <c r="G40" t="s">
+        <v>701</v>
+      </c>
+      <c r="H40" t="s">
         <v>837</v>
-      </c>
-      <c r="E40" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
-        <v>707</v>
-      </c>
-      <c r="G40" t="s">
-        <v>702</v>
-      </c>
-      <c r="H40" t="s">
-        <v>838</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
+        <v>839</v>
+      </c>
+      <c r="D41" t="s">
         <v>840</v>
-      </c>
-      <c r="D41" t="s">
-        <v>841</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G41" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H41" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
+        <v>843</v>
+      </c>
+      <c r="D42" t="s">
         <v>844</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>706</v>
+      </c>
+      <c r="G42" t="s">
+        <v>701</v>
+      </c>
+      <c r="H42" t="s">
         <v>845</v>
-      </c>
-      <c r="E42" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" t="s">
-        <v>707</v>
-      </c>
-      <c r="G42" t="s">
-        <v>702</v>
-      </c>
-      <c r="H42" t="s">
-        <v>846</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
+        <v>847</v>
+      </c>
+      <c r="D43" t="s">
         <v>848</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>706</v>
+      </c>
+      <c r="G43" t="s">
+        <v>701</v>
+      </c>
+      <c r="H43" t="s">
         <v>849</v>
-      </c>
-      <c r="E43" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>707</v>
-      </c>
-      <c r="G43" t="s">
-        <v>702</v>
-      </c>
-      <c r="H43" t="s">
-        <v>850</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
+        <v>851</v>
+      </c>
+      <c r="D44" t="s">
         <v>852</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>706</v>
+      </c>
+      <c r="G44" t="s">
+        <v>701</v>
+      </c>
+      <c r="H44" t="s">
         <v>853</v>
-      </c>
-      <c r="E44" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
-        <v>707</v>
-      </c>
-      <c r="G44" t="s">
-        <v>702</v>
-      </c>
-      <c r="H44" t="s">
-        <v>854</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
+        <v>855</v>
+      </c>
+      <c r="D45" t="s">
         <v>856</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>706</v>
+      </c>
+      <c r="G45" t="s">
+        <v>701</v>
+      </c>
+      <c r="H45" t="s">
         <v>857</v>
-      </c>
-      <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" t="s">
-        <v>707</v>
-      </c>
-      <c r="G45" t="s">
-        <v>702</v>
-      </c>
-      <c r="H45" t="s">
-        <v>858</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
+        <v>859</v>
+      </c>
+      <c r="D46" t="s">
         <v>860</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>706</v>
+      </c>
+      <c r="G46" t="s">
+        <v>701</v>
+      </c>
+      <c r="H46" t="s">
         <v>861</v>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" t="s">
-        <v>707</v>
-      </c>
-      <c r="G46" t="s">
-        <v>702</v>
-      </c>
-      <c r="H46" t="s">
-        <v>862</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
+        <v>863</v>
+      </c>
+      <c r="D47" t="s">
         <v>864</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>706</v>
+      </c>
+      <c r="G47" t="s">
+        <v>701</v>
+      </c>
+      <c r="H47" t="s">
         <v>865</v>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" t="s">
-        <v>707</v>
-      </c>
-      <c r="G47" t="s">
-        <v>702</v>
-      </c>
-      <c r="H47" t="s">
-        <v>866</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
+        <v>867</v>
+      </c>
+      <c r="D48" t="s">
         <v>868</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>706</v>
+      </c>
+      <c r="G48" t="s">
+        <v>701</v>
+      </c>
+      <c r="H48" t="s">
         <v>869</v>
-      </c>
-      <c r="E48" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" t="s">
-        <v>707</v>
-      </c>
-      <c r="G48" t="s">
-        <v>702</v>
-      </c>
-      <c r="H48" t="s">
-        <v>870</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
+        <v>871</v>
+      </c>
+      <c r="D49" t="s">
         <v>872</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>706</v>
+      </c>
+      <c r="G49" t="s">
+        <v>701</v>
+      </c>
+      <c r="H49" t="s">
         <v>873</v>
-      </c>
-      <c r="E49" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" t="s">
-        <v>707</v>
-      </c>
-      <c r="G49" t="s">
-        <v>702</v>
-      </c>
-      <c r="H49" t="s">
-        <v>874</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6157,28 +6154,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
+        <v>875</v>
+      </c>
+      <c r="D50" t="s">
         <v>876</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>706</v>
+      </c>
+      <c r="G50" t="s">
+        <v>701</v>
+      </c>
+      <c r="H50" t="s">
         <v>877</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" t="s">
-        <v>707</v>
-      </c>
-      <c r="G50" t="s">
-        <v>702</v>
-      </c>
-      <c r="H50" t="s">
-        <v>878</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6186,28 +6183,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
+        <v>879</v>
+      </c>
+      <c r="D51" t="s">
         <v>880</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>723</v>
+      </c>
+      <c r="G51" t="s">
         <v>881</v>
       </c>
-      <c r="E51" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" t="s">
-        <v>724</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>882</v>
-      </c>
-      <c r="H51" t="s">
-        <v>883</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6215,28 +6212,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
+        <v>884</v>
+      </c>
+      <c r="D52" t="s">
         <v>885</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
         <v>886</v>
       </c>
-      <c r="E52" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
+        <v>886</v>
+      </c>
+      <c r="H52" t="s">
         <v>887</v>
       </c>
-      <c r="G52" t="s">
-        <v>887</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
         <v>888</v>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6244,28 +6241,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
+        <v>889</v>
+      </c>
+      <c r="D53" t="s">
         <v>890</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>886</v>
+      </c>
+      <c r="G53" t="s">
+        <v>886</v>
+      </c>
+      <c r="H53" t="s">
         <v>891</v>
       </c>
-      <c r="E53" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" t="s">
-        <v>887</v>
-      </c>
-      <c r="G53" t="s">
-        <v>887</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
         <v>892</v>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6273,28 +6270,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
+        <v>893</v>
+      </c>
+      <c r="D54" t="s">
         <v>894</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>886</v>
+      </c>
+      <c r="G54" t="s">
+        <v>886</v>
+      </c>
+      <c r="H54" t="s">
         <v>895</v>
       </c>
-      <c r="E54" t="b">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>887</v>
-      </c>
-      <c r="G54" t="s">
-        <v>887</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
         <v>896</v>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6302,28 +6299,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
+        <v>897</v>
+      </c>
+      <c r="D55" t="s">
         <v>898</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>886</v>
+      </c>
+      <c r="G55" t="s">
+        <v>886</v>
+      </c>
+      <c r="H55" t="s">
         <v>899</v>
       </c>
-      <c r="E55" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>887</v>
-      </c>
-      <c r="G55" t="s">
-        <v>887</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="s">
         <v>900</v>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6331,28 +6328,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
+        <v>901</v>
+      </c>
+      <c r="D56" t="s">
         <v>902</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>886</v>
+      </c>
+      <c r="G56" t="s">
+        <v>886</v>
+      </c>
+      <c r="H56" t="s">
         <v>903</v>
       </c>
-      <c r="E56" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>887</v>
-      </c>
-      <c r="G56" t="s">
-        <v>887</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="s">
         <v>904</v>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6360,28 +6357,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
+        <v>905</v>
+      </c>
+      <c r="D57" t="s">
         <v>906</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>700</v>
+      </c>
+      <c r="G57" t="s">
+        <v>701</v>
+      </c>
+      <c r="H57" t="s">
         <v>907</v>
       </c>
-      <c r="E57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" t="s">
-        <v>701</v>
-      </c>
-      <c r="G57" t="s">
-        <v>702</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
         <v>908</v>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6389,28 +6386,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
+        <v>909</v>
+      </c>
+      <c r="D58" t="s">
         <v>910</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>706</v>
+      </c>
+      <c r="G58" t="s">
+        <v>701</v>
+      </c>
+      <c r="H58" t="s">
         <v>911</v>
       </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" t="s">
-        <v>707</v>
-      </c>
-      <c r="G58" t="s">
-        <v>702</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="s">
         <v>912</v>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6418,28 +6415,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
+        <v>913</v>
+      </c>
+      <c r="D59" t="s">
         <v>914</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>886</v>
+      </c>
+      <c r="G59" t="s">
+        <v>886</v>
+      </c>
+      <c r="H59" t="s">
         <v>915</v>
       </c>
-      <c r="E59" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" t="s">
-        <v>887</v>
-      </c>
-      <c r="G59" t="s">
-        <v>887</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
         <v>916</v>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6447,28 +6444,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
+        <v>917</v>
+      </c>
+      <c r="D60" t="s">
         <v>918</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>886</v>
+      </c>
+      <c r="G60" t="s">
+        <v>886</v>
+      </c>
+      <c r="H60" t="s">
         <v>919</v>
       </c>
-      <c r="E60" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" t="s">
-        <v>887</v>
-      </c>
-      <c r="G60" t="s">
-        <v>887</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
         <v>920</v>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6476,28 +6473,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
+        <v>921</v>
+      </c>
+      <c r="D61" t="s">
         <v>922</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>886</v>
+      </c>
+      <c r="G61" t="s">
+        <v>886</v>
+      </c>
+      <c r="H61" t="s">
         <v>923</v>
       </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>887</v>
-      </c>
-      <c r="G61" t="s">
-        <v>887</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
         <v>924</v>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6505,92 +6502,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
+        <v>925</v>
+      </c>
+      <c r="D62" t="s">
         <v>926</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>886</v>
+      </c>
+      <c r="G62" t="s">
+        <v>886</v>
+      </c>
+      <c r="H62" t="s">
         <v>927</v>
       </c>
-      <c r="E62" t="b">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>887</v>
-      </c>
-      <c r="G62" t="s">
-        <v>887</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
         <v>928</v>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
+        <v>929</v>
+      </c>
+      <c r="D63" t="s">
         <v>930</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>723</v>
+      </c>
+      <c r="G63" t="s">
+        <v>701</v>
+      </c>
+      <c r="H63" t="s">
         <v>931</v>
       </c>
-      <c r="E63" t="b">
-        <v>1</v>
-      </c>
-      <c r="F63" t="s">
-        <v>724</v>
-      </c>
-      <c r="G63" t="s">
-        <v>702</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
         <v>932</v>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
+        <v>933</v>
+      </c>
+      <c r="D64" t="s">
         <v>934</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>723</v>
+      </c>
+      <c r="G64" t="s">
+        <v>701</v>
+      </c>
+      <c r="H64" t="s">
         <v>935</v>
       </c>
-      <c r="E64" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>724</v>
-      </c>
-      <c r="G64" t="s">
-        <v>702</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
         <v>936</v>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6598,28 +6595,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
+        <v>937</v>
+      </c>
+      <c r="D65" t="s">
         <v>938</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>706</v>
+      </c>
+      <c r="G65" t="s">
+        <v>881</v>
+      </c>
+      <c r="H65" t="s">
         <v>939</v>
       </c>
-      <c r="E65" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" t="s">
-        <v>707</v>
-      </c>
-      <c r="G65" t="s">
-        <v>882</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
         <v>940</v>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="s">
-        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -6654,25 +6651,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>941</v>
+      </c>
+      <c r="C1" t="s">
         <v>942</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>943</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>944</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>945</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>946</v>
       </c>
-      <c r="G1" t="s">
-        <v>947</v>
-      </c>
       <c r="H1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6686,7 +6683,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6706,28 +6703,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>954</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6735,39 +6732,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>955</v>
+      </c>
+      <c r="C4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D4" t="s">
         <v>956</v>
       </c>
-      <c r="C4" t="s">
-        <v>949</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>957</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>958</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>959</v>
       </c>
-      <c r="G4" t="s">
-        <v>960</v>
-      </c>
       <c r="H4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5" t="s">
+        <v>960</v>
+      </c>
+      <c r="C5" t="s">
         <v>961</v>
-      </c>
-      <c r="C5" t="s">
-        <v>962</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6785,18 +6782,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B6" t="s">
+        <v>963</v>
+      </c>
+      <c r="C6" t="s">
         <v>964</v>
-      </c>
-      <c r="C6" t="s">
-        <v>965</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6814,18 +6811,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7" t="s">
+        <v>966</v>
+      </c>
+      <c r="C7" t="s">
         <v>967</v>
-      </c>
-      <c r="C7" t="s">
-        <v>968</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6843,18 +6840,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B8" t="s">
+        <v>969</v>
+      </c>
+      <c r="C8" t="s">
         <v>970</v>
-      </c>
-      <c r="C8" t="s">
-        <v>971</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6872,18 +6869,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
+        <v>972</v>
+      </c>
+      <c r="C9" t="s">
         <v>973</v>
-      </c>
-      <c r="C9" t="s">
-        <v>974</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6901,18 +6898,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
+        <v>975</v>
+      </c>
+      <c r="C10" t="s">
         <v>976</v>
-      </c>
-      <c r="C10" t="s">
-        <v>977</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6930,18 +6927,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
+        <v>978</v>
+      </c>
+      <c r="C11" t="s">
         <v>979</v>
-      </c>
-      <c r="C11" t="s">
-        <v>980</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6959,18 +6956,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B12" t="s">
+        <v>981</v>
+      </c>
+      <c r="C12" t="s">
         <v>982</v>
-      </c>
-      <c r="C12" t="s">
-        <v>983</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6988,7 +6985,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -7776,31 +7773,35 @@
       <c r="M5" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P5" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X5" s="2"/>
     </row>
@@ -7809,10 +7810,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>218</v>
@@ -7825,10 +7826,10 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>222</v>
@@ -7839,31 +7840,35 @@
       <c r="M6" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P6" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X6" s="2"/>
     </row>
@@ -7872,10 +7877,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>218</v>
@@ -7888,10 +7893,10 @@
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>222</v>
@@ -7902,31 +7907,35 @@
       <c r="M7" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P7" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X7" s="2"/>
     </row>
@@ -7935,10 +7944,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>218</v>
@@ -7951,10 +7960,10 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>222</v>
@@ -7965,31 +7974,35 @@
       <c r="M8" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P8" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X8" s="2"/>
     </row>
@@ -7998,28 +8011,28 @@
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>218</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>220</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>222</v>
@@ -8030,31 +8043,35 @@
       <c r="M9" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P9" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X9" s="2"/>
     </row>
@@ -8063,10 +8080,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>218</v>
@@ -8078,13 +8095,13 @@
         <v>183</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>220</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>222</v>
@@ -8095,31 +8112,35 @@
       <c r="M10" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P10" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X10" s="2"/>
     </row>
@@ -8128,28 +8149,28 @@
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>218</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>222</v>
@@ -8160,31 +8181,35 @@
       <c r="M11" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P11" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X11" s="2"/>
     </row>
@@ -8193,10 +8218,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>218</v>
@@ -8208,13 +8233,13 @@
         <v>183</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>222</v>
@@ -8225,31 +8250,35 @@
       <c r="M12" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P12" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X12" s="2"/>
     </row>
@@ -8258,28 +8287,28 @@
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>218</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>222</v>
@@ -8290,31 +8319,35 @@
       <c r="M13" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P13" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X13" s="2"/>
     </row>
@@ -8323,10 +8356,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>218</v>
@@ -8338,13 +8371,13 @@
         <v>183</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>222</v>
@@ -8355,31 +8388,35 @@
       <c r="M14" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="N14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P14" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X14" s="2"/>
     </row>
@@ -8388,10 +8425,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>218</v>
@@ -8403,13 +8440,13 @@
         <v>183</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>222</v>
@@ -8420,31 +8457,35 @@
       <c r="M15" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="N15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P15" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X15" s="2"/>
     </row>
@@ -8453,10 +8494,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>218</v>
@@ -8468,13 +8509,13 @@
         <v>183</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>222</v>
@@ -8486,34 +8527,34 @@
         <v>224</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X16" s="2"/>
     </row>
@@ -8522,7 +8563,7 @@
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>217</v>
@@ -8537,13 +8578,13 @@
         <v>183</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>220</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>222</v>
@@ -8554,31 +8595,35 @@
       <c r="M17" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="P17" s="2" t="s">
         <v>218</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>219</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X17" s="2"/>
     </row>
@@ -8920,16 +8965,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1" t="s">
         <v>267</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>268</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>269</v>
-      </c>
-      <c r="F1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8943,7 +8988,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -8968,16 +9013,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" t="s">
         <v>272</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>273</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>274</v>
-      </c>
-      <c r="F4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8991,10 +9036,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" t="s">
         <v>276</v>
-      </c>
-      <c r="F5" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9002,16 +9047,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" t="s">
         <v>279</v>
-      </c>
-      <c r="F6" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9025,10 +9070,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" t="s">
         <v>281</v>
-      </c>
-      <c r="F7" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9042,10 +9087,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" t="s">
         <v>283</v>
-      </c>
-      <c r="F8" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9059,10 +9104,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F9" t="s">
         <v>285</v>
-      </c>
-      <c r="F9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9070,16 +9115,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" t="s">
         <v>287</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>288</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>289</v>
-      </c>
-      <c r="F10" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9093,10 +9138,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F11" t="s">
         <v>291</v>
-      </c>
-      <c r="F11" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9110,10 +9155,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F12" t="s">
         <v>293</v>
-      </c>
-      <c r="F12" t="s">
-        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -9146,34 +9191,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" t="s">
         <v>295</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>296</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>297</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>298</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>299</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>300</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>301</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>302</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>303</v>
-      </c>
-      <c r="N1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -9184,10 +9229,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -9199,7 +9244,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -9221,16 +9266,16 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9241,40 +9286,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" t="s">
         <v>311</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>312</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" t="s">
         <v>313</v>
       </c>
-      <c r="F4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>314</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>315</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>316</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>317</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>318</v>
-      </c>
-      <c r="L4" t="s">
-        <v>319</v>
       </c>
       <c r="M4" t="s">
         <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -9297,13 +9342,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
+        <v>320</v>
+      </c>
+      <c r="L5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M5" t="s">
         <v>321</v>
-      </c>
-      <c r="L5" t="s">
-        <v>321</v>
-      </c>
-      <c r="M5" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9326,13 +9371,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
+        <v>320</v>
+      </c>
+      <c r="L6" t="s">
+        <v>320</v>
+      </c>
+      <c r="M6" t="s">
         <v>321</v>
-      </c>
-      <c r="L6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9355,13 +9400,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
+        <v>320</v>
+      </c>
+      <c r="L7" t="s">
+        <v>320</v>
+      </c>
+      <c r="M7" t="s">
         <v>321</v>
-      </c>
-      <c r="L7" t="s">
-        <v>321</v>
-      </c>
-      <c r="M7" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9384,13 +9429,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
+        <v>320</v>
+      </c>
+      <c r="L8" t="s">
+        <v>320</v>
+      </c>
+      <c r="M8" t="s">
         <v>321</v>
-      </c>
-      <c r="L8" t="s">
-        <v>321</v>
-      </c>
-      <c r="M8" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -9413,13 +9458,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
+        <v>320</v>
+      </c>
+      <c r="L9" t="s">
+        <v>320</v>
+      </c>
+      <c r="M9" t="s">
         <v>321</v>
-      </c>
-      <c r="L9" t="s">
-        <v>321</v>
-      </c>
-      <c r="M9" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -9442,13 +9487,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
+        <v>320</v>
+      </c>
+      <c r="L10" t="s">
+        <v>320</v>
+      </c>
+      <c r="M10" t="s">
         <v>321</v>
-      </c>
-      <c r="L10" t="s">
-        <v>321</v>
-      </c>
-      <c r="M10" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -9471,13 +9516,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M11" t="s">
         <v>321</v>
-      </c>
-      <c r="L11" t="s">
-        <v>321</v>
-      </c>
-      <c r="M11" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -9500,13 +9545,13 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -9514,10 +9559,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>324</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>325</v>
       </c>
       <c r="G13" t="s">
         <v>186</v>
@@ -9529,16 +9574,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L13" t="s">
+        <v>325</v>
+      </c>
+      <c r="M13" t="s">
         <v>326</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>327</v>
-      </c>
-      <c r="N13" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -9546,10 +9591,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>330</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9558,7 +9603,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -9566,10 +9611,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>332</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>333</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9578,7 +9623,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -9586,10 +9631,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>335</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9598,7 +9643,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -9606,19 +9651,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" t="s">
         <v>339</v>
       </c>
-      <c r="F17" t="s">
+      <c r="N17" t="s">
         <v>340</v>
-      </c>
-      <c r="N17" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -9626,10 +9671,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9638,7 +9683,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -9646,10 +9691,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9658,7 +9703,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9666,10 +9711,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>349</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9678,7 +9723,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9686,19 +9731,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" t="s">
+        <v>338</v>
+      </c>
+      <c r="F21" t="s">
+        <v>339</v>
+      </c>
+      <c r="N21" t="s">
         <v>352</v>
-      </c>
-      <c r="E21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F21" t="s">
-        <v>340</v>
-      </c>
-      <c r="N21" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -9706,16 +9751,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>355</v>
-      </c>
       <c r="E22" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>324</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -9723,10 +9768,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>357</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9740,10 +9785,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9757,10 +9802,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>360</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>361</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9774,10 +9819,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>363</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9791,10 +9836,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9808,10 +9853,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>367</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -9825,10 +9870,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>369</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -9837,10 +9882,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
+        <v>326</v>
+      </c>
+      <c r="N29" t="s">
         <v>327</v>
-      </c>
-      <c r="N29" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -9848,10 +9893,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>370</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>371</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -9865,10 +9910,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>373</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -9882,10 +9927,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>374</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>375</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -9894,10 +9939,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
+        <v>326</v>
+      </c>
+      <c r="N32" t="s">
         <v>327</v>
-      </c>
-      <c r="N32" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -9905,10 +9950,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -9917,7 +9962,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -9953,31 +9998,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" t="s">
         <v>379</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>380</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>381</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>382</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" t="s">
         <v>383</v>
       </c>
-      <c r="H1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>384</v>
       </c>
-      <c r="J1" t="s">
-        <v>385</v>
-      </c>
       <c r="K1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -10003,10 +10048,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I2" t="s">
         <v>305</v>
-      </c>
-      <c r="I2" t="s">
-        <v>306</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -10020,34 +10065,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -10058,31 +10103,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D4" t="s">
         <v>395</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>396</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>397</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>398</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>399</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>400</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>401</v>
       </c>
-      <c r="J4" t="s">
-        <v>402</v>
-      </c>
       <c r="K4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -10090,7 +10135,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10114,7 +10159,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10122,7 +10167,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10146,7 +10191,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10154,7 +10199,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10178,7 +10223,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10186,7 +10231,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10210,7 +10255,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -10241,16 +10286,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E1" t="s">
         <v>409</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>410</v>
-      </c>
-      <c r="F1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10267,7 +10312,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -10280,10 +10325,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10294,13 +10339,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>413</v>
+      </c>
+      <c r="D4" t="s">
         <v>414</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>415</v>
-      </c>
-      <c r="E4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10308,7 +10353,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10317,7 +10362,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10325,7 +10370,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10334,7 +10379,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10342,7 +10387,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10351,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10359,7 +10404,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10368,7 +10413,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10406,43 +10451,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" t="s">
         <v>425</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>426</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>427</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>428</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>429</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>430</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J1" t="s">
         <v>431</v>
       </c>
-      <c r="I1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>432</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>433</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>434</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>435</v>
-      </c>
-      <c r="N1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10456,19 +10501,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -10494,43 +10539,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" t="s">
         <v>446</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>447</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>448</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>449</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>450</v>
-      </c>
-      <c r="N3" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10538,60 +10583,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C4" t="s">
         <v>452</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>453</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>454</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>455</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>456</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>457</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>319</v>
+      </c>
+      <c r="J4" t="s">
         <v>458</v>
       </c>
-      <c r="I4" t="s">
-        <v>320</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>459</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>460</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>461</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>462</v>
-      </c>
-      <c r="N4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>464</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>465</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10603,39 +10648,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
+        <v>465</v>
+      </c>
+      <c r="J5" t="s">
         <v>466</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>467</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>468</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>469</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>470</v>
-      </c>
-      <c r="N5" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10647,39 +10692,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
+        <v>472</v>
+      </c>
+      <c r="J6" t="s">
         <v>473</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>474</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>475</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>476</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>477</v>
-      </c>
-      <c r="N6" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10691,39 +10736,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
+        <v>479</v>
+      </c>
+      <c r="J7" t="s">
         <v>480</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>481</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>482</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>483</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>484</v>
-      </c>
-      <c r="N7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10735,39 +10780,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J8" t="s">
         <v>487</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>488</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>489</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>490</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>491</v>
-      </c>
-      <c r="N8" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10779,39 +10824,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
+        <v>493</v>
+      </c>
+      <c r="J9" t="s">
         <v>494</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>495</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>496</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>497</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>498</v>
-      </c>
-      <c r="N9" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -10823,39 +10868,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
+        <v>500</v>
+      </c>
+      <c r="J10" t="s">
         <v>501</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>502</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>503</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>504</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>505</v>
-      </c>
-      <c r="N10" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -10867,39 +10912,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
+        <v>507</v>
+      </c>
+      <c r="J11" t="s">
         <v>508</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>509</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>510</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>511</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>512</v>
-      </c>
-      <c r="N11" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -10911,39 +10956,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
+        <v>514</v>
+      </c>
+      <c r="J12" t="s">
         <v>515</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>516</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>517</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>518</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>519</v>
-      </c>
-      <c r="N12" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -10955,39 +11000,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
+        <v>521</v>
+      </c>
+      <c r="J13" t="s">
         <v>522</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>523</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>524</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>525</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>526</v>
-      </c>
-      <c r="N13" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -10999,39 +11044,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
+        <v>528</v>
+      </c>
+      <c r="J14" t="s">
         <v>529</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>530</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>531</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>532</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>533</v>
-      </c>
-      <c r="N14" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -11043,42 +11088,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
+        <v>535</v>
+      </c>
+      <c r="J15" t="s">
         <v>536</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>537</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>538</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>539</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>540</v>
-      </c>
-      <c r="N15" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
+        <v>541</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
         <v>542</v>
       </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>543</v>
-      </c>
-      <c r="F16" t="s">
-        <v>544</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -11087,42 +11132,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
+        <v>544</v>
+      </c>
+      <c r="J16" t="s">
         <v>545</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>546</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>547</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>548</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>549</v>
-      </c>
-      <c r="N16" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
+        <v>550</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>542</v>
+      </c>
+      <c r="F17" t="s">
         <v>551</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>543</v>
-      </c>
-      <c r="F17" t="s">
-        <v>552</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11131,42 +11176,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
+        <v>552</v>
+      </c>
+      <c r="J17" t="s">
         <v>553</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>554</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>555</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>556</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>557</v>
-      </c>
-      <c r="N17" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
+        <v>558</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F18" t="s">
         <v>559</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>543</v>
-      </c>
-      <c r="F18" t="s">
-        <v>560</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11175,42 +11220,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
+        <v>560</v>
+      </c>
+      <c r="J18" t="s">
         <v>561</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>562</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>563</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>564</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>565</v>
-      </c>
-      <c r="N18" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
+        <v>566</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>542</v>
+      </c>
+      <c r="F19" t="s">
         <v>567</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>543</v>
-      </c>
-      <c r="F19" t="s">
-        <v>568</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11219,42 +11264,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
+        <v>568</v>
+      </c>
+      <c r="J19" t="s">
         <v>569</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>570</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>571</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>572</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>573</v>
-      </c>
-      <c r="N19" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
+        <v>574</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>542</v>
+      </c>
+      <c r="F20" t="s">
         <v>575</v>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F20" t="s">
-        <v>576</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11263,42 +11308,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
+        <v>576</v>
+      </c>
+      <c r="J20" t="s">
         <v>577</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>578</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>579</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>580</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>581</v>
-      </c>
-      <c r="N20" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
+        <v>582</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>542</v>
+      </c>
+      <c r="F21" t="s">
         <v>583</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>543</v>
-      </c>
-      <c r="F21" t="s">
-        <v>584</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11307,42 +11352,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
+        <v>584</v>
+      </c>
+      <c r="J21" t="s">
         <v>585</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>586</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>587</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>588</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>589</v>
-      </c>
-      <c r="N21" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
+        <v>590</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>542</v>
+      </c>
+      <c r="F22" t="s">
         <v>591</v>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>543</v>
-      </c>
-      <c r="F22" t="s">
-        <v>592</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11351,42 +11396,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
+        <v>592</v>
+      </c>
+      <c r="J22" t="s">
         <v>593</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>594</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>595</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>596</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>597</v>
-      </c>
-      <c r="N22" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
+        <v>598</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
         <v>599</v>
       </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>600</v>
-      </c>
-      <c r="F23" t="s">
-        <v>601</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11395,86 +11440,86 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
+        <v>601</v>
+      </c>
+      <c r="J23" t="s">
         <v>602</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>603</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>604</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>605</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>606</v>
-      </c>
-      <c r="N23" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
+        <v>607</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>599</v>
+      </c>
+      <c r="F24" t="s">
         <v>608</v>
       </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>600</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
         <v>609</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>610</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>611</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>612</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>613</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>614</v>
-      </c>
-      <c r="N24" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>599</v>
+      </c>
+      <c r="F25" t="s">
         <v>616</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>600</v>
-      </c>
-      <c r="F25" t="s">
-        <v>617</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11483,22 +11528,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
+        <v>618</v>
+      </c>
+      <c r="L25" t="s">
         <v>619</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>620</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>621</v>
-      </c>
-      <c r="N25" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11506,13 +11551,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
+        <v>622</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>623</v>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>624</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11524,22 +11569,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
+        <v>624</v>
+      </c>
+      <c r="J26" t="s">
         <v>625</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>626</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>627</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>628</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>629</v>
-      </c>
-      <c r="N26" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11547,16 +11592,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
+        <v>630</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>623</v>
+      </c>
+      <c r="F27" t="s">
         <v>631</v>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>624</v>
-      </c>
-      <c r="F27" t="s">
-        <v>632</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11565,39 +11610,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
+        <v>632</v>
+      </c>
+      <c r="J27" t="s">
         <v>633</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>634</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>635</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>636</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>637</v>
-      </c>
-      <c r="N27" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11609,39 +11654,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
+        <v>639</v>
+      </c>
+      <c r="J28" t="s">
         <v>640</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>641</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>642</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>643</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>644</v>
-      </c>
-      <c r="N28" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11653,39 +11698,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
+        <v>646</v>
+      </c>
+      <c r="J29" t="s">
         <v>647</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>648</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>649</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>650</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>651</v>
-      </c>
-      <c r="N29" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11697,42 +11742,42 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
+        <v>653</v>
+      </c>
+      <c r="J30" t="s">
         <v>654</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>655</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>656</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>657</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>658</v>
-      </c>
-      <c r="N30" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -11741,22 +11786,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
+        <v>660</v>
+      </c>
+      <c r="J31" t="s">
         <v>661</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>662</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>663</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>664</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>665</v>
-      </c>
-      <c r="N31" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11764,16 +11809,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
+        <v>666</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>464</v>
+      </c>
+      <c r="F32" t="s">
         <v>667</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>465</v>
-      </c>
-      <c r="F32" t="s">
-        <v>668</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11782,22 +11827,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
+        <v>668</v>
+      </c>
+      <c r="J32" t="s">
         <v>669</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>670</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>671</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>672</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>673</v>
-      </c>
-      <c r="N32" t="s">
-        <v>674</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -699,7 +699,7 @@
     <t>Eyes_Cute.png</t>
   </si>
   <si>
-    <t>v0\Shiba\Red</t>
+    <t>v3\Shiba\Red</t>
   </si>
   <si>
     <t>Head_Thin.png</t>
@@ -744,7 +744,7 @@
     <t>Shiba_Black.png</t>
   </si>
   <si>
-    <t>v0\Shiba\Black</t>
+    <t>v3\Shiba\Black</t>
   </si>
   <si>
     <t>Head_Chubby.png</t>
@@ -756,7 +756,7 @@
     <t>Shiba_Cream.png</t>
   </si>
   <si>
-    <t>v0\Shiba\Cream</t>
+    <t>v3\Shiba\Cream</t>
   </si>
   <si>
     <t>胖胡麻柴</t>
@@ -765,7 +765,7 @@
     <t>Shiba_Sesame.png</t>
   </si>
   <si>
-    <t>v0\Shiba\Sesame</t>
+    <t>v3\Shiba\Sesame</t>
   </si>
   <si>
     <t>胖赤柴</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="996">
   <si>
     <t>Dog</t>
   </si>
@@ -591,418 +591,454 @@
     <t>Tongue_Regular</t>
   </si>
   <si>
-    <t>Nose</t>
-  </si>
-  <si>
-    <t>Mouse</t>
+    <t>DefaultNose</t>
+  </si>
+  <si>
+    <t>DefaultMouse</t>
+  </si>
+  <si>
+    <t>Mouse_Silent</t>
+  </si>
+  <si>
+    <t>Ears_Normal</t>
+  </si>
+  <si>
+    <t>Ears_Drooped</t>
+  </si>
+  <si>
+    <t>Eyes_NormalMood</t>
+  </si>
+  <si>
+    <t>Eyes_Bored</t>
+  </si>
+  <si>
+    <t>Eyes_Happy</t>
+  </si>
+  <si>
+    <t>Eyes_Admiring</t>
+  </si>
+  <si>
+    <t>Eyes_Stunned</t>
+  </si>
+  <si>
+    <t>Eyes_Signaling</t>
+  </si>
+  <si>
+    <t>只影响图标和桌宠模式，不影响打牌模式</t>
+  </si>
+  <si>
+    <t>震惊呆住，例如看见置闰搞砸了事情</t>
+  </si>
+  <si>
+    <t>策划粗记名</t>
+  </si>
+  <si>
+    <t>图标名称</t>
+  </si>
+  <si>
+    <t>默认耳朵</t>
+  </si>
+  <si>
+    <t>默认眼神</t>
+  </si>
+  <si>
+    <t>默认舌头</t>
+  </si>
+  <si>
+    <t>默认眼镜</t>
+  </si>
+  <si>
+    <t>资源所在文件夹</t>
+  </si>
+  <si>
+    <t>狗头</t>
+  </si>
+  <si>
+    <t>狗左爪</t>
+  </si>
+  <si>
+    <t>狗右爪</t>
+  </si>
+  <si>
+    <t>舌头</t>
+  </si>
+  <si>
+    <t>鼻子</t>
+  </si>
+  <si>
+    <t>嘴巴</t>
+  </si>
+  <si>
+    <t>沉默嘴</t>
+  </si>
+  <si>
+    <t>高兴耳朵</t>
+  </si>
+  <si>
+    <t>飞机耳</t>
+  </si>
+  <si>
+    <t>默认眼睛</t>
+  </si>
+  <si>
+    <t>无聊眼睛</t>
+  </si>
+  <si>
+    <t>高兴眼睛</t>
+  </si>
+  <si>
+    <t>崇拜眼睛</t>
+  </si>
+  <si>
+    <t>呆住眼睛</t>
+  </si>
+  <si>
+    <t>使眼色</t>
+  </si>
+  <si>
+    <t>赤柴原色</t>
+  </si>
+  <si>
+    <t>Shiba_Red.png</t>
+  </si>
+  <si>
+    <t>Ears_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
+    <t>v3\Shiba\Red</t>
+  </si>
+  <si>
+    <t>Head_Thin.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Left.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.png</t>
+  </si>
+  <si>
+    <t>Tongue_Regular.png</t>
+  </si>
+  <si>
+    <t>Nose_Brown.png</t>
+  </si>
+  <si>
+    <t>Mouse_Natural.png</t>
+  </si>
+  <si>
+    <t>Mouse_Sky.png</t>
+  </si>
+  <si>
+    <t>Ears_Plane.png</t>
+  </si>
+  <si>
+    <t>Eyes_Bored.png</t>
+  </si>
+  <si>
+    <t>Eyes_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Lucky.png</t>
+  </si>
+  <si>
+    <t>Eyes_Neutral.png</t>
+  </si>
+  <si>
+    <t>Eyes_Wink.png</t>
+  </si>
+  <si>
+    <t>胖黑柴</t>
+  </si>
+  <si>
+    <t>Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>v3\Shiba\Black</t>
+  </si>
+  <si>
+    <t>Head_Chubby.png</t>
+  </si>
+  <si>
+    <t>胖白柴</t>
+  </si>
+  <si>
+    <t>Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>v3\Shiba\Cream</t>
+  </si>
+  <si>
+    <t>胖胡麻柴</t>
+  </si>
+  <si>
+    <t>Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>v3\Shiba\Sesame</t>
+  </si>
+  <si>
+    <t>胖赤柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinRed.png</t>
+  </si>
+  <si>
+    <t>Sunglasses_Blade.png</t>
+  </si>
+  <si>
+    <t>胡渣赤柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenRed.png</t>
+  </si>
+  <si>
+    <t>Monocle_black.png</t>
+  </si>
+  <si>
+    <t>Head_Unshaven.png</t>
+  </si>
+  <si>
+    <t>瘦黑柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>EyePatch.png</t>
+  </si>
+  <si>
+    <t>胡渣黑柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>Monocle_golden.png</t>
+  </si>
+  <si>
+    <t>瘦白柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>胡渣白柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
+    <t>3DGlasses.png</t>
+  </si>
+  <si>
+    <t>瘦芝麻柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>胡渣胡麻柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
+    <t>新狗狗 1013</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ItemRarity</t>
+  </si>
+  <si>
+    <t>FrameAssetPath</t>
+  </si>
+  <si>
+    <t>PlateAssetPath</t>
+  </si>
+  <si>
+    <t>ERarity</t>
+  </si>
+  <si>
+    <t>显示名称</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>边框</t>
+  </si>
+  <si>
+    <t>底板</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Common.png</t>
+  </si>
+  <si>
+    <t>Unommon</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Uncommon.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Uncommon.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Legendary.png</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>神话</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Mythic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Mythic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special2.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special2.png</t>
+  </si>
+  <si>
+    <t>DogReactionTrigger</t>
+  </si>
+  <si>
+    <t>AssetRef</t>
+  </si>
+  <si>
+    <t>EarAsset</t>
+  </si>
+  <si>
+    <t>EyeAsset</t>
+  </si>
+  <si>
+    <t>MouseAsset</t>
+  </si>
+  <si>
+    <t>OverrideHeadwear</t>
+  </si>
+  <si>
+    <t>WearGlasses</t>
+  </si>
+  <si>
+    <t>LeftPawAnimation</t>
+  </si>
+  <si>
+    <t>RightPawAnimation</t>
+  </si>
+  <si>
+    <t>TongueAnimation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>EDogReactionTrigger</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
+  </si>
+  <si>
+    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
+  </si>
+  <si>
+    <t>该功能处于改版器，暂时禁用效果。bool字段保留后续用其他方式表示狗狗沉默。</t>
+  </si>
+  <si>
+    <t>左指画面左侧，而非狗自己的左</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>引用枚举</t>
+  </si>
+  <si>
+    <t>耳朵资源</t>
+  </si>
+  <si>
+    <t>眼睛资源</t>
+  </si>
+  <si>
+    <t>嘴部资源</t>
+  </si>
+  <si>
+    <t>头饰变化</t>
+  </si>
+  <si>
+    <t>戴上眼镜</t>
+  </si>
+  <si>
+    <t>左爪子</t>
+  </si>
+  <si>
+    <t>右爪子</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>手背</t>
+  </si>
+  <si>
+    <t>正常</t>
   </si>
   <si>
     <t>Ears_Happy</t>
   </si>
   <si>
+    <t>Eyes_Cute</t>
+  </si>
+  <si>
     <t>Ears_Plane</t>
   </si>
   <si>
-    <t>Eyes_Bored</t>
-  </si>
-  <si>
-    <t>Eyes_Cute</t>
-  </si>
-  <si>
-    <t>Eyes_Happy</t>
+    <t>Eyes_Wink</t>
   </si>
   <si>
     <t>Eyes_Lucky</t>
   </si>
   <si>
     <t>Eyes_Neutral</t>
-  </si>
-  <si>
-    <t>Eyes_Wink</t>
-  </si>
-  <si>
-    <t>只影响图标和桌宠模式，不影响打牌模式</t>
-  </si>
-  <si>
-    <t>策划粗记名</t>
-  </si>
-  <si>
-    <t>图标名称</t>
-  </si>
-  <si>
-    <t>默认耳朵</t>
-  </si>
-  <si>
-    <t>默认眼神</t>
-  </si>
-  <si>
-    <t>默认舌头</t>
-  </si>
-  <si>
-    <t>默认眼镜</t>
-  </si>
-  <si>
-    <t>资源所在文件夹</t>
-  </si>
-  <si>
-    <t>狗头</t>
-  </si>
-  <si>
-    <t>狗左爪</t>
-  </si>
-  <si>
-    <t>狗右爪</t>
-  </si>
-  <si>
-    <t>舌头</t>
-  </si>
-  <si>
-    <t>鼻子</t>
-  </si>
-  <si>
-    <t>嘴巴</t>
-  </si>
-  <si>
-    <t>高兴耳朵</t>
-  </si>
-  <si>
-    <t>飞机耳</t>
-  </si>
-  <si>
-    <t>无聊眼睛</t>
-  </si>
-  <si>
-    <t>可爱眼睛</t>
-  </si>
-  <si>
-    <t>高兴眼睛</t>
-  </si>
-  <si>
-    <t>幸运眼睛</t>
-  </si>
-  <si>
-    <t>无神眼睛</t>
-  </si>
-  <si>
-    <t>抛媚眼</t>
-  </si>
-  <si>
-    <t>赤柴原色</t>
-  </si>
-  <si>
-    <t>Shiba_Red.png</t>
-  </si>
-  <si>
-    <t>Ears_Happy.png</t>
-  </si>
-  <si>
-    <t>Eyes_Cute.png</t>
-  </si>
-  <si>
-    <t>v3\Shiba\Red</t>
-  </si>
-  <si>
-    <t>Head_Thin.png</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Left.png</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.png</t>
-  </si>
-  <si>
-    <t>Tongue_Regular.png</t>
-  </si>
-  <si>
-    <t>Nose_Brown.png</t>
-  </si>
-  <si>
-    <t>Mouse_Natural.png</t>
-  </si>
-  <si>
-    <t>Ears_Plane.png</t>
-  </si>
-  <si>
-    <t>Eyes_Bored.png</t>
-  </si>
-  <si>
-    <t>Eyes_Happy.png</t>
-  </si>
-  <si>
-    <t>Eyes_Lucky.png</t>
-  </si>
-  <si>
-    <t>Eyes_Neutral.png</t>
-  </si>
-  <si>
-    <t>Eyes_Wink.png</t>
-  </si>
-  <si>
-    <t>胖黑柴</t>
-  </si>
-  <si>
-    <t>Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>v3\Shiba\Black</t>
-  </si>
-  <si>
-    <t>Head_Chubby.png</t>
-  </si>
-  <si>
-    <t>胖白柴</t>
-  </si>
-  <si>
-    <t>Shiba_Cream.png</t>
-  </si>
-  <si>
-    <t>v3\Shiba\Cream</t>
-  </si>
-  <si>
-    <t>胖胡麻柴</t>
-  </si>
-  <si>
-    <t>Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>v3\Shiba\Sesame</t>
-  </si>
-  <si>
-    <t>胖赤柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinRed.png</t>
-  </si>
-  <si>
-    <t>Sunglasses_Blade.png</t>
-  </si>
-  <si>
-    <t>胡渣赤柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>Monocle_black.png</t>
-  </si>
-  <si>
-    <t>Head_Unshaven.png</t>
-  </si>
-  <si>
-    <t>瘦黑柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinBlack.png</t>
-  </si>
-  <si>
-    <t>EyePatch.png</t>
-  </si>
-  <si>
-    <t>胡渣黑柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenBlack.png</t>
-  </si>
-  <si>
-    <t>Monocle_golden.png</t>
-  </si>
-  <si>
-    <t>瘦白柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinCream.png</t>
-  </si>
-  <si>
-    <t>胡渣白柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenCream.png</t>
-  </si>
-  <si>
-    <t>3DGlasses.png</t>
-  </si>
-  <si>
-    <t>瘦芝麻柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinSesame.png</t>
-  </si>
-  <si>
-    <t>胡渣胡麻柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenSesame.png</t>
-  </si>
-  <si>
-    <t>新狗狗 1013</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>ItemRarity</t>
-  </si>
-  <si>
-    <t>FrameAssetPath</t>
-  </si>
-  <si>
-    <t>PlateAssetPath</t>
-  </si>
-  <si>
-    <t>ERarity</t>
-  </si>
-  <si>
-    <t>显示名称</t>
-  </si>
-  <si>
-    <t>品质</t>
-  </si>
-  <si>
-    <t>边框</t>
-  </si>
-  <si>
-    <t>底板</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Common.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Common.png</t>
-  </si>
-  <si>
-    <t>Unommon</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Uncommon.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Uncommon.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Rare.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Rare.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Epic.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Epic.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Legendary.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Legendary.png</t>
-  </si>
-  <si>
-    <t>Mythic</t>
-  </si>
-  <si>
-    <t>神话</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Mythic.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Mythic.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Special1.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Special1.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Special2.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Special2.png</t>
-  </si>
-  <si>
-    <t>DogReactionTrigger</t>
-  </si>
-  <si>
-    <t>AssetRef</t>
-  </si>
-  <si>
-    <t>EarAsset</t>
-  </si>
-  <si>
-    <t>EyeAsset</t>
-  </si>
-  <si>
-    <t>OverrideHeadwear</t>
-  </si>
-  <si>
-    <t>WearGlasses</t>
-  </si>
-  <si>
-    <t>LeftPawAnimation</t>
-  </si>
-  <si>
-    <t>RightPawAnimation</t>
-  </si>
-  <si>
-    <t>TongueAnimation</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>EDogReactionTrigger</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
-  </si>
-  <si>
-    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
-  </si>
-  <si>
-    <t>该功能处于改版器，暂时禁用效果。bool字段保留后续用其他方式表示狗狗沉默。</t>
-  </si>
-  <si>
-    <t>左指画面左侧，而非狗自己的左</t>
-  </si>
-  <si>
-    <t>枚举</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>引用枚举</t>
-  </si>
-  <si>
-    <t>耳朵资源</t>
-  </si>
-  <si>
-    <t>眼睛资源</t>
-  </si>
-  <si>
-    <t>头饰变化</t>
-  </si>
-  <si>
-    <t>戴上眼镜</t>
-  </si>
-  <si>
-    <t>左爪子</t>
-  </si>
-  <si>
-    <t>右爪子</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>手背</t>
-  </si>
-  <si>
-    <t>正常</t>
   </si>
   <si>
     <t>手心，摆手</t>
@@ -3618,7 +3654,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3636,6 +3672,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4586,31 +4625,31 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="C1" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="D1" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="E1" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F1" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="G1" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="H1" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="I1" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="J1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4627,19 +4666,19 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F2" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="G2" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
         <v>109</v>
@@ -4650,31 +4689,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4682,1471 +4721,1471 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="C4" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="F4" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="G4" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="H4" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="I4" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="J4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="D5" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="G5" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H5" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="D6" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G6" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H6" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="D7" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="G7" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H7" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
+        <v>725</v>
+      </c>
+      <c r="D8" t="s">
+        <v>726</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>712</v>
+      </c>
+      <c r="G8" t="s">
         <v>713</v>
       </c>
-      <c r="D8" t="s">
-        <v>714</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>700</v>
-      </c>
-      <c r="G8" t="s">
-        <v>701</v>
-      </c>
       <c r="H8" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="D9" t="s">
+        <v>730</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>718</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>706</v>
-      </c>
       <c r="G9" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H9" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="D10" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G10" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H10" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="D11" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G11" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H11" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="D12" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G12" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H12" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="D13" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G13" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H13" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="D14" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G14" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H14" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="D15" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G15" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H15" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D16" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G16" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H16" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="D17" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G17" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H17" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="D18" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G18" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H18" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="D19" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G19" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H19" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="D20" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G20" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H20" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D21" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G21" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H21" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="D22" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G22" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H22" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="D23" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G23" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H23" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="D24" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G24" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H24" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="D25" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G25" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H25" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="D26" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G26" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H26" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="D27" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G27" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H27" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="D28" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G28" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H28" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="D29" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G29" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H29" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="D30" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G30" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H30" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="D31" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G31" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H31" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="D32" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G32" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H32" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="D33" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G33" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H33" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="D34" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G34" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H34" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="D35" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G35" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H35" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="D36" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G36" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H36" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="D37" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G37" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H37" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="D38" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G38" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H38" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="D39" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G39" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H39" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="D40" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G40" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H40" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="D41" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G41" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H41" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D42" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G42" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H42" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D43" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G43" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H43" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="D44" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G44" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H44" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="D45" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G45" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H45" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="D46" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G46" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H46" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="D47" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G47" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H47" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="D48" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G48" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H48" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="D49" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G49" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H49" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6154,28 +6193,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="D50" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G50" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H50" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6183,28 +6222,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="D51" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G51" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="H51" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6212,28 +6251,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="D52" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G52" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H52" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6241,28 +6280,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="D53" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G53" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H53" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6270,28 +6309,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="D54" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G54" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H54" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6299,28 +6338,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="D55" t="s">
+        <v>910</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
         <v>898</v>
       </c>
-      <c r="E55" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>886</v>
-      </c>
       <c r="G55" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H55" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6328,28 +6367,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="D56" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G56" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H56" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6357,28 +6396,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
       <c r="D57" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="G57" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H57" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6386,28 +6425,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="D58" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G58" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H58" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6415,28 +6454,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="D59" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G59" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H59" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6444,28 +6483,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="D60" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G60" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H60" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6473,28 +6512,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="D61" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G61" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H61" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6502,92 +6541,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="D62" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G62" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H62" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="D63" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G63" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H63" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="D64" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G64" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="H64" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6595,28 +6634,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="D65" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="G65" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="H65" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -6651,25 +6690,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="C1" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
       <c r="D1" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="E1" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="F1" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="G1" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="H1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6683,7 +6722,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6703,28 +6742,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6732,39 +6771,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="C4" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="D4" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="E4" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="F4" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="G4" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="H4" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B5" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="C5" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6782,18 +6821,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B6" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C6" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6811,18 +6850,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B7" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="C7" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6840,18 +6879,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B8" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="C8" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6869,18 +6908,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B9" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="C9" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6898,18 +6937,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B10" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="C10" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6927,18 +6966,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B11" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="C11" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6956,18 +6995,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B12" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="C12" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6985,7 +7024,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
     </row>
   </sheetData>
@@ -7345,7 +7384,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>152</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -7360,7 +7399,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6"/>
+      <c r="A2" s="7"/>
       <c r="B2" s="5" t="s">
         <v>153</v>
       </c>
@@ -7458,22 +7497,22 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8">
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="8"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8">
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7484,7 +7523,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -7496,18 +7535,19 @@
     <col min="11" max="11" width="18.5" customWidth="1"/>
     <col min="12" max="13" width="20.8333333333333" customWidth="1"/>
     <col min="14" max="14" width="15.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="15.9513888888889" customWidth="1"/>
-    <col min="16" max="16" width="14.5" customWidth="1"/>
-    <col min="17" max="17" width="13.4166666666667" customWidth="1"/>
-    <col min="18" max="18" width="14.3333333333333" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="14.8333333333333" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="13.4166666666667" customWidth="1"/>
+    <col min="15" max="15" width="17.5833333333333" customWidth="1"/>
+    <col min="16" max="16" width="15.9513888888889" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
+    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
+    <col min="19" max="19" width="17.0833333333333" customWidth="1"/>
+    <col min="20" max="20" width="14.3333333333333" customWidth="1"/>
+    <col min="21" max="21" width="14.8333333333333" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="15.4166666666667" customWidth="1"/>
+    <col min="24" max="24" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -7577,8 +7617,11 @@
       <c r="W1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="X1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -7648,8 +7691,11 @@
       <c r="W2" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:24">
+      <c r="X2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:25">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
@@ -7657,17 +7703,20 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="W3" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="3" t="s">
         <v>110</v>
       </c>
@@ -7675,959 +7724,1001 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="R4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="S4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="T4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="U4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="W4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+        <v>217</v>
+      </c>
+      <c r="X4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="R5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="T5" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X5" s="2"/>
-    </row>
-    <row r="6" spans="1:24">
+        <v>235</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y5" s="2"/>
+    </row>
+    <row r="6" spans="1:25">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X6" s="2"/>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="Y6" s="2"/>
+    </row>
+    <row r="7" spans="1:25">
       <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="X7" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X7" s="2"/>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="Y7" s="2"/>
+    </row>
+    <row r="8" spans="1:25">
       <c r="B8" s="2">
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="X8" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X8" s="2"/>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="Y8" s="2"/>
+    </row>
+    <row r="9" spans="1:25">
       <c r="B9" s="2">
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X9" s="2"/>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="Y9" s="2"/>
+    </row>
+    <row r="10" spans="1:25">
       <c r="B10" s="2">
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="T10" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X10" s="2"/>
-    </row>
-    <row r="11" spans="1:24">
+        <v>235</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y10" s="2"/>
+    </row>
+    <row r="11" spans="1:25">
       <c r="B11" s="2">
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W11" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X11" s="2"/>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="X11" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y11" s="2"/>
+    </row>
+    <row r="12" spans="1:25">
       <c r="B12" s="2">
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W12" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X12" s="2"/>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="X12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y12" s="2"/>
+    </row>
+    <row r="13" spans="1:25">
       <c r="B13" s="2">
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="R13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S13" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="T13" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X13" s="2"/>
-    </row>
-    <row r="14" spans="1:24">
+        <v>235</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y13" s="2"/>
+    </row>
+    <row r="14" spans="1:25">
       <c r="B14" s="2">
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="T14" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X14" s="2"/>
-    </row>
-    <row r="15" spans="1:24">
+        <v>235</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:25">
       <c r="B15" s="2">
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q15" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="R15" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S15" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="T15" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X15" s="2"/>
-    </row>
-    <row r="16" spans="1:24">
+        <v>235</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y15" s="2"/>
+    </row>
+    <row r="16" spans="1:25">
       <c r="B16" s="2">
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S16" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="T16" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X16" s="2"/>
-    </row>
-    <row r="17" spans="2:24">
+        <v>235</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y16" s="2"/>
+    </row>
+    <row r="17" spans="2:25">
       <c r="B17" s="2">
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="X17" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="X17" s="2"/>
-    </row>
-    <row r="18" spans="2:24">
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="2:25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -8650,8 +8741,9 @@
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="2:24">
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="2:25">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8674,8 +8766,9 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="2:24">
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="2:25">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -8698,8 +8791,9 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="2:24">
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="2:25">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -8722,8 +8816,9 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="2:24">
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="2:25">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -8746,8 +8841,9 @@
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="2:24">
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="2:25">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -8770,8 +8866,9 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="2:24">
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="2:25">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -8794,8 +8891,9 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="2:24">
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="2:25">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -8818,8 +8916,9 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="2:24">
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="2:25">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -8842,8 +8941,9 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="2:24">
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="2:25">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -8866,8 +8966,9 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="2:24">
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="2:25">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -8890,8 +8991,9 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="2:24">
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="2:25">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -8914,8 +9016,9 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="2:24">
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="2:25">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -8938,6 +9041,7 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8965,16 +9069,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8988,7 +9092,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -9013,16 +9117,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9036,10 +9140,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9047,16 +9151,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9070,10 +9174,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F7" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9087,10 +9191,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9104,10 +9208,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F9" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9115,16 +9219,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9138,10 +9242,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9155,10 +9259,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F12" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -9170,7 +9274,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -9178,12 +9282,12 @@
     <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
-    <col min="8" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
-    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+    <col min="8" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -9191,37 +9295,40 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="M1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="N1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>307</v>
+      </c>
+      <c r="O1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -9229,10 +9336,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -9244,10 +9351,10 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>305</v>
+        <v>109</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>310</v>
       </c>
       <c r="L2" t="s">
         <v>109</v>
@@ -9258,27 +9365,30 @@
       <c r="N2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" ht="104.4" spans="1:14">
+      <c r="O2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>313</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>110</v>
       </c>
@@ -9286,43 +9396,46 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="I4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="L4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M4" t="s">
-        <v>205</v>
+        <v>324</v>
       </c>
       <c r="N4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>207</v>
+      </c>
+      <c r="O4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -9338,20 +9451,23 @@
       <c r="H5" t="s">
         <v>8</v>
       </c>
-      <c r="J5" t="b">
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
-        <v>320</v>
-      </c>
       <c r="L5" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -9362,25 +9478,28 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="H6" t="s">
-        <v>189</v>
-      </c>
-      <c r="J6" t="b">
+        <v>329</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
-        <v>320</v>
-      </c>
       <c r="L6" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -9391,25 +9510,28 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="H7" t="s">
-        <v>188</v>
-      </c>
-      <c r="J7" t="b">
+        <v>190</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
-        <v>320</v>
-      </c>
       <c r="L7" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -9420,25 +9542,28 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="H8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J8" t="b">
+        <v>331</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
-        <v>320</v>
-      </c>
       <c r="L8" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M8" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -9449,25 +9574,28 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="H9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J9" t="b">
+        <v>191</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
-        <v>320</v>
-      </c>
       <c r="L9" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -9478,25 +9606,28 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
-      </c>
-      <c r="J10" t="b">
+        <v>332</v>
+      </c>
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>320</v>
-      </c>
       <c r="L10" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M10" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -9507,25 +9638,28 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="H11" t="s">
-        <v>188</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>320</v>
+        <v>190</v>
+      </c>
+      <c r="I11" t="s">
+        <v>186</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>326</v>
+      </c>
+      <c r="N11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -9536,65 +9670,71 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="H12" t="s">
-        <v>192</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>322</v>
+        <v>333</v>
+      </c>
+      <c r="I12" t="s">
+        <v>186</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="M12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>334</v>
+      </c>
+      <c r="N12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="H13" t="s">
-        <v>189</v>
-      </c>
-      <c r="J13" t="b">
+        <v>329</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" t="b">
         <v>0</v>
       </c>
-      <c r="K13" t="s">
-        <v>320</v>
-      </c>
       <c r="L13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M13" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="N13" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>338</v>
+      </c>
+      <c r="O13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="B14">
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9602,19 +9742,19 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-      <c r="N14" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="B15">
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9622,19 +9762,19 @@
       <c r="F15" t="s">
         <v>8</v>
       </c>
-      <c r="N15" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="B16">
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9642,39 +9782,39 @@
       <c r="F16" t="s">
         <v>17</v>
       </c>
-      <c r="N16" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
+      <c r="O16" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
       <c r="B17">
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="F17" t="s">
-        <v>339</v>
-      </c>
-      <c r="N17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
+        <v>351</v>
+      </c>
+      <c r="O17" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
       <c r="B18">
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9682,19 +9822,19 @@
       <c r="F18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="N18" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
+      <c r="O18" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
       <c r="B19">
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9702,19 +9842,19 @@
       <c r="F19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
+      <c r="O19" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
       <c r="B20">
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9722,56 +9862,56 @@
       <c r="F20" t="s">
         <v>17</v>
       </c>
-      <c r="N20" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
+      <c r="O20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
       <c r="B21">
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E21" t="s">
         <v>350</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="F21" t="s">
         <v>351</v>
       </c>
-      <c r="E21" t="s">
-        <v>338</v>
-      </c>
-      <c r="F21" t="s">
-        <v>339</v>
-      </c>
-      <c r="N21" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14">
+      <c r="O21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
       <c r="B22">
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
       <c r="B23">
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9780,15 +9920,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:15">
       <c r="B24">
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9797,15 +9937,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:15">
       <c r="B25">
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9814,15 +9954,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:15">
       <c r="B26">
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9831,15 +9971,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:15">
       <c r="B27">
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9848,15 +9988,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="2:14">
+    <row r="28" spans="2:15">
       <c r="B28">
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -9865,15 +10005,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:15">
       <c r="B29">
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -9881,22 +10021,22 @@
       <c r="F29" t="s">
         <v>44</v>
       </c>
-      <c r="M29" t="s">
-        <v>326</v>
-      </c>
       <c r="N29" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14">
+        <v>338</v>
+      </c>
+      <c r="O29" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
       <c r="B30">
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -9905,15 +10045,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="2:14">
+    <row r="31" spans="2:15">
       <c r="B31">
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -9922,15 +10062,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="2:14">
+    <row r="32" spans="2:15">
       <c r="B32">
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -9938,22 +10078,22 @@
       <c r="F32" t="s">
         <v>53</v>
       </c>
-      <c r="M32" t="s">
-        <v>326</v>
-      </c>
       <c r="N32" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="2:14">
+        <v>338</v>
+      </c>
+      <c r="O32" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:15">
       <c r="B33">
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -9961,8 +10101,8 @@
       <c r="F33" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N33" t="s">
-        <v>377</v>
+      <c r="O33" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -9998,31 +10138,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D1" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="E1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F1" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="G1" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="H1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I1" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="J1" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="K1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -10048,10 +10188,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="I2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -10065,34 +10205,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -10103,31 +10243,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D4" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="E4" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F4" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="G4" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="H4" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="I4" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="J4" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="K4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -10135,7 +10275,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10159,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10167,7 +10307,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10191,7 +10331,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10199,7 +10339,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10223,7 +10363,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10231,7 +10371,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10255,7 +10395,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -10286,16 +10426,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="E1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="F1" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10312,7 +10452,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -10325,10 +10465,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10339,13 +10479,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10353,7 +10493,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10362,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10370,7 +10510,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10379,7 +10519,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10387,7 +10527,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10396,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10404,7 +10544,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10413,7 +10553,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10451,43 +10591,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="D1" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="E1" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="F1" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="G1" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="H1" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="I1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="K1" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="L1" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="M1" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="N1" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10501,19 +10641,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="H2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -10539,43 +10679,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="J3" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="K3" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="L3" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="M3" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="N3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10583,60 +10723,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C4" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D4" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="E4" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="F4" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="G4" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="H4" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J4" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="K4" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="L4" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="M4" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="N4" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10648,39 +10788,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="J5" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="K5" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="L5" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="M5" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="N5" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10692,39 +10832,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="J6" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="K6" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="L6" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="M6" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="N6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10736,39 +10876,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="J7" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="K7" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="L7" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="M7" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="N7" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10780,39 +10920,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="J8" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="K8" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="L8" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="M8" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="N8" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10824,39 +10964,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="J9" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="K9" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="L9" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="M9" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="N9" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -10868,39 +11008,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="J10" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="K10" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L10" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="M10" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="N10" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -10912,39 +11052,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J11" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="K11" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="L11" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="M11" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="N11" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -10956,39 +11096,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="J12" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K12" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="L12" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="M12" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="N12" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -11000,39 +11140,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="J13" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="K13" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="L13" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="M13" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="N13" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -11044,39 +11184,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="J14" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="K14" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="L14" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="M14" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="N14" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -11088,42 +11228,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="J15" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="K15" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="L15" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="M15" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="N15" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F16" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -11132,42 +11272,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="J16" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="K16" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="L16" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="M16" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="N16" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F17" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11176,42 +11316,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="J17" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="K17" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="L17" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="M17" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="N17" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F18" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11220,42 +11360,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="J18" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="K18" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="L18" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="M18" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="N18" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F19" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11264,42 +11404,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="J19" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="K19" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="L19" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="M19" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="N19" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F20" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11308,42 +11448,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="J20" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="K20" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="L20" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="M20" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="N20" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F21" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11352,42 +11492,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="J21" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="K21" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="L21" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="M21" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="N21" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F22" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11396,42 +11536,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="J22" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="K22" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="L22" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="M22" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="N22" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="F23" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11440,42 +11580,42 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="J23" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="K23" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="L23" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="M23" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="N23" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="F24" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -11484,42 +11624,42 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="J24" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="K24" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="L24" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="M24" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="N24" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="F25" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11528,22 +11668,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="L25" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="M25" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="N25" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11551,13 +11691,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11569,22 +11709,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="J26" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="K26" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="L26" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="M26" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="N26" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11592,16 +11732,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F27" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11610,39 +11750,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="J27" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="K27" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="L27" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="M27" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="N27" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11654,39 +11794,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="J28" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="K28" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="L28" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="M28" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="N28" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11698,39 +11838,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="J29" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="K29" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="L29" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="M29" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="N29" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11742,42 +11882,42 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="J30" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="K30" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="L30" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="M30" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="N30" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -11786,22 +11926,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="J31" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="K31" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="L31" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="M31" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="N31" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11809,16 +11949,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F32" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11827,22 +11967,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="J32" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="K32" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="L32" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="M32" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="N32" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="990">
   <si>
     <t>Dog</t>
   </si>
@@ -729,7 +729,7 @@
     <t>Mouse_Natural.png</t>
   </si>
   <si>
-    <t>Mouse_Sky.png</t>
+    <t>Mouse_Shy.png</t>
   </si>
   <si>
     <t>Ears_Plane.png</t>
@@ -1021,24 +1021,6 @@
   </si>
   <si>
     <t>正常</t>
-  </si>
-  <si>
-    <t>Ears_Happy</t>
-  </si>
-  <si>
-    <t>Eyes_Cute</t>
-  </si>
-  <si>
-    <t>Ears_Plane</t>
-  </si>
-  <si>
-    <t>Eyes_Wink</t>
-  </si>
-  <si>
-    <t>Eyes_Lucky</t>
-  </si>
-  <si>
-    <t>Eyes_Neutral</t>
   </si>
   <si>
     <t>手心，摆手</t>
@@ -4625,28 +4607,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D1" t="s">
+        <v>682</v>
+      </c>
+      <c r="E1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F1" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1" t="s">
+        <v>684</v>
+      </c>
+      <c r="H1" t="s">
+        <v>685</v>
+      </c>
+      <c r="I1" t="s">
         <v>686</v>
-      </c>
-      <c r="C1" t="s">
-        <v>687</v>
-      </c>
-      <c r="D1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E1" t="s">
-        <v>438</v>
-      </c>
-      <c r="F1" t="s">
-        <v>689</v>
-      </c>
-      <c r="G1" t="s">
-        <v>690</v>
-      </c>
-      <c r="H1" t="s">
-        <v>691</v>
-      </c>
-      <c r="I1" t="s">
-        <v>692</v>
       </c>
       <c r="J1" t="s">
         <v>308</v>
@@ -4669,10 +4651,10 @@
         <v>310</v>
       </c>
       <c r="F2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="G2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -4689,31 +4671,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4721,28 +4703,28 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C4" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="D4" t="s">
         <v>275</v>
       </c>
       <c r="E4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="F4" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="G4" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="H4" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="I4" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="J4" t="s">
         <v>325</v>
@@ -4750,1442 +4732,1442 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D5" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="G5" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H5" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D6" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G6" t="s">
+        <v>707</v>
+      </c>
+      <c r="H6" t="s">
         <v>713</v>
-      </c>
-      <c r="H6" t="s">
-        <v>719</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="G7" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D8" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="G8" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D9" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G9" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H9" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D10" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G10" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H10" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D11" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G11" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H11" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="D12" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G12" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H12" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D13" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G13" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H13" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D14" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G14" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H14" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="D15" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G15" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H15" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D16" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G16" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H16" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D17" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G17" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H17" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="D18" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G18" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H18" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D19" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G19" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H19" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D20" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G20" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H20" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D21" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G21" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H21" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D22" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G22" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H22" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D23" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G23" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H23" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D24" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G24" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H24" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D25" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G25" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H25" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="D26" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G26" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H26" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="D27" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G27" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H27" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="D28" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G28" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H28" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="D29" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G29" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H29" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="D30" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G30" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H30" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D31" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G31" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H31" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="D32" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G32" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H32" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="D33" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G33" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H33" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="D34" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G34" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H34" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D35" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G35" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H35" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="D36" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G36" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H36" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="D37" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G37" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H37" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="D38" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G38" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H38" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="D39" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G39" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H39" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="D40" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G40" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H40" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="D41" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G41" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H41" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="D42" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G42" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H42" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="D43" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G43" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H43" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="D44" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G44" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H44" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="D45" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G45" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H45" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="D46" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G46" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H46" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="D47" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G47" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H47" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="D48" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G48" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H48" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="D49" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G49" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H49" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6193,28 +6175,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="D50" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G50" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H50" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6222,28 +6204,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="D51" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G51" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="H51" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6251,28 +6233,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="D52" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G52" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H52" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6280,28 +6262,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="D53" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
+        <v>892</v>
+      </c>
+      <c r="G53" t="s">
+        <v>892</v>
+      </c>
+      <c r="H53" t="s">
+        <v>897</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
         <v>898</v>
-      </c>
-      <c r="G53" t="s">
-        <v>898</v>
-      </c>
-      <c r="H53" t="s">
-        <v>903</v>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6309,28 +6291,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="D54" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G54" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H54" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6338,28 +6320,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="D55" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G55" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H55" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6367,28 +6349,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="D56" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G56" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H56" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6396,28 +6378,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="D57" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="G57" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H57" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6425,28 +6407,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="D58" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G58" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H58" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6454,28 +6436,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="D59" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G59" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H59" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6483,28 +6465,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D60" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G60" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H60" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6512,28 +6494,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="D61" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G61" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H61" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6541,92 +6523,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="D62" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="G62" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="H62" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="D63" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G63" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H63" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="D64" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G64" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H64" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6634,28 +6616,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="D65" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G65" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="H65" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -6690,25 +6672,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="C1" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="D1" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="E1" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="F1" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G1" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6742,28 +6724,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6771,25 +6753,25 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C4" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="D4" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="E4" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="F4" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="G4" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="H4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="I4" t="s">
         <v>325</v>
@@ -6797,13 +6779,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B5" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C5" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6821,18 +6803,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B6" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C6" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6850,18 +6832,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B7" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C7" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6879,18 +6861,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B8" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C8" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6908,18 +6890,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B9" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="C9" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6937,18 +6919,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B10" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="C10" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6966,18 +6948,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B11" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C11" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6995,18 +6977,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B12" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="C12" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -7024,7 +7006,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -9281,8 +9263,9 @@
     <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
-    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
-    <col min="8" max="11" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="11" width="11.5" customWidth="1"/>
     <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
     <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
   </cols>
@@ -9446,13 +9429,13 @@
         <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>175</v>
       </c>
       <c r="H5" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -9478,13 +9461,13 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>329</v>
+        <v>189</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -9510,13 +9493,13 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>330</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
         <v>190</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -9542,13 +9525,13 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="H8" t="s">
-        <v>331</v>
+        <v>194</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -9574,13 +9557,13 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="H9" t="s">
         <v>191</v>
       </c>
       <c r="I9" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -9606,13 +9589,13 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="H10" t="s">
-        <v>332</v>
+        <v>192</v>
       </c>
       <c r="I10" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -9638,10 +9621,10 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>330</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I11" t="s">
         <v>186</v>
@@ -9670,22 +9653,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>330</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
-        <v>333</v>
+        <v>193</v>
       </c>
       <c r="I12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="M12" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="N12" t="s">
         <v>327</v>
@@ -9696,19 +9679,19 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="H13" t="s">
-        <v>329</v>
+        <v>194</v>
       </c>
       <c r="I13" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -9717,13 +9700,13 @@
         <v>326</v>
       </c>
       <c r="M13" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N13" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="O13" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -9731,10 +9714,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9743,7 +9726,7 @@
         <v>8</v>
       </c>
       <c r="O14" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -9751,10 +9734,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9763,7 +9746,7 @@
         <v>8</v>
       </c>
       <c r="O15" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -9771,10 +9754,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9783,7 +9766,7 @@
         <v>17</v>
       </c>
       <c r="O16" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -9791,19 +9774,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F17" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="O17" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -9811,10 +9794,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9823,7 +9806,7 @@
         <v>60</v>
       </c>
       <c r="O18" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -9831,10 +9814,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9843,7 +9826,7 @@
         <v>67</v>
       </c>
       <c r="O19" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -9851,10 +9834,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9863,7 +9846,7 @@
         <v>17</v>
       </c>
       <c r="O20" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -9871,19 +9854,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E21" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F21" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="O21" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="2:15">
@@ -9891,16 +9874,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -9908,10 +9891,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9925,10 +9908,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9942,10 +9925,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9959,10 +9942,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9976,10 +9959,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9993,10 +9976,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -10010,10 +9993,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -10022,10 +10005,10 @@
         <v>44</v>
       </c>
       <c r="N29" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="O29" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -10033,10 +10016,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -10050,10 +10033,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -10067,10 +10050,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -10079,10 +10062,10 @@
         <v>53</v>
       </c>
       <c r="N32" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="O32" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:15">
@@ -10090,10 +10073,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -10102,7 +10085,7 @@
         <v>67</v>
       </c>
       <c r="O33" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -10138,28 +10121,28 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="F1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="G1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H1" t="s">
         <v>298</v>
       </c>
       <c r="I1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="J1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="K1" t="s">
         <v>308</v>
@@ -10205,31 +10188,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>325</v>
@@ -10243,28 +10226,28 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" t="s">
+        <v>403</v>
+      </c>
+      <c r="G4" t="s">
+        <v>404</v>
+      </c>
+      <c r="H4" t="s">
+        <v>405</v>
+      </c>
+      <c r="I4" t="s">
         <v>406</v>
       </c>
-      <c r="D4" t="s">
+      <c r="J4" t="s">
         <v>407</v>
-      </c>
-      <c r="E4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F4" t="s">
-        <v>409</v>
-      </c>
-      <c r="G4" t="s">
-        <v>410</v>
-      </c>
-      <c r="H4" t="s">
-        <v>411</v>
-      </c>
-      <c r="I4" t="s">
-        <v>412</v>
-      </c>
-      <c r="J4" t="s">
-        <v>413</v>
       </c>
       <c r="K4" t="s">
         <v>325</v>
@@ -10275,7 +10258,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10299,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10307,7 +10290,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10331,7 +10314,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10339,7 +10322,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10363,7 +10346,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10371,7 +10354,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10395,7 +10378,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -10429,13 +10412,13 @@
         <v>270</v>
       </c>
       <c r="D1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10465,10 +10448,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10479,13 +10462,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10493,7 +10476,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10502,7 +10485,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10510,7 +10493,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10519,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10527,7 +10510,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10536,7 +10519,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10544,7 +10527,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10553,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10591,43 +10574,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H1" t="s">
         <v>436</v>
-      </c>
-      <c r="C1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F1" t="s">
-        <v>440</v>
-      </c>
-      <c r="G1" t="s">
-        <v>441</v>
-      </c>
-      <c r="H1" t="s">
-        <v>442</v>
       </c>
       <c r="I1" t="s">
         <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="K1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="L1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="M1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="N1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10644,13 +10627,13 @@
         <v>310</v>
       </c>
       <c r="E2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="H2" t="s">
         <v>310</v>
@@ -10679,43 +10662,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" t="s">
         <v>452</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" t="s">
         <v>453</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="L3" t="s">
         <v>454</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="M3" t="s">
         <v>455</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="N3" t="s">
         <v>456</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J3" t="s">
-        <v>458</v>
-      </c>
-      <c r="K3" t="s">
-        <v>459</v>
-      </c>
-      <c r="L3" t="s">
-        <v>460</v>
-      </c>
-      <c r="M3" t="s">
-        <v>461</v>
-      </c>
-      <c r="N3" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10723,60 +10706,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" t="s">
+        <v>459</v>
+      </c>
+      <c r="E4" t="s">
+        <v>460</v>
+      </c>
+      <c r="F4" t="s">
+        <v>461</v>
+      </c>
+      <c r="G4" t="s">
+        <v>462</v>
+      </c>
+      <c r="H4" t="s">
         <v>463</v>
-      </c>
-      <c r="C4" t="s">
-        <v>464</v>
-      </c>
-      <c r="D4" t="s">
-        <v>465</v>
-      </c>
-      <c r="E4" t="s">
-        <v>466</v>
-      </c>
-      <c r="F4" t="s">
-        <v>467</v>
-      </c>
-      <c r="G4" t="s">
-        <v>468</v>
-      </c>
-      <c r="H4" t="s">
-        <v>469</v>
       </c>
       <c r="I4" t="s">
         <v>325</v>
       </c>
       <c r="J4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="K4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="M4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="N4" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10788,39 +10771,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="J5" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="K5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="L5" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="M5" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N5" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10832,39 +10815,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="J6" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="K6" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="L6" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="M6" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="N6" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10876,39 +10859,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="J7" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="K7" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="L7" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="M7" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="N7" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10920,39 +10903,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="J8" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="K8" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="L8" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M8" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="N8" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10964,39 +10947,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="J9" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="K9" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="L9" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="M9" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="N9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -11008,39 +10991,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="J10" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="K10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="L10" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="M10" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="N10" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -11052,39 +11035,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="J11" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="K11" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="L11" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="M11" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="N11" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -11096,39 +11079,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="J12" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="K12" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="L12" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="M12" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="N12" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -11140,39 +11123,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="J13" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="K13" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="L13" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M13" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="N13" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -11184,39 +11167,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="J14" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="K14" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="L14" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="M14" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="N14" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -11228,42 +11211,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="J15" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="K15" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="L15" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="M15" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="N15" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F16" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -11272,42 +11255,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="J16" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="K16" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="L16" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="M16" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="N16" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F17" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11316,42 +11299,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="J17" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="K17" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="L17" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="M17" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="N17" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F18" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11360,42 +11343,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="J18" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="K18" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="L18" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="M18" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="N18" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F19" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11404,42 +11387,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="J19" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="K19" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="L19" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="M19" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="N19" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F20" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11448,42 +11431,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="J20" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="K20" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="L20" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="M20" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="N20" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F21" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11492,42 +11475,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="J21" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="K21" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="L21" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="M21" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="N21" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F22" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11536,42 +11519,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="J22" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="K22" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="L22" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="M22" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="N22" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="F23" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11580,86 +11563,86 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="J23" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="K23" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="L23" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="M23" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="N23" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
+        <v>613</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>605</v>
+      </c>
+      <c r="F24" t="s">
+        <v>614</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>615</v>
+      </c>
+      <c r="J24" t="s">
+        <v>616</v>
+      </c>
+      <c r="K24" t="s">
+        <v>617</v>
+      </c>
+      <c r="L24" t="s">
+        <v>618</v>
+      </c>
+      <c r="M24" t="s">
         <v>619</v>
       </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>611</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="N24" t="s">
         <v>620</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
-        <v>621</v>
-      </c>
-      <c r="J24" t="s">
-        <v>622</v>
-      </c>
-      <c r="K24" t="s">
-        <v>623</v>
-      </c>
-      <c r="L24" t="s">
-        <v>624</v>
-      </c>
-      <c r="M24" t="s">
-        <v>625</v>
-      </c>
-      <c r="N24" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="F25" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11668,22 +11651,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="L25" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="M25" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="N25" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11691,13 +11674,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11709,22 +11692,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="J26" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="K26" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="L26" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="M26" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="N26" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11732,16 +11715,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F27" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11750,39 +11733,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="J27" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="K27" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="L27" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="M27" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="N27" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11794,39 +11777,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="J28" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="K28" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="L28" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="M28" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="N28" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11838,39 +11821,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="J29" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="K29" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="L29" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="M29" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="N29" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11882,39 +11865,39 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="J30" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="K30" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="L30" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="M30" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="N30" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F31" t="s">
         <v>290</v>
@@ -11926,22 +11909,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="J31" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="K31" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="L31" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="M31" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="N31" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11949,16 +11932,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F32" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11967,22 +11950,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="J32" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="K32" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="L32" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="M32" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="N32" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="987">
   <si>
     <t>Dog</t>
   </si>
@@ -951,9 +951,6 @@
     <t>OverrideHeadwear</t>
   </si>
   <si>
-    <t>WearGlasses</t>
-  </si>
-  <si>
     <t>LeftPawAnimation</t>
   </si>
   <si>
@@ -969,247 +966,241 @@
     <t>EDogReactionTrigger</t>
   </si>
   <si>
+    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
+  </si>
+  <si>
+    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
+  </si>
+  <si>
+    <t>左指画面左侧，而非狗自己的左</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>引用枚举</t>
+  </si>
+  <si>
+    <t>耳朵资源</t>
+  </si>
+  <si>
+    <t>眼睛资源</t>
+  </si>
+  <si>
+    <t>嘴部资源</t>
+  </si>
+  <si>
+    <t>头饰变化</t>
+  </si>
+  <si>
+    <t>左爪子</t>
+  </si>
+  <si>
+    <t>右爪子</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>手背</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>手心，摆手</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>哈喽</t>
+  </si>
+  <si>
+    <t>手心，摆手两次</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
+  </si>
+  <si>
+    <t>WaitingForBet</t>
+  </si>
+  <si>
+    <t>等待下注时</t>
+  </si>
+  <si>
+    <t>默认，该品种狗默认表情</t>
+  </si>
+  <si>
+    <t>Dealt</t>
+  </si>
+  <si>
+    <t>等待玩家选牌</t>
+  </si>
+  <si>
+    <t>WaitingForHint</t>
+  </si>
+  <si>
+    <t>玩家选牌中等待询问时</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问</t>
+  </si>
+  <si>
+    <t>HintResult</t>
+  </si>
+  <si>
+    <t>展示询问结果</t>
+  </si>
+  <si>
+    <t>Bespoke</t>
+  </si>
+  <si>
+    <t>约定</t>
+  </si>
+  <si>
+    <t>如果玩家进行了询问，再作出相应的预测表情。（未真实现具体内容只做表内意图表达）</t>
+  </si>
+  <si>
+    <t>HintExhausted</t>
+  </si>
+  <si>
+    <t>询问机会用尽</t>
+  </si>
+  <si>
+    <t>如果玩家又更改了选牌，则作出拒绝回答的表情。</t>
+  </si>
+  <si>
+    <t>RefuseHint</t>
+  </si>
+  <si>
+    <t>拒绝询问</t>
+  </si>
+  <si>
+    <t>如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
+  </si>
+  <si>
+    <t>严肃，面无表情</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>看到结算结果</t>
+  </si>
+  <si>
+    <t>根据牌型优劣作出相应表情（未真实现具体内容只做表内意图表达）</t>
+  </si>
+  <si>
+    <t>InteractionHint</t>
+  </si>
+  <si>
+    <t>提示玩家可以询问</t>
+  </si>
+  <si>
+    <t>SawNothing</t>
+  </si>
+  <si>
+    <t>看到坏牌</t>
+  </si>
+  <si>
+    <t>SawOnePair</t>
+  </si>
+  <si>
+    <t>看到一对</t>
+  </si>
+  <si>
+    <t>SawTwoPair</t>
+  </si>
+  <si>
+    <t>看到两对</t>
+  </si>
+  <si>
+    <t>SawThreeOfAKind</t>
+  </si>
+  <si>
+    <t>看到三条</t>
+  </si>
+  <si>
+    <t>SawStraight</t>
+  </si>
+  <si>
+    <t>看到顺子</t>
+  </si>
+  <si>
+    <t>SawFlush</t>
+  </si>
+  <si>
+    <t>看到同花</t>
+  </si>
+  <si>
+    <t>SawFullHouse</t>
+  </si>
+  <si>
+    <t>看到葫芦</t>
+  </si>
+  <si>
+    <t>SawFourOfAKind</t>
+  </si>
+  <si>
+    <t>看到四条</t>
+  </si>
+  <si>
+    <t>SawStraightFlush</t>
+  </si>
+  <si>
+    <t>看到同花顺</t>
+  </si>
+  <si>
+    <t>SawRoyalFlush</t>
+  </si>
+  <si>
+    <t>看到皇家同花顺</t>
+  </si>
+  <si>
+    <t>RefuseRefreshment</t>
+  </si>
+  <si>
+    <t>劝玩家别喝了</t>
+  </si>
+  <si>
+    <t>当有Buff持续中时，玩家又在背包中点击了Refreshment，则狗狗作出该表情动作</t>
+  </si>
+  <si>
+    <t>StateName</t>
+  </si>
+  <si>
+    <t>MinInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MaxInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MinDurationSeconds</t>
+  </si>
+  <si>
+    <t>CooldownSeconds</t>
+  </si>
+  <si>
+    <t>EnableTongueFeedback</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>bool</t>
-  </si>
-  <si>
-    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
-  </si>
-  <si>
-    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
-  </si>
-  <si>
-    <t>该功能处于改版器，暂时禁用效果。bool字段保留后续用其他方式表示狗狗沉默。</t>
-  </si>
-  <si>
-    <t>左指画面左侧，而非狗自己的左</t>
-  </si>
-  <si>
-    <t>枚举</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>引用枚举</t>
-  </si>
-  <si>
-    <t>耳朵资源</t>
-  </si>
-  <si>
-    <t>眼睛资源</t>
-  </si>
-  <si>
-    <t>嘴部资源</t>
-  </si>
-  <si>
-    <t>头饰变化</t>
-  </si>
-  <si>
-    <t>戴上眼镜</t>
-  </si>
-  <si>
-    <t>左爪子</t>
-  </si>
-  <si>
-    <t>右爪子</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>手背</t>
-  </si>
-  <si>
-    <t>正常</t>
-  </si>
-  <si>
-    <t>手心，摆手</t>
-  </si>
-  <si>
-    <t>Hello</t>
-  </si>
-  <si>
-    <t>哈喽</t>
-  </si>
-  <si>
-    <t>手心，摆手两次</t>
-  </si>
-  <si>
-    <t>哈气</t>
-  </si>
-  <si>
-    <t>舌头上下略微移动</t>
-  </si>
-  <si>
-    <t>WaitingForBet</t>
-  </si>
-  <si>
-    <t>等待下注时</t>
-  </si>
-  <si>
-    <t>默认，该品种狗默认表情</t>
-  </si>
-  <si>
-    <t>Dealt</t>
-  </si>
-  <si>
-    <t>等待玩家选牌</t>
-  </si>
-  <si>
-    <t>WaitingForHint</t>
-  </si>
-  <si>
-    <t>玩家选牌中等待询问时</t>
-  </si>
-  <si>
-    <t>严肃，面无表情，等待玩家询问</t>
-  </si>
-  <si>
-    <t>HintResult</t>
-  </si>
-  <si>
-    <t>展示询问结果</t>
-  </si>
-  <si>
-    <t>Bespoke</t>
-  </si>
-  <si>
-    <t>约定</t>
-  </si>
-  <si>
-    <t>如果玩家进行了询问，再作出相应的预测表情。（未真实现具体内容只做表内意图表达）</t>
-  </si>
-  <si>
-    <t>HintExhausted</t>
-  </si>
-  <si>
-    <t>询问机会用尽</t>
-  </si>
-  <si>
-    <t>如果玩家又更改了选牌，则作出拒绝回答的表情。</t>
-  </si>
-  <si>
-    <t>RefuseHint</t>
-  </si>
-  <si>
-    <t>拒绝询问</t>
-  </si>
-  <si>
-    <t>如果玩家再次询问，则作出拒绝回答的动作。</t>
-  </si>
-  <si>
-    <t>Drawing</t>
-  </si>
-  <si>
-    <t>补牌中</t>
-  </si>
-  <si>
-    <t>严肃，面无表情</t>
-  </si>
-  <si>
-    <t>Settled</t>
-  </si>
-  <si>
-    <t>看到结算结果</t>
-  </si>
-  <si>
-    <t>根据牌型优劣作出相应表情（未真实现具体内容只做表内意图表达）</t>
-  </si>
-  <si>
-    <t>InteractionHint</t>
-  </si>
-  <si>
-    <t>提示玩家可以询问</t>
-  </si>
-  <si>
-    <t>SawNothing</t>
-  </si>
-  <si>
-    <t>看到坏牌</t>
-  </si>
-  <si>
-    <t>SawOnePair</t>
-  </si>
-  <si>
-    <t>看到一对</t>
-  </si>
-  <si>
-    <t>SawTwoPair</t>
-  </si>
-  <si>
-    <t>看到两对</t>
-  </si>
-  <si>
-    <t>SawThreeOfAKind</t>
-  </si>
-  <si>
-    <t>看到三条</t>
-  </si>
-  <si>
-    <t>SawStraight</t>
-  </si>
-  <si>
-    <t>看到顺子</t>
-  </si>
-  <si>
-    <t>SawFlush</t>
-  </si>
-  <si>
-    <t>看到同花</t>
-  </si>
-  <si>
-    <t>SawFullHouse</t>
-  </si>
-  <si>
-    <t>看到葫芦</t>
-  </si>
-  <si>
-    <t>SawFourOfAKind</t>
-  </si>
-  <si>
-    <t>看到四条</t>
-  </si>
-  <si>
-    <t>SawStraightFlush</t>
-  </si>
-  <si>
-    <t>看到同花顺</t>
-  </si>
-  <si>
-    <t>SawRoyalFlush</t>
-  </si>
-  <si>
-    <t>看到皇家同花顺</t>
-  </si>
-  <si>
-    <t>RefuseRefreshment</t>
-  </si>
-  <si>
-    <t>劝玩家别喝了</t>
-  </si>
-  <si>
-    <t>当有Buff持续中时，玩家又在背包中点击了Refreshment，则狗狗作出该表情动作</t>
-  </si>
-  <si>
-    <t>StateName</t>
-  </si>
-  <si>
-    <t>MinInputEventsPerMinute</t>
-  </si>
-  <si>
-    <t>MaxInputEventsPerMinute</t>
-  </si>
-  <si>
-    <t>MinDurationSeconds</t>
-  </si>
-  <si>
-    <t>CooldownSeconds</t>
-  </si>
-  <si>
-    <t>EnableTongueFeedback</t>
-  </si>
-  <si>
-    <t>Priority</t>
   </si>
   <si>
     <t>行 ID</t>
@@ -4607,31 +4598,31 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D1" t="s">
+        <v>679</v>
+      </c>
+      <c r="E1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" t="s">
         <v>680</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>681</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>682</v>
       </c>
-      <c r="E1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>683</v>
       </c>
-      <c r="G1" t="s">
-        <v>684</v>
-      </c>
-      <c r="H1" t="s">
-        <v>685</v>
-      </c>
-      <c r="I1" t="s">
-        <v>686</v>
-      </c>
       <c r="J1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4648,19 +4639,19 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="F2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="G2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="J2" t="s">
         <v>109</v>
@@ -4671,31 +4662,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4703,1471 +4694,1471 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C4" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D4" t="s">
         <v>275</v>
       </c>
       <c r="E4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F4" t="s">
+        <v>697</v>
+      </c>
+      <c r="G4" t="s">
+        <v>698</v>
+      </c>
+      <c r="H4" t="s">
+        <v>699</v>
+      </c>
+      <c r="I4" t="s">
         <v>700</v>
       </c>
-      <c r="G4" t="s">
-        <v>701</v>
-      </c>
-      <c r="H4" t="s">
-        <v>702</v>
-      </c>
-      <c r="I4" t="s">
-        <v>703</v>
-      </c>
       <c r="J4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>703</v>
+      </c>
+      <c r="G5" t="s">
         <v>704</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>705</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>706</v>
-      </c>
-      <c r="G5" t="s">
-        <v>707</v>
-      </c>
-      <c r="H5" t="s">
-        <v>708</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>707</v>
+      </c>
+      <c r="D6" t="s">
+        <v>708</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>709</v>
+      </c>
+      <c r="G6" t="s">
+        <v>704</v>
+      </c>
+      <c r="H6" t="s">
         <v>710</v>
-      </c>
-      <c r="D6" t="s">
-        <v>711</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>712</v>
-      </c>
-      <c r="G6" t="s">
-        <v>707</v>
-      </c>
-      <c r="H6" t="s">
-        <v>713</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>712</v>
+      </c>
+      <c r="D7" t="s">
+        <v>713</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>703</v>
+      </c>
+      <c r="G7" t="s">
+        <v>704</v>
+      </c>
+      <c r="H7" t="s">
+        <v>714</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>715</v>
-      </c>
-      <c r="D7" t="s">
-        <v>716</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>706</v>
-      </c>
-      <c r="G7" t="s">
-        <v>707</v>
-      </c>
-      <c r="H7" t="s">
-        <v>717</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D8" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="G8" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H8" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D9" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G9" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H9" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>724</v>
+      </c>
+      <c r="D10" t="s">
+        <v>725</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>726</v>
+      </c>
+      <c r="G10" t="s">
+        <v>704</v>
+      </c>
+      <c r="H10" t="s">
         <v>727</v>
       </c>
-      <c r="D10" t="s">
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
         <v>728</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>729</v>
-      </c>
-      <c r="G10" t="s">
-        <v>707</v>
-      </c>
-      <c r="H10" t="s">
-        <v>730</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D11" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G11" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H11" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D12" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G12" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H12" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D13" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G13" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H13" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D14" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="G14" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H14" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D15" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="G15" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H15" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D16" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G16" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H16" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D17" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G17" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H17" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D18" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G18" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H18" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D19" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G19" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H19" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D20" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G20" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H20" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D21" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G21" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H21" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D22" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G22" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H22" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D23" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G23" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H23" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D24" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G24" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H24" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D25" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G25" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H25" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D26" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G26" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H26" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D27" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="G27" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H27" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D28" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G28" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H28" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D29" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G29" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H29" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D30" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G30" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H30" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D31" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G31" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H31" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D32" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G32" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H32" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D33" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G33" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H33" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D34" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G34" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H34" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D35" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G35" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H35" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D36" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G36" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H36" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D37" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G37" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H37" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D38" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G38" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H38" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D39" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G39" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H39" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D40" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G40" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H40" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D41" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G41" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H41" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D42" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G42" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H42" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D43" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G43" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H43" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D44" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G44" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H44" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D45" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G45" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H45" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D46" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G46" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H46" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D47" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G47" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H47" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D48" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G48" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H48" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D49" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G49" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H49" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6175,28 +6166,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D50" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G50" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H50" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6204,28 +6195,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
+        <v>882</v>
+      </c>
+      <c r="D51" t="s">
+        <v>883</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>726</v>
+      </c>
+      <c r="G51" t="s">
+        <v>884</v>
+      </c>
+      <c r="H51" t="s">
         <v>885</v>
-      </c>
-      <c r="D51" t="s">
-        <v>886</v>
-      </c>
-      <c r="E51" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" t="s">
-        <v>729</v>
-      </c>
-      <c r="G51" t="s">
-        <v>887</v>
-      </c>
-      <c r="H51" t="s">
-        <v>888</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6233,28 +6224,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
+        <v>887</v>
+      </c>
+      <c r="D52" t="s">
+        <v>888</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>889</v>
+      </c>
+      <c r="G52" t="s">
+        <v>889</v>
+      </c>
+      <c r="H52" t="s">
         <v>890</v>
       </c>
-      <c r="D52" t="s">
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
         <v>891</v>
-      </c>
-      <c r="E52" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" t="s">
-        <v>892</v>
-      </c>
-      <c r="G52" t="s">
-        <v>892</v>
-      </c>
-      <c r="H52" t="s">
-        <v>893</v>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6262,28 +6253,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
+        <v>892</v>
+      </c>
+      <c r="D53" t="s">
+        <v>893</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>889</v>
+      </c>
+      <c r="G53" t="s">
+        <v>889</v>
+      </c>
+      <c r="H53" t="s">
+        <v>894</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
         <v>895</v>
-      </c>
-      <c r="D53" t="s">
-        <v>896</v>
-      </c>
-      <c r="E53" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" t="s">
-        <v>892</v>
-      </c>
-      <c r="G53" t="s">
-        <v>892</v>
-      </c>
-      <c r="H53" t="s">
-        <v>897</v>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6291,28 +6282,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
+        <v>896</v>
+      </c>
+      <c r="D54" t="s">
+        <v>897</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>889</v>
+      </c>
+      <c r="G54" t="s">
+        <v>889</v>
+      </c>
+      <c r="H54" t="s">
+        <v>898</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
         <v>899</v>
-      </c>
-      <c r="D54" t="s">
-        <v>900</v>
-      </c>
-      <c r="E54" t="b">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>892</v>
-      </c>
-      <c r="G54" t="s">
-        <v>892</v>
-      </c>
-      <c r="H54" t="s">
-        <v>901</v>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6320,28 +6311,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
+        <v>900</v>
+      </c>
+      <c r="D55" t="s">
+        <v>901</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>889</v>
+      </c>
+      <c r="G55" t="s">
+        <v>889</v>
+      </c>
+      <c r="H55" t="s">
+        <v>902</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="s">
         <v>903</v>
-      </c>
-      <c r="D55" t="s">
-        <v>904</v>
-      </c>
-      <c r="E55" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>892</v>
-      </c>
-      <c r="G55" t="s">
-        <v>892</v>
-      </c>
-      <c r="H55" t="s">
-        <v>905</v>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6349,28 +6340,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
+        <v>904</v>
+      </c>
+      <c r="D56" t="s">
+        <v>905</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>889</v>
+      </c>
+      <c r="G56" t="s">
+        <v>889</v>
+      </c>
+      <c r="H56" t="s">
+        <v>906</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="s">
         <v>907</v>
-      </c>
-      <c r="D56" t="s">
-        <v>908</v>
-      </c>
-      <c r="E56" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>892</v>
-      </c>
-      <c r="G56" t="s">
-        <v>892</v>
-      </c>
-      <c r="H56" t="s">
-        <v>909</v>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6378,28 +6369,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
+        <v>908</v>
+      </c>
+      <c r="D57" t="s">
+        <v>909</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>703</v>
+      </c>
+      <c r="G57" t="s">
+        <v>704</v>
+      </c>
+      <c r="H57" t="s">
+        <v>910</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
         <v>911</v>
-      </c>
-      <c r="D57" t="s">
-        <v>912</v>
-      </c>
-      <c r="E57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" t="s">
-        <v>706</v>
-      </c>
-      <c r="G57" t="s">
-        <v>707</v>
-      </c>
-      <c r="H57" t="s">
-        <v>913</v>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6407,28 +6398,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
+        <v>912</v>
+      </c>
+      <c r="D58" t="s">
+        <v>913</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>709</v>
+      </c>
+      <c r="G58" t="s">
+        <v>704</v>
+      </c>
+      <c r="H58" t="s">
+        <v>914</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="s">
         <v>915</v>
-      </c>
-      <c r="D58" t="s">
-        <v>916</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" t="s">
-        <v>712</v>
-      </c>
-      <c r="G58" t="s">
-        <v>707</v>
-      </c>
-      <c r="H58" t="s">
-        <v>917</v>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6436,28 +6427,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
+        <v>916</v>
+      </c>
+      <c r="D59" t="s">
+        <v>917</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>889</v>
+      </c>
+      <c r="G59" t="s">
+        <v>889</v>
+      </c>
+      <c r="H59" t="s">
+        <v>918</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
         <v>919</v>
-      </c>
-      <c r="D59" t="s">
-        <v>920</v>
-      </c>
-      <c r="E59" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" t="s">
-        <v>892</v>
-      </c>
-      <c r="G59" t="s">
-        <v>892</v>
-      </c>
-      <c r="H59" t="s">
-        <v>921</v>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6465,28 +6456,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
+        <v>920</v>
+      </c>
+      <c r="D60" t="s">
+        <v>921</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>889</v>
+      </c>
+      <c r="G60" t="s">
+        <v>889</v>
+      </c>
+      <c r="H60" t="s">
+        <v>922</v>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
         <v>923</v>
-      </c>
-      <c r="D60" t="s">
-        <v>924</v>
-      </c>
-      <c r="E60" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" t="s">
-        <v>892</v>
-      </c>
-      <c r="G60" t="s">
-        <v>892</v>
-      </c>
-      <c r="H60" t="s">
-        <v>925</v>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6494,28 +6485,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
+        <v>924</v>
+      </c>
+      <c r="D61" t="s">
+        <v>925</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>889</v>
+      </c>
+      <c r="G61" t="s">
+        <v>889</v>
+      </c>
+      <c r="H61" t="s">
+        <v>926</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
         <v>927</v>
-      </c>
-      <c r="D61" t="s">
-        <v>928</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>892</v>
-      </c>
-      <c r="G61" t="s">
-        <v>892</v>
-      </c>
-      <c r="H61" t="s">
-        <v>929</v>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6523,92 +6514,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
+        <v>928</v>
+      </c>
+      <c r="D62" t="s">
+        <v>929</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>889</v>
+      </c>
+      <c r="G62" t="s">
+        <v>889</v>
+      </c>
+      <c r="H62" t="s">
+        <v>930</v>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
         <v>931</v>
-      </c>
-      <c r="D62" t="s">
-        <v>932</v>
-      </c>
-      <c r="E62" t="b">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>892</v>
-      </c>
-      <c r="G62" t="s">
-        <v>892</v>
-      </c>
-      <c r="H62" t="s">
-        <v>933</v>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
+        <v>932</v>
+      </c>
+      <c r="D63" t="s">
+        <v>933</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>726</v>
+      </c>
+      <c r="G63" t="s">
+        <v>704</v>
+      </c>
+      <c r="H63" t="s">
+        <v>934</v>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
         <v>935</v>
-      </c>
-      <c r="D63" t="s">
-        <v>936</v>
-      </c>
-      <c r="E63" t="b">
-        <v>1</v>
-      </c>
-      <c r="F63" t="s">
-        <v>729</v>
-      </c>
-      <c r="G63" t="s">
-        <v>707</v>
-      </c>
-      <c r="H63" t="s">
-        <v>937</v>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
+        <v>936</v>
+      </c>
+      <c r="D64" t="s">
+        <v>937</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>726</v>
+      </c>
+      <c r="G64" t="s">
+        <v>704</v>
+      </c>
+      <c r="H64" t="s">
+        <v>938</v>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
         <v>939</v>
-      </c>
-      <c r="D64" t="s">
-        <v>940</v>
-      </c>
-      <c r="E64" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>729</v>
-      </c>
-      <c r="G64" t="s">
-        <v>707</v>
-      </c>
-      <c r="H64" t="s">
-        <v>941</v>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6616,28 +6607,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
+        <v>940</v>
+      </c>
+      <c r="D65" t="s">
+        <v>941</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>709</v>
+      </c>
+      <c r="G65" t="s">
+        <v>884</v>
+      </c>
+      <c r="H65" t="s">
+        <v>942</v>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
         <v>943</v>
-      </c>
-      <c r="D65" t="s">
-        <v>944</v>
-      </c>
-      <c r="E65" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" t="s">
-        <v>712</v>
-      </c>
-      <c r="G65" t="s">
-        <v>887</v>
-      </c>
-      <c r="H65" t="s">
-        <v>945</v>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="s">
-        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -6672,25 +6663,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C1" t="s">
+        <v>945</v>
+      </c>
+      <c r="D1" t="s">
+        <v>946</v>
+      </c>
+      <c r="E1" t="s">
         <v>947</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>948</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>949</v>
       </c>
-      <c r="E1" t="s">
-        <v>950</v>
-      </c>
-      <c r="F1" t="s">
-        <v>951</v>
-      </c>
-      <c r="G1" t="s">
-        <v>952</v>
-      </c>
       <c r="H1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6704,7 +6695,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6724,28 +6715,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>958</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6753,39 +6744,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C4" t="s">
+        <v>951</v>
+      </c>
+      <c r="D4" t="s">
+        <v>959</v>
+      </c>
+      <c r="E4" t="s">
+        <v>960</v>
+      </c>
+      <c r="F4" t="s">
         <v>961</v>
       </c>
-      <c r="C4" t="s">
-        <v>954</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>962</v>
       </c>
-      <c r="E4" t="s">
-        <v>963</v>
-      </c>
-      <c r="F4" t="s">
-        <v>964</v>
-      </c>
-      <c r="G4" t="s">
-        <v>965</v>
-      </c>
       <c r="H4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B5" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C5" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6803,18 +6794,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B6" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C6" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6832,18 +6823,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B7" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="C7" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6861,18 +6852,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B8" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C8" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6890,18 +6881,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B9" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C9" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6919,18 +6910,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B10" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="C10" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6948,18 +6939,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B11" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C11" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6977,18 +6968,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B12" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C12" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -7006,7 +6997,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -9256,7 +9247,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -9265,12 +9256,12 @@
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="12.75" customWidth="1"/>
     <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="11" width="11.5" customWidth="1"/>
-    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
-    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
+    <col min="9" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -9307,11 +9298,8 @@
       <c r="N1" t="s">
         <v>307</v>
       </c>
-      <c r="O1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -9319,10 +9307,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -9337,7 +9325,7 @@
         <v>109</v>
       </c>
       <c r="K2" t="s">
-        <v>310</v>
+        <v>109</v>
       </c>
       <c r="L2" t="s">
         <v>109</v>
@@ -9348,30 +9336,24 @@
       <c r="N2" t="s">
         <v>109</v>
       </c>
-      <c r="O2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" ht="104.4" spans="1:15">
+    </row>
+    <row r="3" ht="104.4" spans="1:14">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>110</v>
       </c>
@@ -9379,46 +9361,43 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G4" t="s">
         <v>315</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>316</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>317</v>
       </c>
-      <c r="F4" t="s">
-        <v>316</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>318</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>319</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>320</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
+        <v>207</v>
+      </c>
+      <c r="N4" t="s">
         <v>321</v>
       </c>
-      <c r="K4" t="s">
-        <v>322</v>
-      </c>
-      <c r="L4" t="s">
-        <v>323</v>
-      </c>
-      <c r="M4" t="s">
-        <v>324</v>
-      </c>
-      <c r="N4" t="s">
-        <v>207</v>
-      </c>
-      <c r="O4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -9437,20 +9416,17 @@
       <c r="I5" t="s">
         <v>185</v>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
+      <c r="K5" t="s">
+        <v>322</v>
       </c>
       <c r="L5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M5" t="s">
-        <v>326</v>
-      </c>
-      <c r="N5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -9469,20 +9445,17 @@
       <c r="I6" t="s">
         <v>185</v>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
+      <c r="K6" t="s">
+        <v>322</v>
       </c>
       <c r="L6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M6" t="s">
-        <v>326</v>
-      </c>
-      <c r="N6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -9501,20 +9474,17 @@
       <c r="I7" t="s">
         <v>185</v>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
+      <c r="K7" t="s">
+        <v>322</v>
       </c>
       <c r="L7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M7" t="s">
-        <v>326</v>
-      </c>
-      <c r="N7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -9533,20 +9503,17 @@
       <c r="I8" t="s">
         <v>185</v>
       </c>
-      <c r="K8" t="b">
-        <v>0</v>
+      <c r="K8" t="s">
+        <v>322</v>
       </c>
       <c r="L8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M8" t="s">
-        <v>326</v>
-      </c>
-      <c r="N8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -9565,20 +9532,17 @@
       <c r="I9" t="s">
         <v>185</v>
       </c>
-      <c r="K9" t="b">
-        <v>0</v>
+      <c r="K9" t="s">
+        <v>322</v>
       </c>
       <c r="L9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M9" t="s">
-        <v>326</v>
-      </c>
-      <c r="N9" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -9597,20 +9561,17 @@
       <c r="I10" t="s">
         <v>185</v>
       </c>
-      <c r="K10" t="b">
-        <v>0</v>
+      <c r="K10" t="s">
+        <v>322</v>
       </c>
       <c r="L10" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M10" t="s">
-        <v>326</v>
-      </c>
-      <c r="N10" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -9629,20 +9590,17 @@
       <c r="I11" t="s">
         <v>186</v>
       </c>
-      <c r="K11" t="b">
-        <v>1</v>
+      <c r="K11" t="s">
+        <v>322</v>
       </c>
       <c r="L11" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M11" t="s">
-        <v>326</v>
-      </c>
-      <c r="N11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -9661,28 +9619,25 @@
       <c r="I12" t="s">
         <v>185</v>
       </c>
-      <c r="K12" t="b">
-        <v>1</v>
+      <c r="K12" t="s">
+        <v>324</v>
       </c>
       <c r="L12" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M12" t="s">
-        <v>328</v>
-      </c>
-      <c r="N12" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G13" t="s">
         <v>187</v>
@@ -9693,31 +9648,28 @@
       <c r="I13" t="s">
         <v>185</v>
       </c>
-      <c r="K13" t="b">
-        <v>0</v>
+      <c r="K13" t="s">
+        <v>322</v>
       </c>
       <c r="L13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M13" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N13" t="s">
-        <v>332</v>
-      </c>
-      <c r="O13" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="B14">
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9725,19 +9677,19 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-      <c r="O14" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="B15">
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9745,19 +9697,19 @@
       <c r="F15" t="s">
         <v>8</v>
       </c>
-      <c r="O15" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="B16">
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9765,39 +9717,39 @@
       <c r="F16" t="s">
         <v>17</v>
       </c>
-      <c r="O16" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15">
+      <c r="N16" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17">
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" t="s">
+        <v>341</v>
+      </c>
+      <c r="N17" t="s">
         <v>342</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="F17" t="s">
-        <v>345</v>
-      </c>
-      <c r="O17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15">
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18">
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9805,19 +9757,19 @@
       <c r="F18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="O18" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15">
+      <c r="N18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
       <c r="B19">
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9825,19 +9777,19 @@
       <c r="F19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="O19" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15">
+      <c r="N19" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
       <c r="B20">
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9845,56 +9797,56 @@
       <c r="F20" t="s">
         <v>17</v>
       </c>
-      <c r="O20" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15">
+      <c r="N20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21">
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E21" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F21" t="s">
-        <v>345</v>
-      </c>
-      <c r="O21" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15">
+        <v>341</v>
+      </c>
+      <c r="N21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22">
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23">
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9903,15 +9855,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:14">
       <c r="B24">
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9920,15 +9872,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:14">
       <c r="B25">
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9937,15 +9889,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:14">
       <c r="B26">
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9954,15 +9906,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:14">
       <c r="B27">
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9971,15 +9923,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:14">
       <c r="B28">
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -9988,15 +9940,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:14">
       <c r="B29">
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -10004,22 +9956,22 @@
       <c r="F29" t="s">
         <v>44</v>
       </c>
+      <c r="M29" t="s">
+        <v>328</v>
+      </c>
       <c r="N29" t="s">
-        <v>332</v>
-      </c>
-      <c r="O29" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
       <c r="B30">
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -10028,15 +9980,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:14">
       <c r="B31">
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -10045,15 +9997,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:14">
       <c r="B32">
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -10061,22 +10013,22 @@
       <c r="F32" t="s">
         <v>53</v>
       </c>
+      <c r="M32" t="s">
+        <v>328</v>
+      </c>
       <c r="N32" t="s">
-        <v>332</v>
-      </c>
-      <c r="O32" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="2:15">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:14">
       <c r="B33">
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -10084,8 +10036,8 @@
       <c r="F33" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="O33" t="s">
-        <v>383</v>
+      <c r="N33" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -10121,31 +10073,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G1" t="s">
         <v>384</v>
-      </c>
-      <c r="D1" t="s">
-        <v>385</v>
-      </c>
-      <c r="E1" t="s">
-        <v>386</v>
-      </c>
-      <c r="F1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G1" t="s">
-        <v>388</v>
       </c>
       <c r="H1" t="s">
         <v>298</v>
       </c>
       <c r="I1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -10171,10 +10123,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -10188,34 +10140,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -10226,31 +10178,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" t="s">
+        <v>399</v>
+      </c>
+      <c r="F4" t="s">
         <v>400</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>401</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>402</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>403</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>404</v>
       </c>
-      <c r="H4" t="s">
-        <v>405</v>
-      </c>
-      <c r="I4" t="s">
-        <v>406</v>
-      </c>
-      <c r="J4" t="s">
-        <v>407</v>
-      </c>
       <c r="K4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -10258,7 +10210,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10282,7 +10234,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10290,7 +10242,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10314,7 +10266,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10322,7 +10274,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10346,7 +10298,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10354,7 +10306,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10378,7 +10330,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -10412,13 +10364,13 @@
         <v>270</v>
       </c>
       <c r="D1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10435,7 +10387,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -10448,10 +10400,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10462,13 +10414,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10476,7 +10428,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10485,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10493,7 +10445,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10502,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10510,7 +10462,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10519,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10527,7 +10479,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10536,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10574,43 +10526,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E1" t="s">
         <v>430</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>431</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>432</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>433</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J1" t="s">
         <v>434</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>435</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>436</v>
       </c>
-      <c r="I1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>437</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>438</v>
-      </c>
-      <c r="L1" t="s">
-        <v>439</v>
-      </c>
-      <c r="M1" t="s">
-        <v>440</v>
-      </c>
-      <c r="N1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10624,19 +10576,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="E2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H2" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -10662,43 +10614,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" t="s">
         <v>449</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" t="s">
         <v>450</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" t="s">
         <v>451</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>452</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>453</v>
-      </c>
-      <c r="L3" t="s">
-        <v>454</v>
-      </c>
-      <c r="M3" t="s">
-        <v>455</v>
-      </c>
-      <c r="N3" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10706,60 +10658,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E4" t="s">
         <v>457</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>458</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>459</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>460</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
+        <v>321</v>
+      </c>
+      <c r="J4" t="s">
         <v>461</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>462</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L4" t="s">
         <v>463</v>
       </c>
-      <c r="I4" t="s">
-        <v>325</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>464</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>465</v>
-      </c>
-      <c r="L4" t="s">
-        <v>466</v>
-      </c>
-      <c r="M4" t="s">
-        <v>467</v>
-      </c>
-      <c r="N4" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10771,39 +10723,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
+        <v>468</v>
+      </c>
+      <c r="J5" t="s">
+        <v>469</v>
+      </c>
+      <c r="K5" t="s">
+        <v>470</v>
+      </c>
+      <c r="L5" t="s">
         <v>471</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>472</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>473</v>
-      </c>
-      <c r="L5" t="s">
-        <v>474</v>
-      </c>
-      <c r="M5" t="s">
-        <v>475</v>
-      </c>
-      <c r="N5" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10815,39 +10767,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
+        <v>475</v>
+      </c>
+      <c r="J6" t="s">
+        <v>476</v>
+      </c>
+      <c r="K6" t="s">
+        <v>477</v>
+      </c>
+      <c r="L6" t="s">
         <v>478</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>479</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
         <v>480</v>
-      </c>
-      <c r="L6" t="s">
-        <v>481</v>
-      </c>
-      <c r="M6" t="s">
-        <v>482</v>
-      </c>
-      <c r="N6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10859,39 +10811,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
+        <v>482</v>
+      </c>
+      <c r="J7" t="s">
+        <v>483</v>
+      </c>
+      <c r="K7" t="s">
+        <v>484</v>
+      </c>
+      <c r="L7" t="s">
         <v>485</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>486</v>
       </c>
-      <c r="K7" t="s">
+      <c r="N7" t="s">
         <v>487</v>
-      </c>
-      <c r="L7" t="s">
-        <v>488</v>
-      </c>
-      <c r="M7" t="s">
-        <v>489</v>
-      </c>
-      <c r="N7" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10903,39 +10855,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="J8" t="s">
+        <v>490</v>
+      </c>
+      <c r="K8" t="s">
+        <v>491</v>
+      </c>
+      <c r="L8" t="s">
         <v>492</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>493</v>
       </c>
-      <c r="K8" t="s">
+      <c r="N8" t="s">
         <v>494</v>
-      </c>
-      <c r="L8" t="s">
-        <v>495</v>
-      </c>
-      <c r="M8" t="s">
-        <v>496</v>
-      </c>
-      <c r="N8" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10947,39 +10899,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
+        <v>496</v>
+      </c>
+      <c r="J9" t="s">
+        <v>497</v>
+      </c>
+      <c r="K9" t="s">
+        <v>498</v>
+      </c>
+      <c r="L9" t="s">
         <v>499</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>500</v>
       </c>
-      <c r="K9" t="s">
+      <c r="N9" t="s">
         <v>501</v>
-      </c>
-      <c r="L9" t="s">
-        <v>502</v>
-      </c>
-      <c r="M9" t="s">
-        <v>503</v>
-      </c>
-      <c r="N9" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -10991,39 +10943,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
+        <v>503</v>
+      </c>
+      <c r="J10" t="s">
+        <v>504</v>
+      </c>
+      <c r="K10" t="s">
+        <v>505</v>
+      </c>
+      <c r="L10" t="s">
         <v>506</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>507</v>
       </c>
-      <c r="K10" t="s">
+      <c r="N10" t="s">
         <v>508</v>
-      </c>
-      <c r="L10" t="s">
-        <v>509</v>
-      </c>
-      <c r="M10" t="s">
-        <v>510</v>
-      </c>
-      <c r="N10" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -11035,39 +10987,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
+        <v>510</v>
+      </c>
+      <c r="J11" t="s">
+        <v>511</v>
+      </c>
+      <c r="K11" t="s">
+        <v>512</v>
+      </c>
+      <c r="L11" t="s">
         <v>513</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>514</v>
       </c>
-      <c r="K11" t="s">
+      <c r="N11" t="s">
         <v>515</v>
-      </c>
-      <c r="L11" t="s">
-        <v>516</v>
-      </c>
-      <c r="M11" t="s">
-        <v>517</v>
-      </c>
-      <c r="N11" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -11079,39 +11031,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
+        <v>517</v>
+      </c>
+      <c r="J12" t="s">
+        <v>518</v>
+      </c>
+      <c r="K12" t="s">
+        <v>519</v>
+      </c>
+      <c r="L12" t="s">
         <v>520</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>521</v>
       </c>
-      <c r="K12" t="s">
+      <c r="N12" t="s">
         <v>522</v>
-      </c>
-      <c r="L12" t="s">
-        <v>523</v>
-      </c>
-      <c r="M12" t="s">
-        <v>524</v>
-      </c>
-      <c r="N12" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -11123,39 +11075,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
+        <v>524</v>
+      </c>
+      <c r="J13" t="s">
+        <v>525</v>
+      </c>
+      <c r="K13" t="s">
+        <v>526</v>
+      </c>
+      <c r="L13" t="s">
         <v>527</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>528</v>
       </c>
-      <c r="K13" t="s">
+      <c r="N13" t="s">
         <v>529</v>
-      </c>
-      <c r="L13" t="s">
-        <v>530</v>
-      </c>
-      <c r="M13" t="s">
-        <v>531</v>
-      </c>
-      <c r="N13" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -11167,39 +11119,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
+        <v>531</v>
+      </c>
+      <c r="J14" t="s">
+        <v>532</v>
+      </c>
+      <c r="K14" t="s">
+        <v>533</v>
+      </c>
+      <c r="L14" t="s">
         <v>534</v>
       </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
         <v>535</v>
       </c>
-      <c r="K14" t="s">
+      <c r="N14" t="s">
         <v>536</v>
-      </c>
-      <c r="L14" t="s">
-        <v>537</v>
-      </c>
-      <c r="M14" t="s">
-        <v>538</v>
-      </c>
-      <c r="N14" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -11211,42 +11163,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
+        <v>538</v>
+      </c>
+      <c r="J15" t="s">
+        <v>539</v>
+      </c>
+      <c r="K15" t="s">
+        <v>540</v>
+      </c>
+      <c r="L15" t="s">
         <v>541</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>542</v>
       </c>
-      <c r="K15" t="s">
+      <c r="N15" t="s">
         <v>543</v>
-      </c>
-      <c r="L15" t="s">
-        <v>544</v>
-      </c>
-      <c r="M15" t="s">
-        <v>545</v>
-      </c>
-      <c r="N15" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F16" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -11255,42 +11207,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
+        <v>547</v>
+      </c>
+      <c r="J16" t="s">
+        <v>548</v>
+      </c>
+      <c r="K16" t="s">
+        <v>549</v>
+      </c>
+      <c r="L16" t="s">
         <v>550</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>551</v>
       </c>
-      <c r="K16" t="s">
+      <c r="N16" t="s">
         <v>552</v>
-      </c>
-      <c r="L16" t="s">
-        <v>553</v>
-      </c>
-      <c r="M16" t="s">
-        <v>554</v>
-      </c>
-      <c r="N16" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F17" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11299,42 +11251,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
+        <v>555</v>
+      </c>
+      <c r="J17" t="s">
+        <v>556</v>
+      </c>
+      <c r="K17" t="s">
+        <v>557</v>
+      </c>
+      <c r="L17" t="s">
         <v>558</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>559</v>
       </c>
-      <c r="K17" t="s">
+      <c r="N17" t="s">
         <v>560</v>
-      </c>
-      <c r="L17" t="s">
-        <v>561</v>
-      </c>
-      <c r="M17" t="s">
-        <v>562</v>
-      </c>
-      <c r="N17" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F18" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11343,42 +11295,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
+        <v>563</v>
+      </c>
+      <c r="J18" t="s">
+        <v>564</v>
+      </c>
+      <c r="K18" t="s">
+        <v>565</v>
+      </c>
+      <c r="L18" t="s">
         <v>566</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>567</v>
       </c>
-      <c r="K18" t="s">
+      <c r="N18" t="s">
         <v>568</v>
-      </c>
-      <c r="L18" t="s">
-        <v>569</v>
-      </c>
-      <c r="M18" t="s">
-        <v>570</v>
-      </c>
-      <c r="N18" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F19" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11387,42 +11339,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
+        <v>571</v>
+      </c>
+      <c r="J19" t="s">
+        <v>572</v>
+      </c>
+      <c r="K19" t="s">
+        <v>573</v>
+      </c>
+      <c r="L19" t="s">
         <v>574</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>575</v>
       </c>
-      <c r="K19" t="s">
+      <c r="N19" t="s">
         <v>576</v>
-      </c>
-      <c r="L19" t="s">
-        <v>577</v>
-      </c>
-      <c r="M19" t="s">
-        <v>578</v>
-      </c>
-      <c r="N19" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F20" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11431,42 +11383,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
+        <v>579</v>
+      </c>
+      <c r="J20" t="s">
+        <v>580</v>
+      </c>
+      <c r="K20" t="s">
+        <v>581</v>
+      </c>
+      <c r="L20" t="s">
         <v>582</v>
       </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>583</v>
       </c>
-      <c r="K20" t="s">
+      <c r="N20" t="s">
         <v>584</v>
-      </c>
-      <c r="L20" t="s">
-        <v>585</v>
-      </c>
-      <c r="M20" t="s">
-        <v>586</v>
-      </c>
-      <c r="N20" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F21" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11475,42 +11427,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
+        <v>587</v>
+      </c>
+      <c r="J21" t="s">
+        <v>588</v>
+      </c>
+      <c r="K21" t="s">
+        <v>589</v>
+      </c>
+      <c r="L21" t="s">
         <v>590</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>591</v>
       </c>
-      <c r="K21" t="s">
+      <c r="N21" t="s">
         <v>592</v>
-      </c>
-      <c r="L21" t="s">
-        <v>593</v>
-      </c>
-      <c r="M21" t="s">
-        <v>594</v>
-      </c>
-      <c r="N21" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F22" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11519,42 +11471,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
+        <v>595</v>
+      </c>
+      <c r="J22" t="s">
+        <v>596</v>
+      </c>
+      <c r="K22" t="s">
+        <v>597</v>
+      </c>
+      <c r="L22" t="s">
         <v>598</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>599</v>
       </c>
-      <c r="K22" t="s">
+      <c r="N22" t="s">
         <v>600</v>
-      </c>
-      <c r="L22" t="s">
-        <v>601</v>
-      </c>
-      <c r="M22" t="s">
-        <v>602</v>
-      </c>
-      <c r="N22" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F23" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11563,86 +11515,86 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
+        <v>604</v>
+      </c>
+      <c r="J23" t="s">
+        <v>605</v>
+      </c>
+      <c r="K23" t="s">
+        <v>606</v>
+      </c>
+      <c r="L23" t="s">
         <v>607</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>608</v>
       </c>
-      <c r="K23" t="s">
+      <c r="N23" t="s">
         <v>609</v>
-      </c>
-      <c r="L23" t="s">
-        <v>610</v>
-      </c>
-      <c r="M23" t="s">
-        <v>611</v>
-      </c>
-      <c r="N23" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
+        <v>610</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>602</v>
+      </c>
+      <c r="F24" t="s">
+        <v>611</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>612</v>
+      </c>
+      <c r="J24" t="s">
         <v>613</v>
       </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>605</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="K24" t="s">
         <v>614</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="L24" t="s">
         <v>615</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>616</v>
       </c>
-      <c r="K24" t="s">
+      <c r="N24" t="s">
         <v>617</v>
-      </c>
-      <c r="L24" t="s">
-        <v>618</v>
-      </c>
-      <c r="M24" t="s">
-        <v>619</v>
-      </c>
-      <c r="N24" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F25" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11651,22 +11603,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
+        <v>621</v>
+      </c>
+      <c r="L25" t="s">
+        <v>622</v>
+      </c>
+      <c r="M25" t="s">
+        <v>623</v>
+      </c>
+      <c r="N25" t="s">
         <v>624</v>
-      </c>
-      <c r="L25" t="s">
-        <v>625</v>
-      </c>
-      <c r="M25" t="s">
-        <v>626</v>
-      </c>
-      <c r="N25" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11674,13 +11626,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11692,22 +11644,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
+        <v>627</v>
+      </c>
+      <c r="J26" t="s">
+        <v>628</v>
+      </c>
+      <c r="K26" t="s">
+        <v>629</v>
+      </c>
+      <c r="L26" t="s">
         <v>630</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>631</v>
       </c>
-      <c r="K26" t="s">
+      <c r="N26" t="s">
         <v>632</v>
-      </c>
-      <c r="L26" t="s">
-        <v>633</v>
-      </c>
-      <c r="M26" t="s">
-        <v>634</v>
-      </c>
-      <c r="N26" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11715,16 +11667,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F27" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11733,39 +11685,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
+        <v>635</v>
+      </c>
+      <c r="J27" t="s">
+        <v>636</v>
+      </c>
+      <c r="K27" t="s">
+        <v>637</v>
+      </c>
+      <c r="L27" t="s">
         <v>638</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>639</v>
       </c>
-      <c r="K27" t="s">
+      <c r="N27" t="s">
         <v>640</v>
-      </c>
-      <c r="L27" t="s">
-        <v>641</v>
-      </c>
-      <c r="M27" t="s">
-        <v>642</v>
-      </c>
-      <c r="N27" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11777,39 +11729,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
+        <v>642</v>
+      </c>
+      <c r="J28" t="s">
+        <v>643</v>
+      </c>
+      <c r="K28" t="s">
+        <v>644</v>
+      </c>
+      <c r="L28" t="s">
         <v>645</v>
       </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
         <v>646</v>
       </c>
-      <c r="K28" t="s">
+      <c r="N28" t="s">
         <v>647</v>
-      </c>
-      <c r="L28" t="s">
-        <v>648</v>
-      </c>
-      <c r="M28" t="s">
-        <v>649</v>
-      </c>
-      <c r="N28" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11821,39 +11773,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
+        <v>649</v>
+      </c>
+      <c r="J29" t="s">
+        <v>650</v>
+      </c>
+      <c r="K29" t="s">
+        <v>651</v>
+      </c>
+      <c r="L29" t="s">
         <v>652</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>653</v>
       </c>
-      <c r="K29" t="s">
+      <c r="N29" t="s">
         <v>654</v>
-      </c>
-      <c r="L29" t="s">
-        <v>655</v>
-      </c>
-      <c r="M29" t="s">
-        <v>656</v>
-      </c>
-      <c r="N29" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11865,39 +11817,39 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
+        <v>656</v>
+      </c>
+      <c r="J30" t="s">
+        <v>657</v>
+      </c>
+      <c r="K30" t="s">
+        <v>658</v>
+      </c>
+      <c r="L30" t="s">
         <v>659</v>
       </c>
-      <c r="J30" t="s">
+      <c r="M30" t="s">
         <v>660</v>
       </c>
-      <c r="K30" t="s">
+      <c r="N30" t="s">
         <v>661</v>
-      </c>
-      <c r="L30" t="s">
-        <v>662</v>
-      </c>
-      <c r="M30" t="s">
-        <v>663</v>
-      </c>
-      <c r="N30" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F31" t="s">
         <v>290</v>
@@ -11909,22 +11861,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
+        <v>663</v>
+      </c>
+      <c r="J31" t="s">
+        <v>664</v>
+      </c>
+      <c r="K31" t="s">
+        <v>665</v>
+      </c>
+      <c r="L31" t="s">
         <v>666</v>
       </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>667</v>
       </c>
-      <c r="K31" t="s">
+      <c r="N31" t="s">
         <v>668</v>
-      </c>
-      <c r="L31" t="s">
-        <v>669</v>
-      </c>
-      <c r="M31" t="s">
-        <v>670</v>
-      </c>
-      <c r="N31" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11932,16 +11884,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F32" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11950,22 +11902,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
+        <v>671</v>
+      </c>
+      <c r="J32" t="s">
+        <v>672</v>
+      </c>
+      <c r="K32" t="s">
+        <v>673</v>
+      </c>
+      <c r="L32" t="s">
         <v>674</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>675</v>
       </c>
-      <c r="K32" t="s">
+      <c r="N32" t="s">
         <v>676</v>
-      </c>
-      <c r="L32" t="s">
-        <v>677</v>
-      </c>
-      <c r="M32" t="s">
-        <v>678</v>
-      </c>
-      <c r="N32" t="s">
-        <v>679</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -786,7 +786,7 @@
     <t>Shiba_ThinRed.png</t>
   </si>
   <si>
-    <t>Sunglasses_Blade.png</t>
+    <t>v2\Eyewear\Sunglasses_Blade.png</t>
   </si>
   <si>
     <t>胡渣赤柴</t>
@@ -795,7 +795,7 @@
     <t>Shiba_UnshavenRed.png</t>
   </si>
   <si>
-    <t>Monocle_black.png</t>
+    <t>v2\Eyewear\Monocle_black.png</t>
   </si>
   <si>
     <t>Head_Unshaven.png</t>
@@ -807,7 +807,7 @@
     <t>Shiba_ThinBlack.png</t>
   </si>
   <si>
-    <t>EyePatch.png</t>
+    <t>v2\Eyewear\EyePatch.png</t>
   </si>
   <si>
     <t>胡渣黑柴</t>
@@ -816,7 +816,7 @@
     <t>Shiba_UnshavenBlack.png</t>
   </si>
   <si>
-    <t>Monocle_golden.png</t>
+    <t>v2\Eyewear\Monocle_golden.png</t>
   </si>
   <si>
     <t>瘦白柴</t>
@@ -831,7 +831,7 @@
     <t>Shiba_UnshavenCream.png</t>
   </si>
   <si>
-    <t>3DGlasses.png</t>
+    <t>v2\Eyewear\3DGlasses.png</t>
   </si>
   <si>
     <t>瘦芝麻柴</t>
@@ -7496,13 +7496,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
-    <col min="4" max="8" width="21.9166666666667" customWidth="1"/>
+    <col min="4" max="7" width="21.9166666666667" customWidth="1"/>
+    <col min="8" max="8" width="30.25" customWidth="1"/>
     <col min="9" max="9" width="15.5" customWidth="1"/>
     <col min="10" max="10" width="16.5833333333333" customWidth="1"/>
     <col min="11" max="11" width="18.5" customWidth="1"/>
@@ -9015,6 +9016,24 @@
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="2:25">
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="2:25">
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="8:8">
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="8:8">
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="8:8">
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="8:8">
+      <c r="H36" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="1022">
   <si>
     <t>Dog</t>
   </si>
@@ -696,7 +696,7 @@
     <t>使眼色</t>
   </si>
   <si>
-    <t>赤柴原色</t>
+    <t>原色赤柴</t>
   </si>
   <si>
     <t>Shiba_Red.png</t>
@@ -708,6 +708,9 @@
     <t>Eyes_Cute.png</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>v3\Shiba\Red</t>
   </si>
   <si>
@@ -786,67 +789,172 @@
     <t>Shiba_ThinRed.png</t>
   </si>
   <si>
+    <t>电玩赤柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenRed.png</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\PixelDealShades.png</t>
+  </si>
+  <si>
+    <t>电竞黑柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>Head_Unshaven.png</t>
+  </si>
+  <si>
+    <t>电玩妹白柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>学者黑柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\Monocle_golden.png</t>
+  </si>
+  <si>
+    <t>贵族白柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\Monocle_black.png</t>
+  </si>
+  <si>
+    <t>贵族麻柴</t>
+  </si>
+  <si>
+    <t>Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>绅士赤柴</t>
+  </si>
+  <si>
+    <t>学长赤柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\NerdyGlasses_Black.png</t>
+  </si>
+  <si>
+    <t>书呆子黑柴</t>
+  </si>
+  <si>
+    <t>学妹白柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\NerdyGlasses_DizzyRed.png</t>
+  </si>
+  <si>
+    <t>阿呆胡麻柴</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\NerdyGlasses_SillyLilac.png</t>
+  </si>
+  <si>
+    <t>王牌赤柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\AviatorSunglasses_Silver.png</t>
+  </si>
+  <si>
+    <t>机车黑柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\AviatorSunglasses_Black.png</t>
+  </si>
+  <si>
+    <t>名媛白柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\AviatorSunglasses_RoseGold.png</t>
+  </si>
+  <si>
+    <t>五星上将胡麻柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\FiveStarAviators.png</t>
+  </si>
+  <si>
+    <t>五星上将黑柴</t>
+  </si>
+  <si>
+    <t>硬汉白柴</t>
+  </si>
+  <si>
+    <t>经理赤柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\BrowlineGlasses_Black.png</t>
+  </si>
+  <si>
+    <t>总监黑柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\BrowlineGlasses_Tortoiseshell.png</t>
+  </si>
+  <si>
+    <t>秘书白柴</t>
+  </si>
+  <si>
+    <t>资深顾问胡麻柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\BrowlineGlasses_WalnutWood.png</t>
+  </si>
+  <si>
+    <t>法务白柴</t>
+  </si>
+  <si>
+    <t>潮玩赤柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\3DGlasses.png</t>
+  </si>
+  <si>
+    <t>影迷白柴</t>
+  </si>
+  <si>
+    <t>潮玩胡麻柴</t>
+  </si>
+  <si>
+    <t>掠夺者赤柴</t>
+  </si>
+  <si>
+    <t>v2\Eyewear\EyePatch.png</t>
+  </si>
+  <si>
+    <t>独眼黑柴</t>
+  </si>
+  <si>
+    <t>海盗胡麻柴</t>
+  </si>
+  <si>
+    <t>赛博赤柴</t>
+  </si>
+  <si>
     <t>v2\Eyewear\Sunglasses_Blade.png</t>
   </si>
   <si>
-    <t>胡渣赤柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>v2\Eyewear\Monocle_black.png</t>
-  </si>
-  <si>
-    <t>Head_Unshaven.png</t>
-  </si>
-  <si>
-    <t>瘦黑柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinBlack.png</t>
-  </si>
-  <si>
-    <t>v2\Eyewear\EyePatch.png</t>
-  </si>
-  <si>
-    <t>胡渣黑柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenBlack.png</t>
-  </si>
-  <si>
-    <t>v2\Eyewear\Monocle_golden.png</t>
-  </si>
-  <si>
-    <t>瘦白柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinCream.png</t>
-  </si>
-  <si>
-    <t>胡渣白柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenCream.png</t>
-  </si>
-  <si>
-    <t>v2\Eyewear\3DGlasses.png</t>
-  </si>
-  <si>
-    <t>瘦芝麻柴</t>
-  </si>
-  <si>
-    <t>Shiba_ThinSesame.png</t>
-  </si>
-  <si>
-    <t>胡渣胡麻柴</t>
-  </si>
-  <si>
-    <t>Shiba_UnshavenSesame.png</t>
-  </si>
-  <si>
-    <t>新狗狗 1013</t>
+    <t>黑客黑柴</t>
+  </si>
+  <si>
+    <t>酷妹白柴</t>
+  </si>
+  <si>
+    <t>夜客胡麻柴</t>
   </si>
   <si>
     <t>Name</t>
@@ -1261,9 +1369,6 @@
   </si>
   <si>
     <t>Casual</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Focused</t>
@@ -3627,7 +3732,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3645,9 +3750,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4598,31 +4700,31 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>677</v>
+        <v>712</v>
       </c>
       <c r="C1" t="s">
-        <v>678</v>
+        <v>713</v>
       </c>
       <c r="D1" t="s">
-        <v>679</v>
+        <v>714</v>
       </c>
       <c r="E1" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="F1" t="s">
-        <v>680</v>
+        <v>715</v>
       </c>
       <c r="G1" t="s">
-        <v>681</v>
+        <v>716</v>
       </c>
       <c r="H1" t="s">
-        <v>682</v>
+        <v>717</v>
       </c>
       <c r="I1" t="s">
-        <v>683</v>
+        <v>718</v>
       </c>
       <c r="J1" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4639,19 +4741,19 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="F2" t="s">
-        <v>684</v>
+        <v>719</v>
       </c>
       <c r="G2" t="s">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="J2" t="s">
         <v>109</v>
@@ -4662,31 +4764,31 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>686</v>
+        <v>721</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>688</v>
+        <v>723</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>689</v>
+        <v>724</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>690</v>
+        <v>725</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>691</v>
+        <v>726</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>692</v>
+        <v>727</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>693</v>
+        <v>728</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>694</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4694,1471 +4796,1471 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>695</v>
+        <v>730</v>
       </c>
       <c r="C4" t="s">
-        <v>696</v>
+        <v>731</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="E4" t="s">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="F4" t="s">
-        <v>697</v>
+        <v>732</v>
       </c>
       <c r="G4" t="s">
-        <v>698</v>
+        <v>733</v>
       </c>
       <c r="H4" t="s">
-        <v>699</v>
+        <v>734</v>
       </c>
       <c r="I4" t="s">
-        <v>700</v>
+        <v>735</v>
       </c>
       <c r="J4" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>701</v>
+        <v>736</v>
       </c>
       <c r="D5" t="s">
-        <v>702</v>
+        <v>737</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>703</v>
+        <v>738</v>
       </c>
       <c r="G5" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H5" t="s">
-        <v>705</v>
+        <v>740</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>706</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D6" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G6" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H6" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>711</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>712</v>
+        <v>747</v>
       </c>
       <c r="D7" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>703</v>
+        <v>738</v>
       </c>
       <c r="G7" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H7" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>715</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>716</v>
+        <v>751</v>
       </c>
       <c r="D8" t="s">
-        <v>717</v>
+        <v>752</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>703</v>
+        <v>738</v>
       </c>
       <c r="G8" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H8" t="s">
-        <v>718</v>
+        <v>753</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>719</v>
+        <v>754</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>720</v>
+        <v>755</v>
       </c>
       <c r="D9" t="s">
-        <v>721</v>
+        <v>756</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G9" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H9" t="s">
-        <v>722</v>
+        <v>757</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>723</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>724</v>
+        <v>759</v>
       </c>
       <c r="D10" t="s">
-        <v>725</v>
+        <v>760</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G10" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H10" t="s">
-        <v>727</v>
+        <v>762</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>728</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>729</v>
+        <v>764</v>
       </c>
       <c r="D11" t="s">
-        <v>730</v>
+        <v>765</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G11" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H11" t="s">
-        <v>731</v>
+        <v>766</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>732</v>
+        <v>767</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>733</v>
+        <v>768</v>
       </c>
       <c r="D12" t="s">
-        <v>734</v>
+        <v>769</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G12" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H12" t="s">
-        <v>735</v>
+        <v>770</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>736</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>737</v>
+        <v>772</v>
       </c>
       <c r="D13" t="s">
-        <v>738</v>
+        <v>773</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G13" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H13" t="s">
-        <v>739</v>
+        <v>774</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>740</v>
+        <v>775</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>741</v>
+        <v>776</v>
       </c>
       <c r="D14" t="s">
-        <v>742</v>
+        <v>777</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G14" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H14" t="s">
-        <v>743</v>
+        <v>778</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>744</v>
+        <v>779</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>745</v>
+        <v>780</v>
       </c>
       <c r="D15" t="s">
-        <v>746</v>
+        <v>781</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G15" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H15" t="s">
-        <v>747</v>
+        <v>782</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>748</v>
+        <v>783</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>749</v>
+        <v>784</v>
       </c>
       <c r="D16" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G16" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H16" t="s">
-        <v>751</v>
+        <v>786</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="D17" t="s">
-        <v>754</v>
+        <v>789</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G17" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H17" t="s">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="D18" t="s">
-        <v>758</v>
+        <v>793</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G18" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H18" t="s">
-        <v>759</v>
+        <v>794</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>760</v>
+        <v>795</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>546</v>
+        <v>581</v>
       </c>
       <c r="D19" t="s">
-        <v>761</v>
+        <v>796</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G19" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H19" t="s">
-        <v>762</v>
+        <v>797</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="D20" t="s">
-        <v>764</v>
+        <v>799</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G20" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H20" t="s">
-        <v>765</v>
+        <v>800</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>766</v>
+        <v>801</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="D21" t="s">
-        <v>767</v>
+        <v>802</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G21" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H21" t="s">
-        <v>768</v>
+        <v>803</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="D22" t="s">
-        <v>770</v>
+        <v>805</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G22" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H22" t="s">
-        <v>771</v>
+        <v>806</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>772</v>
+        <v>807</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="D23" t="s">
-        <v>773</v>
+        <v>808</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G23" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H23" t="s">
-        <v>774</v>
+        <v>809</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>775</v>
+        <v>810</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>586</v>
+        <v>621</v>
       </c>
       <c r="D24" t="s">
-        <v>776</v>
+        <v>811</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G24" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H24" t="s">
-        <v>777</v>
+        <v>812</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>778</v>
+        <v>813</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>594</v>
+        <v>629</v>
       </c>
       <c r="D25" t="s">
-        <v>779</v>
+        <v>814</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G25" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H25" t="s">
-        <v>780</v>
+        <v>815</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>781</v>
+        <v>816</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>782</v>
+        <v>817</v>
       </c>
       <c r="D26" t="s">
-        <v>783</v>
+        <v>818</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G26" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H26" t="s">
-        <v>784</v>
+        <v>819</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>785</v>
+        <v>820</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>786</v>
+        <v>821</v>
       </c>
       <c r="D27" t="s">
-        <v>787</v>
+        <v>822</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G27" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H27" t="s">
-        <v>788</v>
+        <v>823</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>789</v>
+        <v>824</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>790</v>
+        <v>825</v>
       </c>
       <c r="D28" t="s">
-        <v>791</v>
+        <v>826</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G28" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H28" t="s">
-        <v>792</v>
+        <v>827</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>793</v>
+        <v>828</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="D29" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G29" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H29" t="s">
-        <v>796</v>
+        <v>831</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>797</v>
+        <v>832</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>798</v>
+        <v>833</v>
       </c>
       <c r="D30" t="s">
-        <v>799</v>
+        <v>834</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G30" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H30" t="s">
-        <v>800</v>
+        <v>835</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>801</v>
+        <v>836</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>802</v>
+        <v>837</v>
       </c>
       <c r="D31" t="s">
-        <v>803</v>
+        <v>838</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G31" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H31" t="s">
-        <v>804</v>
+        <v>839</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>805</v>
+        <v>840</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>806</v>
+        <v>841</v>
       </c>
       <c r="D32" t="s">
-        <v>807</v>
+        <v>842</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G32" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H32" t="s">
-        <v>808</v>
+        <v>843</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>809</v>
+        <v>844</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>810</v>
+        <v>845</v>
       </c>
       <c r="D33" t="s">
-        <v>811</v>
+        <v>846</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G33" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H33" t="s">
-        <v>812</v>
+        <v>847</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>813</v>
+        <v>848</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>814</v>
+        <v>849</v>
       </c>
       <c r="D34" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G34" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H34" t="s">
-        <v>816</v>
+        <v>851</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>817</v>
+        <v>852</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>818</v>
+        <v>853</v>
       </c>
       <c r="D35" t="s">
-        <v>819</v>
+        <v>854</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G35" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H35" t="s">
-        <v>820</v>
+        <v>855</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>821</v>
+        <v>856</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>822</v>
+        <v>857</v>
       </c>
       <c r="D36" t="s">
-        <v>823</v>
+        <v>858</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G36" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H36" t="s">
-        <v>824</v>
+        <v>859</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>825</v>
+        <v>860</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>826</v>
+        <v>861</v>
       </c>
       <c r="D37" t="s">
-        <v>827</v>
+        <v>862</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G37" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H37" t="s">
-        <v>828</v>
+        <v>863</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>829</v>
+        <v>864</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>830</v>
+        <v>865</v>
       </c>
       <c r="D38" t="s">
-        <v>831</v>
+        <v>866</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G38" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H38" t="s">
-        <v>832</v>
+        <v>867</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>833</v>
+        <v>868</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>834</v>
+        <v>869</v>
       </c>
       <c r="D39" t="s">
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G39" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H39" t="s">
-        <v>836</v>
+        <v>871</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>837</v>
+        <v>872</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>838</v>
+        <v>873</v>
       </c>
       <c r="D40" t="s">
-        <v>839</v>
+        <v>874</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G40" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H40" t="s">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>841</v>
+        <v>876</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>842</v>
+        <v>877</v>
       </c>
       <c r="D41" t="s">
-        <v>843</v>
+        <v>878</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G41" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H41" t="s">
-        <v>844</v>
+        <v>879</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>845</v>
+        <v>880</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>846</v>
+        <v>881</v>
       </c>
       <c r="D42" t="s">
-        <v>847</v>
+        <v>882</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G42" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H42" t="s">
-        <v>848</v>
+        <v>883</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>849</v>
+        <v>884</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>850</v>
+        <v>885</v>
       </c>
       <c r="D43" t="s">
-        <v>851</v>
+        <v>886</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G43" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H43" t="s">
-        <v>852</v>
+        <v>887</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>853</v>
+        <v>888</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>854</v>
+        <v>889</v>
       </c>
       <c r="D44" t="s">
-        <v>855</v>
+        <v>890</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G44" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H44" t="s">
-        <v>856</v>
+        <v>891</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>857</v>
+        <v>892</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>858</v>
+        <v>893</v>
       </c>
       <c r="D45" t="s">
-        <v>859</v>
+        <v>894</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G45" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H45" t="s">
-        <v>860</v>
+        <v>895</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>861</v>
+        <v>896</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>862</v>
+        <v>897</v>
       </c>
       <c r="D46" t="s">
-        <v>863</v>
+        <v>898</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G46" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H46" t="s">
-        <v>864</v>
+        <v>899</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>865</v>
+        <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>866</v>
+        <v>901</v>
       </c>
       <c r="D47" t="s">
-        <v>867</v>
+        <v>902</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G47" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H47" t="s">
-        <v>868</v>
+        <v>903</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>869</v>
+        <v>904</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>870</v>
+        <v>905</v>
       </c>
       <c r="D48" t="s">
-        <v>871</v>
+        <v>906</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G48" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H48" t="s">
-        <v>872</v>
+        <v>907</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>873</v>
+        <v>908</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>874</v>
+        <v>909</v>
       </c>
       <c r="D49" t="s">
-        <v>875</v>
+        <v>910</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G49" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H49" t="s">
-        <v>876</v>
+        <v>911</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>877</v>
+        <v>912</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6166,28 +6268,28 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>878</v>
+        <v>913</v>
       </c>
       <c r="D50" t="s">
-        <v>879</v>
+        <v>914</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G50" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H50" t="s">
-        <v>880</v>
+        <v>915</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>881</v>
+        <v>916</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6195,28 +6297,28 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>882</v>
+        <v>917</v>
       </c>
       <c r="D51" t="s">
-        <v>883</v>
+        <v>918</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G51" t="s">
-        <v>884</v>
+        <v>919</v>
       </c>
       <c r="H51" t="s">
-        <v>885</v>
+        <v>920</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>886</v>
+        <v>921</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6224,28 +6326,28 @@
         <v>1051</v>
       </c>
       <c r="C52" t="s">
-        <v>887</v>
+        <v>922</v>
       </c>
       <c r="D52" t="s">
-        <v>888</v>
+        <v>923</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G52" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H52" t="s">
-        <v>890</v>
+        <v>925</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>891</v>
+        <v>926</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6253,28 +6355,28 @@
         <v>1052</v>
       </c>
       <c r="C53" t="s">
-        <v>892</v>
+        <v>927</v>
       </c>
       <c r="D53" t="s">
-        <v>893</v>
+        <v>928</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G53" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H53" t="s">
-        <v>894</v>
+        <v>929</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6282,28 +6384,28 @@
         <v>1053</v>
       </c>
       <c r="C54" t="s">
-        <v>896</v>
+        <v>931</v>
       </c>
       <c r="D54" t="s">
-        <v>897</v>
+        <v>932</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G54" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H54" t="s">
-        <v>898</v>
+        <v>933</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>899</v>
+        <v>934</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6311,28 +6413,28 @@
         <v>1054</v>
       </c>
       <c r="C55" t="s">
-        <v>900</v>
+        <v>935</v>
       </c>
       <c r="D55" t="s">
-        <v>901</v>
+        <v>936</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G55" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H55" t="s">
-        <v>902</v>
+        <v>937</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>903</v>
+        <v>938</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6340,28 +6442,28 @@
         <v>1055</v>
       </c>
       <c r="C56" t="s">
-        <v>904</v>
+        <v>939</v>
       </c>
       <c r="D56" t="s">
-        <v>905</v>
+        <v>940</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G56" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H56" t="s">
-        <v>906</v>
+        <v>941</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>907</v>
+        <v>942</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6369,28 +6471,28 @@
         <v>1056</v>
       </c>
       <c r="C57" t="s">
-        <v>908</v>
+        <v>943</v>
       </c>
       <c r="D57" t="s">
-        <v>909</v>
+        <v>944</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>703</v>
+        <v>738</v>
       </c>
       <c r="G57" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H57" t="s">
-        <v>910</v>
+        <v>945</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>911</v>
+        <v>946</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -6398,28 +6500,28 @@
         <v>1057</v>
       </c>
       <c r="C58" t="s">
-        <v>912</v>
+        <v>947</v>
       </c>
       <c r="D58" t="s">
-        <v>913</v>
+        <v>948</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G58" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H58" t="s">
-        <v>914</v>
+        <v>949</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>915</v>
+        <v>950</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -6427,28 +6529,28 @@
         <v>1058</v>
       </c>
       <c r="C59" t="s">
-        <v>916</v>
+        <v>951</v>
       </c>
       <c r="D59" t="s">
-        <v>917</v>
+        <v>952</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G59" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H59" t="s">
-        <v>918</v>
+        <v>953</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>919</v>
+        <v>954</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -6456,28 +6558,28 @@
         <v>1059</v>
       </c>
       <c r="C60" t="s">
-        <v>920</v>
+        <v>955</v>
       </c>
       <c r="D60" t="s">
-        <v>921</v>
+        <v>956</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G60" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H60" t="s">
-        <v>922</v>
+        <v>957</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>923</v>
+        <v>958</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -6485,28 +6587,28 @@
         <v>1060</v>
       </c>
       <c r="C61" t="s">
+        <v>959</v>
+      </c>
+      <c r="D61" t="s">
+        <v>960</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
         <v>924</v>
       </c>
-      <c r="D61" t="s">
-        <v>925</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>889</v>
-      </c>
       <c r="G61" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H61" t="s">
-        <v>926</v>
+        <v>961</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>927</v>
+        <v>962</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -6514,92 +6616,92 @@
         <v>1061</v>
       </c>
       <c r="C62" t="s">
-        <v>928</v>
+        <v>963</v>
       </c>
       <c r="D62" t="s">
-        <v>929</v>
+        <v>964</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G62" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="H62" t="s">
-        <v>930</v>
+        <v>965</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>931</v>
+        <v>966</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B63">
         <v>1062</v>
       </c>
       <c r="C63" t="s">
-        <v>932</v>
+        <v>967</v>
       </c>
       <c r="D63" t="s">
-        <v>933</v>
+        <v>968</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G63" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H63" t="s">
-        <v>934</v>
+        <v>969</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>935</v>
+        <v>970</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B64">
         <v>1063</v>
       </c>
       <c r="C64" t="s">
-        <v>936</v>
+        <v>971</v>
       </c>
       <c r="D64" t="s">
-        <v>937</v>
+        <v>972</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="G64" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="H64" t="s">
-        <v>938</v>
+        <v>973</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>939</v>
+        <v>974</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -6607,28 +6709,28 @@
         <v>1064</v>
       </c>
       <c r="C65" t="s">
-        <v>940</v>
+        <v>975</v>
       </c>
       <c r="D65" t="s">
-        <v>941</v>
+        <v>976</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="G65" t="s">
-        <v>884</v>
+        <v>919</v>
       </c>
       <c r="H65" t="s">
-        <v>942</v>
+        <v>977</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>943</v>
+        <v>978</v>
       </c>
     </row>
   </sheetData>
@@ -6663,25 +6765,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>944</v>
+        <v>979</v>
       </c>
       <c r="C1" t="s">
-        <v>945</v>
+        <v>980</v>
       </c>
       <c r="D1" t="s">
-        <v>946</v>
+        <v>981</v>
       </c>
       <c r="E1" t="s">
-        <v>947</v>
+        <v>982</v>
       </c>
       <c r="F1" t="s">
-        <v>948</v>
+        <v>983</v>
       </c>
       <c r="G1" t="s">
-        <v>949</v>
+        <v>984</v>
       </c>
       <c r="H1" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6695,7 +6797,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6715,28 +6817,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>950</v>
+        <v>985</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>951</v>
+        <v>986</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>952</v>
+        <v>987</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>953</v>
+        <v>988</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>954</v>
+        <v>989</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>955</v>
+        <v>990</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>956</v>
+        <v>991</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>957</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -6744,39 +6846,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>958</v>
+        <v>993</v>
       </c>
       <c r="C4" t="s">
-        <v>951</v>
+        <v>986</v>
       </c>
       <c r="D4" t="s">
-        <v>959</v>
+        <v>994</v>
       </c>
       <c r="E4" t="s">
-        <v>960</v>
+        <v>995</v>
       </c>
       <c r="F4" t="s">
-        <v>961</v>
+        <v>996</v>
       </c>
       <c r="G4" t="s">
-        <v>962</v>
+        <v>997</v>
       </c>
       <c r="H4" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>963</v>
+        <v>998</v>
       </c>
       <c r="C5" t="s">
-        <v>964</v>
+        <v>999</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -6794,18 +6896,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>965</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6823,18 +6925,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>968</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B7" t="s">
-        <v>969</v>
+        <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>970</v>
+        <v>1005</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6852,18 +6954,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>971</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B8" t="s">
-        <v>972</v>
+        <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>973</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6881,18 +6983,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B9" t="s">
-        <v>975</v>
+        <v>1010</v>
       </c>
       <c r="C9" t="s">
-        <v>976</v>
+        <v>1011</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6910,18 +7012,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>977</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B10" t="s">
-        <v>978</v>
+        <v>1013</v>
       </c>
       <c r="C10" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6939,18 +7041,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>980</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B11" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="C11" t="s">
-        <v>982</v>
+        <v>1017</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6968,18 +7070,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>983</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B12" t="s">
-        <v>984</v>
+        <v>1019</v>
       </c>
       <c r="C12" t="s">
-        <v>985</v>
+        <v>1020</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6997,7 +7099,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>986</v>
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
@@ -7357,7 +7459,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>152</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -7372,7 +7474,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7"/>
+      <c r="A2" s="6"/>
       <c r="B2" s="5" t="s">
         <v>153</v>
       </c>
@@ -7470,22 +7572,22 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8">
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="9"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8">
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="9"/>
+      <c r="H15" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7496,7 +7598,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -7686,7 +7788,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="1" t="s">
         <v>196</v>
       </c>
     </row>
@@ -7783,54 +7885,56 @@
       <c r="G5" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>223</v>
+      </c>
       <c r="I5" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y5" s="2"/>
     </row>
@@ -7839,10 +7943,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>221</v>
@@ -7853,54 +7957,56 @@
       <c r="G6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>223</v>
+      </c>
       <c r="I6" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y6" s="2"/>
     </row>
@@ -7909,10 +8015,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>221</v>
@@ -7923,54 +8029,56 @@
       <c r="G7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>223</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y7" s="2"/>
     </row>
@@ -7979,10 +8087,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>221</v>
@@ -7993,54 +8101,56 @@
       <c r="G8" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>223</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y8" s="2"/>
     </row>
@@ -8049,70 +8159,70 @@
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>221</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y9" s="2"/>
     </row>
@@ -8139,52 +8249,52 @@
         <v>252</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y10" s="2"/>
     </row>
@@ -8193,70 +8303,70 @@
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>221</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y11" s="2"/>
     </row>
@@ -8265,70 +8375,70 @@
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>221</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y12" s="2"/>
     </row>
@@ -8337,70 +8447,70 @@
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>221</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y13" s="2"/>
     </row>
@@ -8409,10 +8519,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>221</v>
@@ -8424,55 +8534,55 @@
         <v>183</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y14" s="2"/>
     </row>
@@ -8481,10 +8591,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>221</v>
@@ -8496,55 +8606,55 @@
         <v>183</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y15" s="2"/>
     </row>
@@ -8553,10 +8663,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>221</v>
@@ -8568,55 +8678,55 @@
         <v>183</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y16" s="2"/>
     </row>
@@ -8625,7 +8735,7 @@
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>220</v>
@@ -8640,400 +8750,1761 @@
         <v>183</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>221</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>222</v>
       </c>
       <c r="T17" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="2:25">
+      <c r="B18" s="2">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R18" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="S18" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="U18" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="X17" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="Y17" s="2"/>
-    </row>
-    <row r="18" spans="2:25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
+      <c r="X18" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="19" spans="2:25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
+      <c r="B19" s="2">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="20" spans="2:25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
+      <c r="B20" s="2">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="21" spans="2:25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
+      <c r="B21" s="2">
+        <v>1017</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="22" spans="2:25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
+      <c r="B22" s="2">
+        <v>1018</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="23" spans="2:25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
+      <c r="B23" s="2">
+        <v>1019</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="24" spans="2:25">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
+      <c r="B24" s="2">
+        <v>1020</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="25" spans="2:25">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
+      <c r="B25" s="2">
+        <v>1021</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="26" spans="2:25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
+      <c r="B26" s="2">
+        <v>1022</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="27" spans="2:25">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
+      <c r="B27" s="2">
+        <v>1023</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="28" spans="2:25">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
+      <c r="B28" s="2">
+        <v>1024</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="29" spans="2:25">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
+      <c r="B29" s="2">
+        <v>1025</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="30" spans="2:25">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
+      <c r="B30" s="2">
+        <v>1026</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="31" spans="2:25">
-      <c r="H31" s="2"/>
+      <c r="B31">
+        <v>1027</v>
+      </c>
+      <c r="C31" t="s">
+        <v>292</v>
+      </c>
+      <c r="D31" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F31" t="s">
+        <v>222</v>
+      </c>
+      <c r="G31" t="s">
+        <v>183</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I31" t="s">
+        <v>244</v>
+      </c>
+      <c r="J31" t="s">
+        <v>255</v>
+      </c>
+      <c r="K31" t="s">
+        <v>226</v>
+      </c>
+      <c r="L31" t="s">
+        <v>227</v>
+      </c>
+      <c r="M31" t="s">
+        <v>228</v>
+      </c>
+      <c r="N31" t="s">
+        <v>229</v>
+      </c>
+      <c r="O31" t="s">
+        <v>230</v>
+      </c>
+      <c r="P31" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>221</v>
+      </c>
+      <c r="R31" t="s">
+        <v>232</v>
+      </c>
+      <c r="S31" t="s">
+        <v>222</v>
+      </c>
+      <c r="T31" t="s">
+        <v>233</v>
+      </c>
+      <c r="U31" t="s">
+        <v>234</v>
+      </c>
+      <c r="V31" t="s">
+        <v>235</v>
+      </c>
+      <c r="W31" t="s">
+        <v>236</v>
+      </c>
+      <c r="X31" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="32" spans="2:25">
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="8:8">
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="8:8">
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="8:8">
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="8:8">
-      <c r="H36" s="2"/>
+      <c r="B32">
+        <v>1028</v>
+      </c>
+      <c r="C32" t="s">
+        <v>293</v>
+      </c>
+      <c r="D32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" t="s">
+        <v>221</v>
+      </c>
+      <c r="F32" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I32" t="s">
+        <v>224</v>
+      </c>
+      <c r="J32" t="s">
+        <v>225</v>
+      </c>
+      <c r="K32" t="s">
+        <v>226</v>
+      </c>
+      <c r="L32" t="s">
+        <v>227</v>
+      </c>
+      <c r="M32" t="s">
+        <v>228</v>
+      </c>
+      <c r="N32" t="s">
+        <v>229</v>
+      </c>
+      <c r="O32" t="s">
+        <v>230</v>
+      </c>
+      <c r="P32" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>221</v>
+      </c>
+      <c r="R32" t="s">
+        <v>232</v>
+      </c>
+      <c r="S32" t="s">
+        <v>222</v>
+      </c>
+      <c r="T32" t="s">
+        <v>233</v>
+      </c>
+      <c r="U32" t="s">
+        <v>234</v>
+      </c>
+      <c r="V32" t="s">
+        <v>235</v>
+      </c>
+      <c r="W32" t="s">
+        <v>236</v>
+      </c>
+      <c r="X32" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24">
+      <c r="B33">
+        <v>1029</v>
+      </c>
+      <c r="C33" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" t="s">
+        <v>221</v>
+      </c>
+      <c r="F33" t="s">
+        <v>222</v>
+      </c>
+      <c r="G33" t="s">
+        <v>183</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I33" t="s">
+        <v>244</v>
+      </c>
+      <c r="J33" t="s">
+        <v>241</v>
+      </c>
+      <c r="K33" t="s">
+        <v>226</v>
+      </c>
+      <c r="L33" t="s">
+        <v>227</v>
+      </c>
+      <c r="M33" t="s">
+        <v>228</v>
+      </c>
+      <c r="N33" t="s">
+        <v>229</v>
+      </c>
+      <c r="O33" t="s">
+        <v>230</v>
+      </c>
+      <c r="P33" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>221</v>
+      </c>
+      <c r="R33" t="s">
+        <v>232</v>
+      </c>
+      <c r="S33" t="s">
+        <v>222</v>
+      </c>
+      <c r="T33" t="s">
+        <v>233</v>
+      </c>
+      <c r="U33" t="s">
+        <v>234</v>
+      </c>
+      <c r="V33" t="s">
+        <v>235</v>
+      </c>
+      <c r="W33" t="s">
+        <v>236</v>
+      </c>
+      <c r="X33" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24">
+      <c r="B34">
+        <v>1030</v>
+      </c>
+      <c r="C34" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F34" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I34" t="s">
+        <v>247</v>
+      </c>
+      <c r="J34" t="s">
+        <v>241</v>
+      </c>
+      <c r="K34" t="s">
+        <v>226</v>
+      </c>
+      <c r="L34" t="s">
+        <v>227</v>
+      </c>
+      <c r="M34" t="s">
+        <v>228</v>
+      </c>
+      <c r="N34" t="s">
+        <v>229</v>
+      </c>
+      <c r="O34" t="s">
+        <v>230</v>
+      </c>
+      <c r="P34" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>221</v>
+      </c>
+      <c r="R34" t="s">
+        <v>232</v>
+      </c>
+      <c r="S34" t="s">
+        <v>222</v>
+      </c>
+      <c r="T34" t="s">
+        <v>233</v>
+      </c>
+      <c r="U34" t="s">
+        <v>234</v>
+      </c>
+      <c r="V34" t="s">
+        <v>235</v>
+      </c>
+      <c r="W34" t="s">
+        <v>236</v>
+      </c>
+      <c r="X34" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24">
+      <c r="B35">
+        <v>1031</v>
+      </c>
+      <c r="C35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" t="s">
+        <v>221</v>
+      </c>
+      <c r="F35" t="s">
+        <v>222</v>
+      </c>
+      <c r="G35" t="s">
+        <v>183</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I35" t="s">
+        <v>224</v>
+      </c>
+      <c r="J35" t="s">
+        <v>255</v>
+      </c>
+      <c r="K35" t="s">
+        <v>226</v>
+      </c>
+      <c r="L35" t="s">
+        <v>227</v>
+      </c>
+      <c r="M35" t="s">
+        <v>228</v>
+      </c>
+      <c r="N35" t="s">
+        <v>229</v>
+      </c>
+      <c r="O35" t="s">
+        <v>230</v>
+      </c>
+      <c r="P35" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>221</v>
+      </c>
+      <c r="R35" t="s">
+        <v>232</v>
+      </c>
+      <c r="S35" t="s">
+        <v>222</v>
+      </c>
+      <c r="T35" t="s">
+        <v>233</v>
+      </c>
+      <c r="U35" t="s">
+        <v>234</v>
+      </c>
+      <c r="V35" t="s">
+        <v>235</v>
+      </c>
+      <c r="W35" t="s">
+        <v>236</v>
+      </c>
+      <c r="X35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24">
+      <c r="B36">
+        <v>1032</v>
+      </c>
+      <c r="C36" t="s">
+        <v>299</v>
+      </c>
+      <c r="D36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" t="s">
+        <v>222</v>
+      </c>
+      <c r="G36" t="s">
+        <v>183</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I36" t="s">
+        <v>240</v>
+      </c>
+      <c r="J36" t="s">
+        <v>241</v>
+      </c>
+      <c r="K36" t="s">
+        <v>226</v>
+      </c>
+      <c r="L36" t="s">
+        <v>227</v>
+      </c>
+      <c r="M36" t="s">
+        <v>228</v>
+      </c>
+      <c r="N36" t="s">
+        <v>229</v>
+      </c>
+      <c r="O36" t="s">
+        <v>230</v>
+      </c>
+      <c r="P36" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>221</v>
+      </c>
+      <c r="R36" t="s">
+        <v>232</v>
+      </c>
+      <c r="S36" t="s">
+        <v>222</v>
+      </c>
+      <c r="T36" t="s">
+        <v>233</v>
+      </c>
+      <c r="U36" t="s">
+        <v>234</v>
+      </c>
+      <c r="V36" t="s">
+        <v>235</v>
+      </c>
+      <c r="W36" t="s">
+        <v>236</v>
+      </c>
+      <c r="X36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24">
+      <c r="B37">
+        <v>1033</v>
+      </c>
+      <c r="C37" t="s">
+        <v>300</v>
+      </c>
+      <c r="D37" t="s">
+        <v>246</v>
+      </c>
+      <c r="E37" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37" t="s">
+        <v>222</v>
+      </c>
+      <c r="G37" t="s">
+        <v>183</v>
+      </c>
+      <c r="H37" t="s">
+        <v>298</v>
+      </c>
+      <c r="I37" t="s">
+        <v>247</v>
+      </c>
+      <c r="J37" t="s">
+        <v>255</v>
+      </c>
+      <c r="K37" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" t="s">
+        <v>227</v>
+      </c>
+      <c r="M37" t="s">
+        <v>228</v>
+      </c>
+      <c r="N37" t="s">
+        <v>229</v>
+      </c>
+      <c r="O37" t="s">
+        <v>230</v>
+      </c>
+      <c r="P37" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>221</v>
+      </c>
+      <c r="R37" t="s">
+        <v>232</v>
+      </c>
+      <c r="S37" t="s">
+        <v>222</v>
+      </c>
+      <c r="T37" t="s">
+        <v>233</v>
+      </c>
+      <c r="U37" t="s">
+        <v>234</v>
+      </c>
+      <c r="V37" t="s">
+        <v>235</v>
+      </c>
+      <c r="W37" t="s">
+        <v>236</v>
+      </c>
+      <c r="X37" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="2:24">
+      <c r="B38">
+        <v>1034</v>
+      </c>
+      <c r="C38" t="s">
+        <v>301</v>
+      </c>
+      <c r="D38" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" t="s">
+        <v>221</v>
+      </c>
+      <c r="F38" t="s">
+        <v>222</v>
+      </c>
+      <c r="G38" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" t="s">
+        <v>302</v>
+      </c>
+      <c r="I38" t="s">
+        <v>224</v>
+      </c>
+      <c r="J38" t="s">
+        <v>225</v>
+      </c>
+      <c r="K38" t="s">
+        <v>226</v>
+      </c>
+      <c r="L38" t="s">
+        <v>227</v>
+      </c>
+      <c r="M38" t="s">
+        <v>228</v>
+      </c>
+      <c r="N38" t="s">
+        <v>229</v>
+      </c>
+      <c r="O38" t="s">
+        <v>230</v>
+      </c>
+      <c r="P38" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>221</v>
+      </c>
+      <c r="R38" t="s">
+        <v>232</v>
+      </c>
+      <c r="S38" t="s">
+        <v>222</v>
+      </c>
+      <c r="T38" t="s">
+        <v>233</v>
+      </c>
+      <c r="U38" t="s">
+        <v>234</v>
+      </c>
+      <c r="V38" t="s">
+        <v>235</v>
+      </c>
+      <c r="W38" t="s">
+        <v>236</v>
+      </c>
+      <c r="X38" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24">
+      <c r="B39">
+        <v>1035</v>
+      </c>
+      <c r="C39" t="s">
+        <v>303</v>
+      </c>
+      <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
+        <v>221</v>
+      </c>
+      <c r="F39" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" t="s">
+        <v>183</v>
+      </c>
+      <c r="H39" t="s">
+        <v>302</v>
+      </c>
+      <c r="I39" t="s">
+        <v>240</v>
+      </c>
+      <c r="J39" t="s">
+        <v>241</v>
+      </c>
+      <c r="K39" t="s">
+        <v>226</v>
+      </c>
+      <c r="L39" t="s">
+        <v>227</v>
+      </c>
+      <c r="M39" t="s">
+        <v>228</v>
+      </c>
+      <c r="N39" t="s">
+        <v>229</v>
+      </c>
+      <c r="O39" t="s">
+        <v>230</v>
+      </c>
+      <c r="P39" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>221</v>
+      </c>
+      <c r="R39" t="s">
+        <v>232</v>
+      </c>
+      <c r="S39" t="s">
+        <v>222</v>
+      </c>
+      <c r="T39" t="s">
+        <v>233</v>
+      </c>
+      <c r="U39" t="s">
+        <v>234</v>
+      </c>
+      <c r="V39" t="s">
+        <v>235</v>
+      </c>
+      <c r="W39" t="s">
+        <v>236</v>
+      </c>
+      <c r="X39" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="2:24">
+      <c r="B40">
+        <v>1036</v>
+      </c>
+      <c r="C40" t="s">
+        <v>304</v>
+      </c>
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
+        <v>221</v>
+      </c>
+      <c r="F40" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" t="s">
+        <v>183</v>
+      </c>
+      <c r="H40" t="s">
+        <v>302</v>
+      </c>
+      <c r="I40" t="s">
+        <v>244</v>
+      </c>
+      <c r="J40" t="s">
+        <v>241</v>
+      </c>
+      <c r="K40" t="s">
+        <v>226</v>
+      </c>
+      <c r="L40" t="s">
+        <v>227</v>
+      </c>
+      <c r="M40" t="s">
+        <v>228</v>
+      </c>
+      <c r="N40" t="s">
+        <v>229</v>
+      </c>
+      <c r="O40" t="s">
+        <v>230</v>
+      </c>
+      <c r="P40" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>221</v>
+      </c>
+      <c r="R40" t="s">
+        <v>232</v>
+      </c>
+      <c r="S40" t="s">
+        <v>222</v>
+      </c>
+      <c r="T40" t="s">
+        <v>233</v>
+      </c>
+      <c r="U40" t="s">
+        <v>234</v>
+      </c>
+      <c r="V40" t="s">
+        <v>235</v>
+      </c>
+      <c r="W40" t="s">
+        <v>236</v>
+      </c>
+      <c r="X40" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="2:24">
+      <c r="B41">
+        <v>1037</v>
+      </c>
+      <c r="C41" t="s">
+        <v>305</v>
+      </c>
+      <c r="D41" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" t="s">
+        <v>221</v>
+      </c>
+      <c r="F41" t="s">
+        <v>222</v>
+      </c>
+      <c r="G41" t="s">
+        <v>183</v>
+      </c>
+      <c r="H41" t="s">
+        <v>302</v>
+      </c>
+      <c r="I41" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41" t="s">
+        <v>255</v>
+      </c>
+      <c r="K41" t="s">
+        <v>226</v>
+      </c>
+      <c r="L41" t="s">
+        <v>227</v>
+      </c>
+      <c r="M41" t="s">
+        <v>228</v>
+      </c>
+      <c r="N41" t="s">
+        <v>229</v>
+      </c>
+      <c r="O41" t="s">
+        <v>230</v>
+      </c>
+      <c r="P41" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>221</v>
+      </c>
+      <c r="R41" t="s">
+        <v>232</v>
+      </c>
+      <c r="S41" t="s">
+        <v>222</v>
+      </c>
+      <c r="T41" t="s">
+        <v>233</v>
+      </c>
+      <c r="U41" t="s">
+        <v>234</v>
+      </c>
+      <c r="V41" t="s">
+        <v>235</v>
+      </c>
+      <c r="W41" t="s">
+        <v>236</v>
+      </c>
+      <c r="X41" t="s">
+        <v>237</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9061,16 +10532,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="E1" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="F1" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9084,7 +10555,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -9109,16 +10580,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="E4" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="F4" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9132,10 +10603,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="F5" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9143,16 +10614,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="F6" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9166,10 +10637,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9183,10 +10654,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="F8" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9200,10 +10671,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="F9" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9211,16 +10682,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="F10" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9234,10 +10705,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="F11" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9251,10 +10722,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="F12" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -9288,34 +10759,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="E1" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="G1" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="H1" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="I1" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="J1" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="K1" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="L1" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="M1" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="N1" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -9326,10 +10797,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="E2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -9363,13 +10834,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9380,40 +10851,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="E4" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="F4" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="G4" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="H4" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="I4" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="K4" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="L4" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="M4" t="s">
         <v>207</v>
       </c>
       <c r="N4" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -9436,13 +10907,13 @@
         <v>185</v>
       </c>
       <c r="K5" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L5" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M5" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9465,13 +10936,13 @@
         <v>185</v>
       </c>
       <c r="K6" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L6" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M6" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9494,13 +10965,13 @@
         <v>185</v>
       </c>
       <c r="K7" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L7" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M7" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9523,13 +10994,13 @@
         <v>185</v>
       </c>
       <c r="K8" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L8" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M8" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -9552,13 +11023,13 @@
         <v>185</v>
       </c>
       <c r="K9" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L9" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M9" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -9581,13 +11052,13 @@
         <v>185</v>
       </c>
       <c r="K10" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L10" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M10" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -9610,13 +11081,13 @@
         <v>186</v>
       </c>
       <c r="K11" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L11" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="M11" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -9639,13 +11110,13 @@
         <v>185</v>
       </c>
       <c r="K12" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="L12" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="M12" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -9653,10 +11124,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="G13" t="s">
         <v>187</v>
@@ -9668,16 +11139,16 @@
         <v>185</v>
       </c>
       <c r="K13" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L13" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="M13" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="N13" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -9685,10 +11156,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -9697,7 +11168,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -9705,10 +11176,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -9717,7 +11188,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -9725,10 +11196,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -9737,7 +11208,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -9745,19 +11216,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="F17" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="N17" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -9765,10 +11236,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -9777,7 +11248,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -9785,10 +11256,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -9797,7 +11268,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9805,10 +11276,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -9817,7 +11288,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9825,19 +11296,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="E21" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="F21" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="N21" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -9845,16 +11316,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -9862,10 +11333,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -9879,10 +11350,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -9896,10 +11367,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -9913,10 +11384,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -9930,10 +11401,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>365</v>
+        <v>401</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -9947,10 +11418,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -9964,10 +11435,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -9976,10 +11447,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="N29" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -9987,10 +11458,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -10004,10 +11475,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -10021,10 +11492,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -10033,10 +11504,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="N32" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -10044,10 +11515,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -10056,7 +11527,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -10092,31 +11563,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="D1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="E1" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="F1" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="G1" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="H1" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="I1" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="J1" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="K1" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -10142,10 +11613,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="I2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -10159,34 +11630,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -10197,31 +11668,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="D4" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="E4" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="F4" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="G4" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="H4" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="I4" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="J4" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="K4" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -10229,7 +11700,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10253,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10261,7 +11732,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -10285,7 +11756,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10293,7 +11764,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -10317,7 +11788,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10325,7 +11796,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -10349,7 +11820,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -10380,16 +11851,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="E1" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="F1" t="s">
-        <v>413</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10406,7 +11877,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -10419,10 +11890,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10433,13 +11904,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>416</v>
+        <v>451</v>
       </c>
       <c r="D4" t="s">
-        <v>417</v>
+        <v>452</v>
       </c>
       <c r="E4" t="s">
-        <v>418</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10447,7 +11918,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10456,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>420</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10464,7 +11935,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10473,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10481,7 +11952,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -10490,7 +11961,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10498,7 +11969,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10507,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10545,43 +12016,43 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="C1" t="s">
-        <v>428</v>
+        <v>463</v>
       </c>
       <c r="D1" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E1" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="F1" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="G1" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="H1" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="I1" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="J1" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="K1" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="L1" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="M1" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="N1" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -10595,19 +12066,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="H2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -10633,43 +12104,43 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="J3" t="s">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="K3" t="s">
-        <v>450</v>
+        <v>485</v>
       </c>
       <c r="L3" t="s">
-        <v>451</v>
+        <v>486</v>
       </c>
       <c r="M3" t="s">
-        <v>452</v>
+        <v>487</v>
       </c>
       <c r="N3" t="s">
-        <v>453</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -10677,60 +12148,60 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>454</v>
+        <v>489</v>
       </c>
       <c r="C4" t="s">
-        <v>455</v>
+        <v>490</v>
       </c>
       <c r="D4" t="s">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="E4" t="s">
-        <v>457</v>
+        <v>492</v>
       </c>
       <c r="F4" t="s">
-        <v>458</v>
+        <v>493</v>
       </c>
       <c r="G4" t="s">
-        <v>459</v>
+        <v>494</v>
       </c>
       <c r="H4" t="s">
-        <v>460</v>
+        <v>495</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="J4" t="s">
-        <v>461</v>
+        <v>496</v>
       </c>
       <c r="K4" t="s">
-        <v>462</v>
+        <v>497</v>
       </c>
       <c r="L4" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="M4" t="s">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="N4" t="s">
-        <v>465</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>466</v>
+        <v>501</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -10742,39 +12213,39 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="J5" t="s">
-        <v>469</v>
+        <v>504</v>
       </c>
       <c r="K5" t="s">
-        <v>470</v>
+        <v>505</v>
       </c>
       <c r="L5" t="s">
-        <v>471</v>
+        <v>506</v>
       </c>
       <c r="M5" t="s">
-        <v>472</v>
+        <v>507</v>
       </c>
       <c r="N5" t="s">
-        <v>473</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>474</v>
+        <v>509</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -10786,39 +12257,39 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="J6" t="s">
-        <v>476</v>
+        <v>511</v>
       </c>
       <c r="K6" t="s">
-        <v>477</v>
+        <v>512</v>
       </c>
       <c r="L6" t="s">
-        <v>478</v>
+        <v>513</v>
       </c>
       <c r="M6" t="s">
-        <v>479</v>
+        <v>514</v>
       </c>
       <c r="N6" t="s">
-        <v>480</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>481</v>
+        <v>516</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -10830,39 +12301,39 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>482</v>
+        <v>517</v>
       </c>
       <c r="J7" t="s">
-        <v>483</v>
+        <v>518</v>
       </c>
       <c r="K7" t="s">
-        <v>484</v>
+        <v>519</v>
       </c>
       <c r="L7" t="s">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="M7" t="s">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="N7" t="s">
-        <v>487</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>488</v>
+        <v>523</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -10874,39 +12345,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="J8" t="s">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="K8" t="s">
-        <v>491</v>
+        <v>526</v>
       </c>
       <c r="L8" t="s">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="M8" t="s">
-        <v>493</v>
+        <v>528</v>
       </c>
       <c r="N8" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>495</v>
+        <v>530</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -10918,39 +12389,39 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>496</v>
+        <v>531</v>
       </c>
       <c r="J9" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="K9" t="s">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="L9" t="s">
-        <v>499</v>
+        <v>534</v>
       </c>
       <c r="M9" t="s">
-        <v>500</v>
+        <v>535</v>
       </c>
       <c r="N9" t="s">
-        <v>501</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>502</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>467</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
@@ -10962,39 +12433,39 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="J10" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="K10" t="s">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="L10" t="s">
-        <v>506</v>
+        <v>541</v>
       </c>
       <c r="M10" t="s">
-        <v>507</v>
+        <v>542</v>
       </c>
       <c r="N10" t="s">
-        <v>508</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -11006,39 +12477,39 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="J11" t="s">
-        <v>511</v>
+        <v>546</v>
       </c>
       <c r="K11" t="s">
-        <v>512</v>
+        <v>547</v>
       </c>
       <c r="L11" t="s">
-        <v>513</v>
+        <v>548</v>
       </c>
       <c r="M11" t="s">
-        <v>514</v>
+        <v>549</v>
       </c>
       <c r="N11" t="s">
-        <v>515</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -11050,39 +12521,39 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>517</v>
+        <v>552</v>
       </c>
       <c r="J12" t="s">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="K12" t="s">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="L12" t="s">
-        <v>520</v>
+        <v>555</v>
       </c>
       <c r="M12" t="s">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="N12" t="s">
-        <v>522</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>523</v>
+        <v>558</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -11094,39 +12565,39 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>524</v>
+        <v>559</v>
       </c>
       <c r="J13" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="K13" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="L13" t="s">
-        <v>527</v>
+        <v>562</v>
       </c>
       <c r="M13" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="N13" t="s">
-        <v>529</v>
+        <v>564</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F14" t="s">
         <v>73</v>
@@ -11138,39 +12609,39 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="J14" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="K14" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="L14" t="s">
-        <v>534</v>
+        <v>569</v>
       </c>
       <c r="M14" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
       <c r="N14" t="s">
-        <v>536</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>537</v>
+        <v>572</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F15" t="s">
         <v>78</v>
@@ -11182,42 +12653,42 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>538</v>
+        <v>573</v>
       </c>
       <c r="J15" t="s">
-        <v>539</v>
+        <v>574</v>
       </c>
       <c r="K15" t="s">
-        <v>540</v>
+        <v>575</v>
       </c>
       <c r="L15" t="s">
-        <v>541</v>
+        <v>576</v>
       </c>
       <c r="M15" t="s">
-        <v>542</v>
+        <v>577</v>
       </c>
       <c r="N15" t="s">
-        <v>543</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>544</v>
+        <v>579</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F16" t="s">
-        <v>546</v>
+        <v>581</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -11226,42 +12697,42 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>547</v>
+        <v>582</v>
       </c>
       <c r="J16" t="s">
-        <v>548</v>
+        <v>583</v>
       </c>
       <c r="K16" t="s">
-        <v>549</v>
+        <v>584</v>
       </c>
       <c r="L16" t="s">
-        <v>550</v>
+        <v>585</v>
       </c>
       <c r="M16" t="s">
-        <v>551</v>
+        <v>586</v>
       </c>
       <c r="N16" t="s">
-        <v>552</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>553</v>
+        <v>588</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F17" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -11270,42 +12741,42 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>555</v>
+        <v>590</v>
       </c>
       <c r="J17" t="s">
-        <v>556</v>
+        <v>591</v>
       </c>
       <c r="K17" t="s">
-        <v>557</v>
+        <v>592</v>
       </c>
       <c r="L17" t="s">
-        <v>558</v>
+        <v>593</v>
       </c>
       <c r="M17" t="s">
-        <v>559</v>
+        <v>594</v>
       </c>
       <c r="N17" t="s">
-        <v>560</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>561</v>
+        <v>596</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F18" t="s">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11314,42 +12785,42 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>563</v>
+        <v>598</v>
       </c>
       <c r="J18" t="s">
-        <v>564</v>
+        <v>599</v>
       </c>
       <c r="K18" t="s">
-        <v>565</v>
+        <v>600</v>
       </c>
       <c r="L18" t="s">
-        <v>566</v>
+        <v>601</v>
       </c>
       <c r="M18" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="N18" t="s">
-        <v>568</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>569</v>
+        <v>604</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F19" t="s">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -11358,42 +12829,42 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="J19" t="s">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="K19" t="s">
-        <v>573</v>
+        <v>608</v>
       </c>
       <c r="L19" t="s">
-        <v>574</v>
+        <v>609</v>
       </c>
       <c r="M19" t="s">
-        <v>575</v>
+        <v>610</v>
       </c>
       <c r="N19" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F20" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -11402,42 +12873,42 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="J20" t="s">
-        <v>580</v>
+        <v>615</v>
       </c>
       <c r="K20" t="s">
-        <v>581</v>
+        <v>616</v>
       </c>
       <c r="L20" t="s">
-        <v>582</v>
+        <v>617</v>
       </c>
       <c r="M20" t="s">
-        <v>583</v>
+        <v>618</v>
       </c>
       <c r="N20" t="s">
-        <v>584</v>
+        <v>619</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>585</v>
+        <v>620</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F21" t="s">
-        <v>586</v>
+        <v>621</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -11446,42 +12917,42 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>587</v>
+        <v>622</v>
       </c>
       <c r="J21" t="s">
-        <v>588</v>
+        <v>623</v>
       </c>
       <c r="K21" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="L21" t="s">
-        <v>590</v>
+        <v>625</v>
       </c>
       <c r="M21" t="s">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="N21" t="s">
-        <v>592</v>
+        <v>627</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>593</v>
+        <v>628</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="F22" t="s">
-        <v>594</v>
+        <v>629</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -11490,42 +12961,42 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>595</v>
+        <v>630</v>
       </c>
       <c r="J22" t="s">
-        <v>596</v>
+        <v>631</v>
       </c>
       <c r="K22" t="s">
-        <v>597</v>
+        <v>632</v>
       </c>
       <c r="L22" t="s">
-        <v>598</v>
+        <v>633</v>
       </c>
       <c r="M22" t="s">
-        <v>599</v>
+        <v>634</v>
       </c>
       <c r="N22" t="s">
-        <v>600</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="F23" t="s">
-        <v>603</v>
+        <v>638</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -11534,42 +13005,42 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>604</v>
+        <v>639</v>
       </c>
       <c r="J23" t="s">
-        <v>605</v>
+        <v>640</v>
       </c>
       <c r="K23" t="s">
-        <v>606</v>
+        <v>641</v>
       </c>
       <c r="L23" t="s">
-        <v>607</v>
+        <v>642</v>
       </c>
       <c r="M23" t="s">
-        <v>608</v>
+        <v>643</v>
       </c>
       <c r="N23" t="s">
-        <v>609</v>
+        <v>644</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="F24" t="s">
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -11578,42 +13049,42 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>612</v>
+        <v>647</v>
       </c>
       <c r="J24" t="s">
-        <v>613</v>
+        <v>648</v>
       </c>
       <c r="K24" t="s">
-        <v>614</v>
+        <v>649</v>
       </c>
       <c r="L24" t="s">
-        <v>615</v>
+        <v>650</v>
       </c>
       <c r="M24" t="s">
-        <v>616</v>
+        <v>651</v>
       </c>
       <c r="N24" t="s">
-        <v>617</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>618</v>
+        <v>653</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="F25" t="s">
-        <v>619</v>
+        <v>654</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -11622,22 +13093,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>621</v>
+        <v>656</v>
       </c>
       <c r="L25" t="s">
-        <v>622</v>
+        <v>657</v>
       </c>
       <c r="M25" t="s">
-        <v>623</v>
+        <v>658</v>
       </c>
       <c r="N25" t="s">
-        <v>624</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -11645,13 +13116,13 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>625</v>
+        <v>660</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -11663,22 +13134,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>627</v>
+        <v>662</v>
       </c>
       <c r="J26" t="s">
-        <v>628</v>
+        <v>663</v>
       </c>
       <c r="K26" t="s">
-        <v>629</v>
+        <v>664</v>
       </c>
       <c r="L26" t="s">
-        <v>630</v>
+        <v>665</v>
       </c>
       <c r="M26" t="s">
-        <v>631</v>
+        <v>666</v>
       </c>
       <c r="N26" t="s">
-        <v>632</v>
+        <v>667</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -11686,16 +13157,16 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>633</v>
+        <v>668</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="F27" t="s">
-        <v>634</v>
+        <v>669</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -11704,39 +13175,39 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>635</v>
+        <v>670</v>
       </c>
       <c r="J27" t="s">
-        <v>636</v>
+        <v>671</v>
       </c>
       <c r="K27" t="s">
-        <v>637</v>
+        <v>672</v>
       </c>
       <c r="L27" t="s">
-        <v>638</v>
+        <v>673</v>
       </c>
       <c r="M27" t="s">
-        <v>639</v>
+        <v>674</v>
       </c>
       <c r="N27" t="s">
-        <v>640</v>
+        <v>675</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>641</v>
+        <v>676</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -11748,39 +13219,39 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>642</v>
+        <v>677</v>
       </c>
       <c r="J28" t="s">
-        <v>643</v>
+        <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>644</v>
+        <v>679</v>
       </c>
       <c r="L28" t="s">
-        <v>645</v>
+        <v>680</v>
       </c>
       <c r="M28" t="s">
-        <v>646</v>
+        <v>681</v>
       </c>
       <c r="N28" t="s">
-        <v>647</v>
+        <v>682</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>648</v>
+        <v>683</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -11792,39 +13263,39 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>649</v>
+        <v>684</v>
       </c>
       <c r="J29" t="s">
-        <v>650</v>
+        <v>685</v>
       </c>
       <c r="K29" t="s">
-        <v>651</v>
+        <v>686</v>
       </c>
       <c r="L29" t="s">
-        <v>652</v>
+        <v>687</v>
       </c>
       <c r="M29" t="s">
-        <v>653</v>
+        <v>688</v>
       </c>
       <c r="N29" t="s">
-        <v>654</v>
+        <v>689</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>655</v>
+        <v>690</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -11836,42 +13307,42 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>656</v>
+        <v>691</v>
       </c>
       <c r="J30" t="s">
-        <v>657</v>
+        <v>692</v>
       </c>
       <c r="K30" t="s">
-        <v>658</v>
+        <v>693</v>
       </c>
       <c r="L30" t="s">
-        <v>659</v>
+        <v>694</v>
       </c>
       <c r="M30" t="s">
-        <v>660</v>
+        <v>695</v>
       </c>
       <c r="N30" t="s">
-        <v>661</v>
+        <v>696</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>662</v>
+        <v>697</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="F31" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -11880,22 +13351,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>663</v>
+        <v>698</v>
       </c>
       <c r="J31" t="s">
-        <v>664</v>
+        <v>699</v>
       </c>
       <c r="K31" t="s">
-        <v>665</v>
+        <v>700</v>
       </c>
       <c r="L31" t="s">
-        <v>666</v>
+        <v>701</v>
       </c>
       <c r="M31" t="s">
-        <v>667</v>
+        <v>702</v>
       </c>
       <c r="N31" t="s">
-        <v>668</v>
+        <v>703</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -11903,16 +13374,16 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>669</v>
+        <v>704</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F32" t="s">
-        <v>670</v>
+        <v>705</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -11921,22 +13392,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>671</v>
+        <v>706</v>
       </c>
       <c r="J32" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="K32" t="s">
-        <v>673</v>
+        <v>708</v>
       </c>
       <c r="L32" t="s">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="M32" t="s">
-        <v>675</v>
+        <v>710</v>
       </c>
       <c r="N32" t="s">
-        <v>676</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -6928,10 +6928,10 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -6986,10 +6986,10 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="G8">
         <v>0.5</v>
@@ -7073,7 +7073,7 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F11">
         <v>1.2</v>
@@ -7102,10 +7102,10 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G12">
         <v>0</v>
